--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -112,29 +112,51 @@
     <t xml:space="preserve">Divide el dataset en 5 particiones iguales de forma stratified. Además, convierte el dataset a string.</t>
   </si>
   <si>
-    <t xml:space="preserve">CIC18__sin_balanceo__v1__train.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIC18__sin_balanceo__v1__train__1_5.csv
-CIC18__sin_balanceo__v1__train__2_5.csv
-CIC18__sin_balanceo__v1__train__3_5.csv
-CIC18__sin_balanceo__v1__train__4_5.csv
-CIC18__sin_balanceo__v1__train__5_5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIC18__sin_balanceo__v1__ENN_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar la técnica ENN.</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIC18__sin_balanceo__v1__train.csv
 CIC18__sin_balanceo__v1__test.csv</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__sin_balanceo__v1__train.csv
+pd_CIC18__sin_balanceo__v1__test.csv
+pd_CIC18__sin_balanceo__v1__train__1.csv
+pd_CIC18__sin_balanceo__v1__val__1.csv
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__sin_balanceo__v1__train__2.csv
+pd_CIC18__sin_balanceo__v1__val__2.csv
+pd_CIC18__sin_balanceo__v1__train__3.csv
+pd_CIC18__sin_balanceo__v1__val__3.csv
+pd_CIC18__sin_balanceo__v1__train__4.csv
+pd_CIC18__sin_balanceo__v1__val__4.csv
+pd_CIC18__sin_balanceo__v1__train__5.csv
+Pd_CIC18__sin_balanceo__v1__val__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ENN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__sin_balanceo__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicar la técnica ENN.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC18__ENN__v1__train.csv
 CIC18__ENN__v1__test.csv</t>
   </si>
@@ -142,16 +164,192 @@
     <t xml:space="preserve">CIC18__ENN__v1__transformar_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">CIC18__ENN__v1__train.csv
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__ENN__v1__train.csv
+pd_CIC18__ENN__v1__test.csv
+pd_CIC18__ENN__v1__train__1.csv
+pd_CIC18__ENN__v1__val__1.csv
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-CIC18__ENN__v1__train__1_5.csv
-CIC18__ENN__v1__train__2_5.csv
-CIC18__ENN__v1__train__3_5.csv
-CIC18__ENN__v1__train__4_5.csv
-CIC18__ENN__v1__train__5_5.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__ENN__v1__train__2.csv
+pd_CIC18__ENN__v1__val__2.csv
+pd_CIC18__ENN__v1__train__3.csv
+pd_CIC18__ENN__v1__val__3.csv
+pd_CIC18__ENN__v1__train__4.csv
+pd_CIC18__ENN__v1__val__4.csv
+pd_CIC18__ENN__v1__train__5.csv
+Pd_CIC18__ENN__v1__val__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__sin_balanceo__v1__RUS_SMOTE_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicar la técnica RUS/SMOTE. Todo lo que este por encima de 10000 hacemos RUS y lo que este por debajo hacemos SMOTE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__RUS_SMOTE__v1__train.csv
+CIC18__RUS_SMOTE__v1__test.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__RUS_SMOTE__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+CIC18__RUS_SMOTE__v1__test.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__test.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train__1.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__val__1.csv
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__train__2.csv
+pd_CIC18__RUS_SMOTE__v1__val__2.csv
+pd_CIC18__RUS_SMOTE__v1__train__3.csv
+pd_CIC18__RUS_SMOTE__v1__val__3.csv
+pd_CIC18__RUS_SMOTE__v1__train__4.csv
+pd_CIC18__RUS_SMOTE__v1__val__4.csv
+pd_CIC18__RUS_SMOTE__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE__v1__val__5.csv</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">CLASE ORIGINAL</t>
@@ -167,6 +365,9 @@
   </si>
   <si>
     <t xml:space="preserve">RUS (50/50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train (80%)</t>
   </si>
   <si>
     <t xml:space="preserve">BENIGN</t>
@@ -248,29 +449,48 @@
     <t xml:space="preserve">CIC17__cleanning__v1_division_80_20_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">CIC17__cleanning_division__v1__train.csvCIC17__cleanning_division__v1__test.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIC17__sin_balanceo__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIC17__sin_balanceo__v1__train.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIC17__sin_balanceo__v1__train__1_5.csv
-CIC17__sin_balanceo__v1__train__2_5.csv
-CIC17__sin_balanceo__v1__train__3_5.csv
-CIC17__sin_balanceo__v1__train__4_5.csv
-CIC17__sin_balanceo__v1__train__5_5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIC17__sin_balanceo__v1__ENN_v1.ipynb</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIC17__sin_balanceo__v1__train.csv
 CIC17__sin_balanceo__v1__test.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">CIC17__sin_balanceo__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__sin_balanceo__v1__train.csv
+pd_CIC17__sin_balanceo__v1__test.csv
+pd_CIC17__sin_balanceo__v1__train__1.csv
+pd_CIC17__sin_balanceo__v1__val__1.csv
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__sin_balanceo__v1__train__2.csv
+pd_CIC17__sin_balanceo__v1__val__2.csv
+pd_CIC17__sin_balanceo__v1__train__3.csv
+pd_CIC17__sin_balanceo__v1__val__3.csv
+pd_CIC17__sin_balanceo__v1__train__4.csv
+pd_CIC17__sin_balanceo__v1__val__4.csv
+pd_CIC17__sin_balanceo__v1__train__5.csv
+Pd_CIC17__sin_balanceo__v1__val__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__sin_balanceo__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__ENN__v1__train.csv
 CIC17__ENN__v1__test.csv</t>
   </si>
@@ -278,25 +498,39 @@
     <t xml:space="preserve">CIC17__ENN__v1__transformar_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">CIC17__ENN__v1__train.csv
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__ENN__v1__train.csv
+pd_CIC17__ENN__v1__test.csv
+pd_CIC17__ENN__v1__train__1.csv
+pd_CIC17__ENN__v1__val__1.csv
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-CIC17__ENN__v1__train__1_5.csv
-CIC17__ENN__v1__train__2_5.csv
-CIC17__ENN__v1__train__3_5.csv
-CIC17__ENN__v1__train__4_5.csv
-CIC17__ENN__v1__train__5_5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUS/SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__ENN__v1__train__2.csv
+pd_CIC17__ENN__v1__val__2.csv
+pd_CIC17__ENN__v1__train__3.csv
+pd_CIC17__ENN__v1__val__3.csv
+pd_CIC17__ENN__v1__train__4.csv
+pd_CIC17__ENN__v1__val__4.csv
+pd_CIC17__ENN__v1__train__5.csv
+Pd_CIC17__ENN__v1__val__5.csv</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">CIC17__sin_balanceo__v1__RUS_SMOTE_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar la técnica RUS/SMOTE. Todo lo que este por encima de 10000 hacemos RUS y lo que este por debajo hacemos SMOTE.</t>
   </si>
   <si>
     <t xml:space="preserve">CIC17__RUS_SMOTE__v1__train.csv
@@ -306,16 +540,144 @@
     <t xml:space="preserve">CIC17__RUS_SMOTE__v1__transformar_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">CIC17__RUS_SMOTE__v1__train.csv
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+CIC17__RUS_SMOTE__v1__test.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__test.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train__1.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__val__1.csv
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-CIC17__RUS_SMOTE__v1__train__1_5.csv
-CIC17__RUS_SMOTE__v1__train__2_5.csv
-CIC17__RUS_SMOTE__v1__train__3_5.csv
-CIC17__RUS_SMOTE__v1__train__4_5.csv
-CIC17__RUS_SMOTE__v1__train__5_5.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__train__2.csv
+pd_CIC17__RUS_SMOTE__v1__val__2.csv
+pd_CIC17__RUS_SMOTE__v1__train__3.csv
+pd_CIC17__RUS_SMOTE__v1__val__3.csv
+pd_CIC17__RUS_SMOTE__v1__train__4.csv
+pd_CIC17__RUS_SMOTE__v1__val__4.csv
+pd_CIC17__RUS_SMOTE__v1__train__5.csv
+Pd_CIC17__RUS_SMOTE__v1__val__5.csv</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ORIGINAL (CIC17)</t>
@@ -402,23 +764,121 @@
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__transformar_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__train.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__train__1_5.csv
-BCCC17__sin_balanceo__v1__train__2_5.csv
-BCCC17__sin_balanceo__v1__train__3_5.csv
-BCCC17__sin_balanceo__v1__train__4_5.csv
-BCCC17__sin_balanceo__v1__train__5_5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__ENN_v1.ipynb</t>
-  </si>
-  <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__train.csv
 BCCC17__sin_balanceo__v1__test.csv</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__sin_balanceo__v1__train.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__sin_balanceo__v1__test.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__sin_balanceo__v1__train__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__sin_balanceo__v1__val__1.csv
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__sin_balanceo__v1__train__2.csv
+pd_BCCC17__sin_balanceo__v1__val__2.csv
+pd_BCCC17__sin_balanceo__v1__train__3.csv
+pd_BCCC17__sin_balanceo__v1__val__3.csv
+pd_BCCC17__sin_balanceo__v1__train__4.csv
+pd_BCCC17__sin_balanceo__v1__val__4.csv
+pd_BCCC17__sin_balanceo__v1__train__5.csv
+Pd_BCCC17__sin_balanceo__v1__val__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__sin_balanceo__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__ENN__v1__train.csv
 BCCC17__ENN__v1__test.csv</t>
   </si>
@@ -426,15 +886,188 @@
     <t xml:space="preserve">BCCC17__ENN__v1__transformar_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">BCCC17__ENN__v1__train.csv
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">ENN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">ENN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__test.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">ENN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">ENN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__val__1.csv
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__ENN__v1__train__1_5.csv
-BCCC17__ENN__v1__train__2_5.csv
-BCCC17__ENN__v1__train__3_5.csv
-BCCC17__ENN__v1__train__4_5.csv
-BCCC17__ENN__v1__train__5_5.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__ENN__v1__train__2.csv
+pd_BCCC17__ENN__v1__val__2.csv
+pd_BCCC17__ENN__v1__train__3.csv
+pd_BCCC17__ENN__v1__val__3.csv
+pd_BCCC17__ENN__v1__train__4.csv
+pd_BCCC17__ENN__v1__val__4.csv
+pd_BCCC17__ENN__v1__train__5.csv
+Pd_BCCC17__ENN__v1__val_₅.csv</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__RUS_SMOTE_v1.ipynb</t>
@@ -447,16 +1080,239 @@
     <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__transformar_v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__train.csv
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+BCCC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__test.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__test.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__train__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RUS_SMOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__v1__val__1.csv
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-BCCC17__RUS_SMOTE__v1__train__1_5.csv
-BCCC17__RUS_SMOTE__v1__train__2_5.csv
-BCCC17__RUS_SMOTE__v1__train__3_5.csv
-BCCC17__RUS_SMOTE__v1__train__4_5.csv
-BCCC17__RUS_SMOTE__v1__train__5_5.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__train__2.csv
+pd_BCCC17__RUS_SMOTE__v1__val__2.csv
+pd_BCCC17__RUS_SMOTE__v1__train__3.csv
+pd_BCCC17__RUS_SMOTE__v1__val__3.csv
+pd_BCCC17__RUS_SMOTE__v1__train__4.csv
+pd_BCCC17__RUS_SMOTE__v1__val__4.csv
+pd_BCCC17__RUS_SMOTE__v1__train__5.csv
+Pd_BCCC17__RUS_SMOTE__v1__val_₅.csv</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ORIGINAL (BCCC17)</t>
@@ -505,7 +1361,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,6 +1398,12 @@
       <name val="Cascadia Code PL"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Cascadia Code PL"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="13"/>
@@ -588,40 +1450,28 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color theme="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color theme="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
@@ -629,42 +1479,30 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color theme="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -693,7 +1531,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -722,6 +1560,30 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -730,15 +1592,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -774,123 +1628,115 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1151,7 +1997,7 @@
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="68.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="87.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="68.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="61.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="60.66"/>
@@ -1264,57 +2110,91 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="91" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="219.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="262.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="11" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>33</v>
+      <c r="D12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1337,380 +2217,480 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="35.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="19.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="19.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="21.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="21.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="17.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="33.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="13.84"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+    <row r="1" s="20" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B1" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="19" t="n">
+      <c r="C2" s="23" t="n">
         <v>13484658</v>
       </c>
-      <c r="D2" s="19" t="n">
+      <c r="D2" s="23" t="n">
         <v>13445443</v>
       </c>
-      <c r="E2" s="20" t="n">
+      <c r="E2" s="24" t="n">
         <v>2354250</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="F2" s="25" t="n">
+        <v>1883400</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="23" t="n">
         <v>686012</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="23" t="n">
         <v>668461</v>
       </c>
-      <c r="E3" s="23" t="n">
+      <c r="E3" s="28" t="n">
         <v>668461</v>
       </c>
-    </row>
-    <row r="4" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="F3" s="25" t="n">
+        <v>534769</v>
+      </c>
+      <c r="H3" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="23" t="n">
         <v>576191</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="23" t="n">
         <v>576175</v>
       </c>
-      <c r="E4" s="23" t="n">
+      <c r="E4" s="28" t="n">
         <v>576175</v>
       </c>
-    </row>
-    <row r="5" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="18" t="n">
+      <c r="F4" s="25" t="n">
+        <v>460940</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>461912</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="28" t="n">
         <v>434873</v>
       </c>
-    </row>
-    <row r="6" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="18" t="n">
+      <c r="F5" s="25" t="n">
+        <v>347898</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>286191</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="28" t="n">
         <v>282310</v>
       </c>
-    </row>
-    <row r="7" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="18" t="n">
+      <c r="F6" s="25" t="n">
+        <v>225848</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>161934</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="28" t="n">
         <v>161897</v>
       </c>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="18" t="n">
+      <c r="F7" s="25" t="n">
+        <v>129518</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="23" t="n">
         <v>187589</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="23" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="28" t="n">
         <v>117322</v>
       </c>
-    </row>
-    <row r="9" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="F8" s="25" t="n">
+        <v>93858</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="23" t="n">
         <v>41508</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="23" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="28" t="n">
         <v>41455</v>
       </c>
-    </row>
-    <row r="10" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="18" t="n">
+      <c r="F9" s="25" t="n">
+        <v>33164</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
         <v>193360</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="23" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="28" t="n">
         <v>39352</v>
       </c>
-    </row>
-    <row r="11" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="18" t="n">
+      <c r="F10" s="25" t="n">
+        <v>31482</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="23" t="n">
         <v>139890</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="23" t="n">
         <v>19462</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="28" t="n">
         <v>19462</v>
       </c>
-    </row>
-    <row r="12" s="12" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="18" t="n">
+      <c r="F11" s="25" t="n">
+        <v>15569</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" s="16" customFormat="true" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>10990</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>10285</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="28" t="n">
         <v>10285</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="18" t="n">
+      <c r="F12" s="25" t="n">
+        <v>8228</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="23" t="n">
         <v>1730</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="23" t="n">
         <v>1730</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="28" t="n">
         <v>1730</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="18" t="n">
+      <c r="F13" s="25" t="n">
+        <v>1384</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>611</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>611</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="28" t="n">
         <v>611</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="18" t="n">
+      <c r="F14" s="25" t="n">
+        <v>489</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="28" t="n">
         <v>230</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="25" t="n">
+      <c r="F15" s="25" t="n">
+        <v>184</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="31" t="n">
         <v>87</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="31" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="31" t="n">
         <v>87</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="F16" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="G16" s="32"/>
+      <c r="H16" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="16" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>16232893</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="16" t="n">
         <f aca="false">SUM(D2:D16)</f>
         <v>15799693</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="16" t="n">
         <f aca="false">SUM(E2:E16)</f>
         <v>4708500</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
+      <c r="F17" s="16" t="n">
+        <f aca="false">SUM(F2:F16)</f>
+        <v>3766800</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <f aca="false">SUM(G2:G16)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <f aca="false">SUM(H2:H16)</f>
+        <v>150000</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="28"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="19"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="28"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" s="12" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="E19" s="34"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+    </row>
+    <row r="20" s="16" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="12"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="12"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="12"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="12"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="12"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="12"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="12"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="12"/>
+      <c r="G28" s="16"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1732,21 +2712,21 @@
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="55.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="55.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="32.23"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="36" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -1755,288 +2735,288 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
-      <c r="B2" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
-      <c r="B3" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="B3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
-      <c r="B4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
-      <c r="B5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="91" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="D6" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+    </row>
+    <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="D7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="116.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="E8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+    </row>
+    <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="D9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
     </row>
     <row r="10" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-    </row>
-    <row r="11" s="2" customFormat="true" ht="116.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" s="2" customFormat="true" ht="214.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2057,482 +3037,482 @@
   <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="45.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="21.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="34.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="30.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="25.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="8" style="12" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="45.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="26.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="21.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="34.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="30.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="25.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="8" style="16" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="35" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="33" t="s">
+    <row r="1" s="42" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="D1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="G1" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="37" t="n">
+      <c r="A2" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="44" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="38" t="n">
+      <c r="D2" s="45" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="19" t="n">
+      <c r="E2" s="23" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="39" t="n">
+      <c r="F2" s="28" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="23" t="n">
+      <c r="G2" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="37" t="n">
+      <c r="A3" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="44" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="38" t="n">
+      <c r="D3" s="45" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="23" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="39" t="n">
+      <c r="F3" s="28" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="23" t="n">
+      <c r="G3" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="37" t="n">
+      <c r="A4" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="44" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="38" t="n">
+      <c r="D4" s="45" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="23" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="28" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="23" t="n">
+      <c r="G4" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="37" t="n">
+      <c r="A5" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="44" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="45" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="28" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="37" t="n">
+      <c r="A6" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="44" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="45" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="28" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="37" t="n">
+      <c r="A7" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="44" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="45" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="28" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="37" t="n">
+      <c r="A8" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="44" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="45" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="23" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="28" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="37" t="n">
+      <c r="A9" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="44" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="45" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="28" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="37" t="n">
+      <c r="A10" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="44" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="45" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="28" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="37" t="n">
+      <c r="A11" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="44" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D11" s="45" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="28" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="37" t="n">
+      <c r="A12" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="44" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D12" s="45" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="28" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="37" t="n">
+      <c r="A13" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="44" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C13" s="44" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="45" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="23" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="28" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="37" t="n">
+      <c r="A14" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="44" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D14" s="45" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="37" t="n">
+      <c r="A15" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="44" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="44" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="38" t="n">
+      <c r="D15" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="46" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="42" t="n">
+      <c r="A16" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C16" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="42" t="n">
+      <c r="D16" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="16" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>2830743</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="16" t="n">
         <f aca="false">SUM(D2:D16)</f>
         <v>2520792</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="16" t="n">
         <f aca="false">SUM(E2:E16)</f>
         <v>2016633</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="16" t="n">
         <f aca="false">SUM(F2:F16)</f>
         <v>1988935</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="16" t="n">
         <f aca="false">SUM(G2:G16)</f>
         <v>150000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="28"/>
-      <c r="F18" s="18"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="28"/>
-      <c r="F19" s="18"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="A20" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="16" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="16" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19"/>
+      <c r="B21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
+      <c r="B22" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19"/>
+      <c r="B23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19"/>
+      <c r="B24" s="23"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="19"/>
+      <c r="B25" s="23"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19"/>
+      <c r="B26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="19"/>
+      <c r="B27" s="23"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="19"/>
+      <c r="B28" s="23"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="19"/>
+      <c r="B29" s="23"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="19"/>
+      <c r="B30" s="23"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="19"/>
+      <c r="B31" s="23"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19"/>
+      <c r="B32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
+      <c r="B33" s="23"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
+      <c r="B34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
+      <c r="B35" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2554,10 +3534,10 @@
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="70.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="77.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="65.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="70.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="77.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="65.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2576,364 +3556,364 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
+        <v>101</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="115.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="101.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+    </row>
+    <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+    </row>
+    <row r="10" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-    </row>
-    <row r="10" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="45" t="s">
+      <c r="C10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="46" t="s">
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+    </row>
+    <row r="11" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-    </row>
-    <row r="11" s="48" customFormat="true" ht="111.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="45" t="s">
+      <c r="C11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="46" t="s">
+      <c r="E11" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2954,363 +3934,413 @@
   <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="28.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="17.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="30.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="18.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="25.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="12.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="24.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="26.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="28.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="30.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="18.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="25.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="26.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="24.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="49" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="14" t="s">
+    <row r="1" s="51" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-    </row>
-    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="B2" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>1786239</v>
+      </c>
+      <c r="D2" s="28" t="n">
+        <v>1785037</v>
+      </c>
+      <c r="E2" s="23" t="n">
+        <v>1428029</v>
+      </c>
+      <c r="F2" s="28" t="n">
+        <v>1427700</v>
+      </c>
+      <c r="G2" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="19" t="n">
-        <v>1786239</v>
-      </c>
-      <c r="D2" s="39" t="n">
-        <v>1785037</v>
-      </c>
-      <c r="E2" s="19" t="n">
-        <v>1428029</v>
-      </c>
-      <c r="F2" s="23" t="n">
-        <v>1427700</v>
-      </c>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
+      <c r="B3" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="23" t="n">
+        <v>349240</v>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>346201</v>
+      </c>
+      <c r="E3" s="23" t="n">
+        <v>276961</v>
+      </c>
+      <c r="F3" s="28" t="n">
+        <v>275565</v>
+      </c>
+      <c r="G3" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>349240</v>
-      </c>
-      <c r="D3" s="39" t="n">
-        <v>346201</v>
-      </c>
-      <c r="E3" s="19" t="n">
-        <v>276961</v>
-      </c>
-      <c r="F3" s="23" t="n">
-        <v>275565</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+      <c r="B4" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>161323</v>
+      </c>
+      <c r="D4" s="28" t="n">
+        <v>161323</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>129058</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>129044</v>
+      </c>
+      <c r="G4" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>161323</v>
-      </c>
-      <c r="D4" s="39" t="n">
-        <v>161323</v>
-      </c>
-      <c r="E4" s="19" t="n">
-        <v>129058</v>
-      </c>
-      <c r="F4" s="23" t="n">
-        <v>129044</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="B5" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>95733</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>95729</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>76583</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>75502</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>9531</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>9531</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>7625</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>7608</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>95733</v>
-      </c>
-      <c r="D5" s="39" t="n">
-        <v>95729</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>76583</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>75502</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>9531</v>
-      </c>
-      <c r="D6" s="39" t="n">
-        <v>9531</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>7625</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>7608</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>8364</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>8364</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>6691</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>6423</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B8" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>6860</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>6856</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>5485</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>5325</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>5949</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>5949</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>4759</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>4732</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>5508</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>5508</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>4406</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>4393</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>5123</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>4098</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>2734</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>2733</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>2187</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>2176</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>1358</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>1076</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="n">
-        <v>8364</v>
-      </c>
-      <c r="D7" s="39" t="n">
-        <v>8364</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>6691</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>6423</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>6860</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>6856</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>5485</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>5325</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>5949</v>
-      </c>
-      <c r="D9" s="39" t="n">
-        <v>5949</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>4759</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>4732</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>5508</v>
-      </c>
-      <c r="D10" s="39" t="n">
-        <v>5508</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>4406</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>4393</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>5177</v>
-      </c>
-      <c r="D11" s="39" t="n">
-        <v>5123</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>4098</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>3980</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="18" t="n">
+      <c r="G14" s="46" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="n">
-        <v>2734</v>
-      </c>
-      <c r="D12" s="39" t="n">
-        <v>2733</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>2187</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>1358</v>
-      </c>
-      <c r="D13" s="39" t="n">
-        <v>1357</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>1086</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" s="39" t="n">
-        <v>24</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" s="26" t="n">
+      <c r="F15" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="27" t="n">
-        <v>10</v>
+      <c r="G15" s="50" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="16" t="n">
         <f aca="false">SUM(C2:C15)</f>
         <v>2438052</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="16" t="n">
         <f aca="false">SUM(D2:D15)</f>
         <v>2433747</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="16" t="n">
         <f aca="false">SUM(E2:E15)</f>
         <v>1946997</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="16" t="n">
         <f aca="false">SUM(F2:F15)</f>
         <v>1943539</v>
       </c>
+      <c r="G16" s="16" t="n">
+        <f aca="false">SUM(G2:G15)</f>
+        <v>140000</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="28"/>
-      <c r="F18" s="18"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="A19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="16" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="22" t="n">
         <v>48</v>
       </c>
+      <c r="G19" s="16" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I34" s="19"/>
+      <c r="I34" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="145">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -283,6 +283,9 @@
     <t xml:space="preserve">COLUMNAS:</t>
   </si>
   <si>
+    <t xml:space="preserve">CARPETA MODELOS GENERADOS</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17_eda_v1.ipynb</t>
   </si>
   <si>
@@ -383,6 +386,33 @@
 Pd_CIC17__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__training_v1__1_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__training_v1__2_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__training_v1__3_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__training_v1__4_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrenamiento con Simple T5.
+source_max_token_len=150,              
+target_max_token_len=3,             
+batch_size=16,             
+precision=32,             
+max_epochs=10,             
+use_gpu=True,             
+dataloader_num_workers=24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__train__1.csv
+pd_CIC17__RUS_SMOTE__v1__train__2.csv
+pd_CIC17__RUS_SMOTE__v1__train__3.csv
+pd_CIC17__RUS_SMOTE__v1__train__4.csv
+pd_CIC17__RUS_SMOTE__v1__train__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__outputs</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
@@ -560,358 +590,25 @@
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__sin_balanceo__v1__train.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__sin_balanceo__v1__test.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__test.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__transformar_v1.ipynb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__test.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train__1.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__val__1.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train__2.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__val__2.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train__3.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__val__3.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train__4.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__val__4.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__train__5.csv
-Pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__NearMiss_SMOTE__v1__val__5.csv</t>
-    </r>
+    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__train.csv
+BCCC17__NearMiss_SMOTE__v1__test.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__train.csv
+pd_BCCC17__NearMiss_SMOTE__v1__test.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__1.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__2.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__2.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__3.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__3.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__4.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__4.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__5.csv
+Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGINAL (BCCC17)</t>
@@ -960,7 +657,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1012,12 +709,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Cascadia Code PL"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1136,7 +827,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1277,18 +968,50 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1331,26 +1054,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1814,7 +1517,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
         <v>38</v>
       </c>
@@ -1831,7 +1534,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="180.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
         <v>38</v>
       </c>
@@ -1876,7 +1579,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="18.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="30.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="30.47"/>
   </cols>
   <sheetData>
     <row r="1" s="19" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2417,7 +2120,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.85"/>
@@ -2425,10 +2128,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="55.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="61.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="68.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="32.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.59"/>
   </cols>
   <sheetData>
-    <row r="1" s="35" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="37" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2443,6 +2146,9 @@
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>65</v>
       </c>
       <c r="G1" s="36"/>
       <c r="H1" s="36"/>
@@ -2450,312 +2156,344 @@
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="E3" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+        <v>70</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="F6" s="38"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
     </row>
     <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>75</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F7" s="38"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
+      <c r="D8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
+      <c r="E9" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
+        <v>82</v>
+      </c>
+      <c r="F10" s="38"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="214.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-    </row>
-    <row r="12" customFormat="false" ht="46.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+    </row>
+    <row r="12" s="45" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-    </row>
-    <row r="13" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="41"/>
+      <c r="F12" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+    </row>
+    <row r="14" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
+      <c r="D14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2787,7 +2525,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="9" style="15" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="49" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -2795,38 +2533,38 @@
         <v>44</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="43" t="n">
+      <c r="B2" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="43" t="n">
+      <c r="C2" s="51" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="44" t="n">
+      <c r="D2" s="52" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="22" t="n">
@@ -2838,21 +2576,21 @@
       <c r="G2" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H2" s="45" t="n">
+      <c r="H2" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="43" t="n">
+      <c r="A3" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="43" t="n">
+      <c r="C3" s="51" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="44" t="n">
+      <c r="D3" s="52" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="22" t="n">
@@ -2864,21 +2602,21 @@
       <c r="G3" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H3" s="45" t="n">
+      <c r="H3" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="43" t="n">
+      <c r="A4" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="43" t="n">
+      <c r="C4" s="51" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="44" t="n">
+      <c r="D4" s="52" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="22" t="n">
@@ -2890,21 +2628,21 @@
       <c r="G4" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H4" s="45" t="n">
+      <c r="H4" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="43" t="n">
+      <c r="A5" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="51" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="52" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="22" t="n">
@@ -2916,21 +2654,21 @@
       <c r="G5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H5" s="45" t="n">
+      <c r="H5" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="43" t="n">
+      <c r="A6" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="51" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="52" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="22" t="n">
@@ -2942,21 +2680,21 @@
       <c r="G6" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="45" t="n">
+      <c r="H6" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="43" t="n">
+      <c r="A7" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="51" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="52" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="22" t="n">
@@ -2968,21 +2706,21 @@
       <c r="G7" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="43" t="n">
+      <c r="A8" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="51" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="52" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="22" t="n">
@@ -2994,21 +2732,21 @@
       <c r="G8" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="43" t="n">
+      <c r="A9" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="51" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="52" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="22" t="n">
@@ -3020,21 +2758,21 @@
       <c r="G9" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="43" t="n">
+      <c r="A10" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="51" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="52" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="22" t="n">
@@ -3046,21 +2784,21 @@
       <c r="G10" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="51" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="52" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="22" t="n">
@@ -3072,21 +2810,21 @@
       <c r="G11" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="43" t="n">
+      <c r="A12" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="43" t="n">
+      <c r="C12" s="51" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="52" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="22" t="n">
@@ -3098,21 +2836,21 @@
       <c r="G12" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="43" t="n">
+      <c r="A13" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="51" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="52" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="22" t="n">
@@ -3124,21 +2862,21 @@
       <c r="G13" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="43" t="n">
+      <c r="A14" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="43" t="n">
+      <c r="C14" s="51" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="52" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="22" t="n">
@@ -3150,21 +2888,21 @@
       <c r="G14" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H14" s="45" t="n">
+      <c r="H14" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="43" t="n">
+      <c r="A15" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C15" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="52" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="22" t="n">
@@ -3176,21 +2914,21 @@
       <c r="G15" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H15" s="45" t="n">
+      <c r="H15" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="47" t="n">
+      <c r="A16" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="55" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="30" t="n">
@@ -3202,7 +2940,7 @@
       <c r="G16" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="H16" s="48" t="n">
+      <c r="H16" s="56" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -3241,7 +2979,7 @@
       <c r="F19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="48" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="15" t="n">
@@ -3350,133 +3088,133 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+        <v>113</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
     </row>
     <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -3486,258 +3224,258 @@
         <v>26</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
+        <v>121</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
     </row>
     <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
+        <v>123</v>
+      </c>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
+        <v>125</v>
+      </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-    </row>
-    <row r="12" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+    </row>
+    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-    </row>
-    <row r="13" customFormat="false" ht="180.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="s">
+      <c r="D12" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+    </row>
+    <row r="13" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="52" t="s">
+      <c r="B13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
+      <c r="D13" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3769,7 +3507,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="54" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="57" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -3777,13 +3515,13 @@
         <v>44</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>46</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>26</v>
@@ -3798,7 +3536,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B2" s="21" t="n">
         <v>0</v>
@@ -3818,13 +3556,13 @@
       <c r="G2" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H2" s="45" t="n">
+      <c r="H2" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B3" s="21" t="n">
         <v>1</v>
@@ -3844,13 +3582,13 @@
       <c r="G3" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H3" s="45" t="n">
+      <c r="H3" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B4" s="21" t="n">
         <v>2</v>
@@ -3870,13 +3608,13 @@
       <c r="G4" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H4" s="45" t="n">
+      <c r="H4" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B5" s="21" t="n">
         <v>3</v>
@@ -3896,13 +3634,13 @@
       <c r="G5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H5" s="45" t="n">
+      <c r="H5" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B6" s="21" t="n">
         <v>4</v>
@@ -3922,13 +3660,13 @@
       <c r="G6" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="45" t="n">
+      <c r="H6" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>5</v>
@@ -3948,13 +3686,13 @@
       <c r="G7" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>6</v>
@@ -3974,13 +3712,13 @@
       <c r="G8" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>7</v>
@@ -4000,13 +3738,13 @@
       <c r="G9" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>8</v>
@@ -4026,13 +3764,13 @@
       <c r="G10" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>9</v>
@@ -4052,13 +3790,13 @@
       <c r="G11" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>10</v>
@@ -4078,13 +3816,13 @@
       <c r="G12" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>11</v>
@@ -4104,13 +3842,13 @@
       <c r="G13" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B14" s="21" t="n">
         <v>12</v>
@@ -4130,13 +3868,13 @@
       <c r="G14" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H14" s="45" t="n">
+      <c r="H14" s="53" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="55" t="s">
-        <v>102</v>
+      <c r="A15" s="58" t="s">
+        <v>107</v>
       </c>
       <c r="B15" s="29" t="n">
         <v>13</v>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="160">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -190,6 +190,33 @@
 Pd_CIC18__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__training_v1__1_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__training_v1__2_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__training_v1__3_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__training_v1__4_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrenamiento con Simple T5.
+source_max_token_len=150,              
+target_max_token_len=3,             
+batch_size=16,             
+precision=32,             
+max_epochs=10,             
+use_gpu=True,             
+dataloader_num_workers=24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__train__1.csv
+pd_CIC18__RUS_SMOTE__v1__train__2.csv
+pd_CIC18__RUS_SMOTE__v1__train__3.csv
+pd_CIC18__RUS_SMOTE__v1__train__4.csv
+pd_CIC18__RUS_SMOTE__v1__train__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__outputs</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE</t>
   </si>
   <si>
@@ -217,6 +244,240 @@
 Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__2_5.ipynb
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__3_5.ipynb
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__4_5.ipynb
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__1.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__2.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__3.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__4.csv
+pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__outputs</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">CLASE ORIGINAL</t>
   </si>
   <si>
@@ -393,16 +654,6 @@
 pd_CIC17__RUS_SMOTE__v1__training_v1__5_5.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">Entrenamiento con Simple T5.
-source_max_token_len=150,              
-target_max_token_len=3,             
-batch_size=16,             
-precision=32,             
-max_epochs=10,             
-use_gpu=True,             
-dataloader_num_workers=24</t>
-  </si>
-  <si>
     <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__train__1.csv
 pd_CIC17__RUS_SMOTE__v1__train__2.csv
 pd_CIC17__RUS_SMOTE__v1__train__3.csv
@@ -437,6 +688,240 @@
 Pd_CIC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__2_5.ipynb
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__3_5.ipynb
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__4_5.ipynb
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__1.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__2.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__3.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__4.csv
+pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__outputs</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ORIGINAL (CIC17)</t>
   </si>
   <si>
@@ -587,6 +1072,240 @@
 Pd_BCCC17__RUS_SMOTE__v1__val_₅.csv</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__training_v1__1_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__training_v1__2_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__training_v1__3_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__training_v1__4_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__train__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__train__2.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__train__3.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__train__4.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__train__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE__v1__outputs</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
@@ -611,6 +1330,430 @@
 Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__2_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__3_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__4_5.ipynb
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__2.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__3.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__4.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__train__5.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">NearMiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_SMOTE__v1__outputs</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ORIGINAL (BCCC17)</t>
   </si>
   <si>
@@ -657,7 +1800,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -701,6 +1844,12 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Cascadia Code PL"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -827,7 +1976,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -889,6 +2038,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -968,7 +2125,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -988,20 +2145,48 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1012,51 +2197,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1313,14 +2454,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="87.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="105.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="68.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="61.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="60.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="113.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,48 +2659,83 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+    <row r="13" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="E14" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="D15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B16" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1569,12 +2746,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="35.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="19.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="19.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="21.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="21.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.34"/>
@@ -1582,535 +2759,535 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="30.47"/>
   </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="17" t="s">
+    <row r="1" s="21" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="21" t="n">
+      <c r="I1" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="22" t="n">
+      <c r="C2" s="24" t="n">
         <v>13484658</v>
       </c>
-      <c r="D2" s="22" t="n">
+      <c r="D2" s="24" t="n">
         <v>13445443</v>
       </c>
-      <c r="E2" s="23" t="n">
+      <c r="E2" s="25" t="n">
         <v>2354250</v>
       </c>
-      <c r="F2" s="22" t="n">
+      <c r="F2" s="24" t="n">
         <v>1883400</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="3" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="21" t="n">
+      <c r="G2" s="24"/>
+      <c r="H2" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="24" t="n">
         <v>686012</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="24" t="n">
         <v>668461</v>
       </c>
-      <c r="E3" s="27" t="n">
+      <c r="E3" s="29" t="n">
         <v>668461</v>
       </c>
-      <c r="F3" s="22" t="n">
+      <c r="F3" s="24" t="n">
         <v>534769</v>
       </c>
-      <c r="H3" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="4" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="21" t="n">
+      <c r="H3" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="24" t="n">
         <v>576191</v>
       </c>
-      <c r="D4" s="22" t="n">
+      <c r="D4" s="24" t="n">
         <v>576175</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="29" t="n">
         <v>576175</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="F4" s="24" t="n">
         <v>460940</v>
       </c>
-      <c r="H4" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="5" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="H4" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="24" t="n">
         <v>461912</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="24" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="29" t="n">
         <v>434873</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="24" t="n">
         <v>347898</v>
       </c>
-      <c r="H5" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="6" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="H5" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="24" t="n">
         <v>286191</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="24" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="29" t="n">
         <v>282310</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="24" t="n">
         <v>225848</v>
       </c>
-      <c r="H6" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="7" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="H6" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="24" t="n">
         <v>161934</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="24" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="29" t="n">
         <v>161897</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="24" t="n">
         <v>129518</v>
       </c>
-      <c r="H7" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="H7" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="24" t="n">
         <v>187589</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="24" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="29" t="n">
         <v>117322</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="24" t="n">
         <v>93858</v>
       </c>
-      <c r="H8" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="21" t="n">
+      <c r="H8" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="24" t="n">
         <v>41508</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="24" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="29" t="n">
         <v>41455</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="24" t="n">
         <v>33164</v>
       </c>
-      <c r="H9" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="10" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="21" t="n">
+      <c r="H9" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="24" t="n">
         <v>193360</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="24" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="29" t="n">
         <v>39352</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="24" t="n">
         <v>31482</v>
       </c>
-      <c r="H10" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="11" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="21" t="n">
+      <c r="H10" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="24" t="n">
         <v>139890</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="24" t="n">
         <v>19462</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="29" t="n">
         <v>19462</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="24" t="n">
         <v>15569</v>
       </c>
-      <c r="H11" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="12" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="21" t="n">
+      <c r="H11" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" s="17" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="24" t="n">
         <v>10990</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="24" t="n">
         <v>10285</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="29" t="n">
         <v>10285</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="24" t="n">
         <v>8228</v>
       </c>
-      <c r="H12" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="25" t="n">
+      <c r="H12" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="27" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="21" t="n">
+      <c r="A13" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="24" t="n">
         <v>1730</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="24" t="n">
         <v>1730</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="29" t="n">
         <v>1730</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="24" t="n">
         <v>1384</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="25" t="n">
+      <c r="G13" s="17"/>
+      <c r="H13" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="27" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="21" t="n">
+      <c r="A14" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="24" t="n">
         <v>611</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="24" t="n">
         <v>611</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="29" t="n">
         <v>611</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="24" t="n">
         <v>489</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="25" t="n">
+      <c r="G14" s="17"/>
+      <c r="H14" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="27" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="21" t="n">
+      <c r="A15" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="24" t="n">
         <v>230</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="24" t="n">
         <v>230</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="29" t="n">
         <v>230</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="24" t="n">
         <v>184</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="25" t="n">
+      <c r="G15" s="17"/>
+      <c r="H15" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="27" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="29" t="n">
+      <c r="A16" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="32" t="n">
         <v>87</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="32" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="32" t="n">
         <v>87</v>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="F16" s="33" t="n">
         <v>69</v>
       </c>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="32" t="n">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="34" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="17" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>16232893</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="17" t="n">
         <f aca="false">SUM(D2:D16)</f>
         <v>15799693</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">SUM(E2:E16)</f>
         <v>4708500</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">SUM(F2:F16)</f>
         <v>3766800</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">SUM(G2:G16)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">SUM(H2:H16)</f>
         <v>150000</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="17" t="n">
         <f aca="false">SUM(I2:I16)</f>
         <v>150000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="33"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="22"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="33"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-    </row>
-    <row r="20" s="15" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="15" t="n">
+      <c r="E19" s="35"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+    </row>
+    <row r="20" s="17" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="24" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="24" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="15"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="15"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="15"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="15"/>
+      <c r="G24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="15"/>
+      <c r="G25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="15"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="15"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="15"/>
+      <c r="G28" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2121,24 +3298,24 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="78.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="55.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="61.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="68.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="37" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="39" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -2147,119 +3324,119 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="F1" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="13" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
+        <v>77</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
+        <v>81</v>
+      </c>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="38"/>
+        <v>83</v>
+      </c>
+      <c r="F7" s="40"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
@@ -2268,240 +3445,256 @@
         <v>26</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="38"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
+        <v>85</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
+        <v>87</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
     </row>
     <row r="10" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
+        <v>89</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="214.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-    </row>
-    <row r="12" s="45" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+    </row>
+    <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-    </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+    </row>
+    <row r="13" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
+        <v>96</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
+        <v>98</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" customFormat="false" ht="136.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2512,547 +3705,547 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="45.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="21.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="34.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="30.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="25.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="28.18"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="9" style="15" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="45.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="26.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="21.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="34.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="30.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="25.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="28.18"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="9" style="17" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="49" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="46" t="s">
+    <row r="1" s="45" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
+      <c r="H1" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="51" t="n">
+      <c r="A2" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="51" t="n">
+      <c r="C2" s="47" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="52" t="n">
+      <c r="D2" s="48" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="22" t="n">
+      <c r="E2" s="24" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="F2" s="29" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="53" t="n">
+      <c r="G2" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="51" t="n">
+      <c r="A3" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="51" t="n">
+      <c r="C3" s="47" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="52" t="n">
+      <c r="D3" s="48" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="24" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="27" t="n">
+      <c r="F3" s="29" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="53" t="n">
+      <c r="G3" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="51" t="n">
+      <c r="A4" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="51" t="n">
+      <c r="C4" s="47" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="52" t="n">
+      <c r="D4" s="48" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="24" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="F4" s="29" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="53" t="n">
+      <c r="G4" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="51" t="n">
+      <c r="A5" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="51" t="n">
+      <c r="C5" s="47" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="48" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="24" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="29" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="53" t="n">
+      <c r="G5" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="51" t="n">
+      <c r="A6" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="47" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="48" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="24" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="29" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="53" t="n">
+      <c r="G6" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="51" t="n">
+      <c r="A7" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="47" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="48" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="24" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="29" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="53" t="n">
+      <c r="G7" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="51" t="n">
+      <c r="A8" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="51" t="n">
+      <c r="C8" s="47" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="48" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="24" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="29" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="53" t="n">
+      <c r="G8" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="51" t="n">
+      <c r="A9" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="51" t="n">
+      <c r="C9" s="47" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="48" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="24" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="29" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="53" t="n">
+      <c r="G9" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="51" t="n">
+      <c r="A10" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C10" s="47" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="48" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="24" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="29" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="53" t="n">
+      <c r="G10" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="51" t="n">
+      <c r="A11" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="51" t="n">
+      <c r="C11" s="47" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="48" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="24" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="29" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="53" t="n">
+      <c r="G11" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="51" t="n">
+      <c r="A12" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="51" t="n">
+      <c r="C12" s="47" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="52" t="n">
+      <c r="D12" s="48" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="24" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="29" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="53" t="n">
+      <c r="G12" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="51" t="n">
+      <c r="A13" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="51" t="n">
+      <c r="C13" s="47" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="48" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="24" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="29" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="53" t="n">
+      <c r="G13" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="51" t="n">
+      <c r="A14" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="51" t="n">
+      <c r="C14" s="47" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="48" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="53" t="n">
+      <c r="G14" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="51" t="n">
+      <c r="A15" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="51" t="n">
+      <c r="C15" s="47" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="48" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="53" t="n">
+      <c r="G15" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="55" t="n">
+      <c r="A16" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="55" t="n">
+      <c r="C16" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="56" t="n">
+      <c r="G16" s="32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="52" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="17" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>2830743</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="17" t="n">
         <f aca="false">SUM(D2:D16)</f>
         <v>2520792</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">SUM(E2:E16)</f>
         <v>2016633</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">SUM(F2:F16)</f>
         <v>1988935</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">SUM(G2:G16)</f>
         <v>150000</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">SUM(H2:H16)</f>
         <v>150000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="33"/>
-      <c r="F18" s="21"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="33"/>
-      <c r="F19" s="21"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="15" t="n">
+      <c r="A20" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="17" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="24" t="n">
         <v>48</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="17" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="22"/>
+      <c r="B21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="22"/>
+      <c r="B22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="22"/>
+      <c r="B23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="22"/>
+      <c r="B24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22"/>
+      <c r="B25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="22"/>
+      <c r="B26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="22"/>
+      <c r="B27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="22"/>
+      <c r="B28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="22"/>
+      <c r="B29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="22"/>
+      <c r="B30" s="24"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22"/>
+      <c r="B31" s="24"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="22"/>
+      <c r="B32" s="24"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="22"/>
+      <c r="B33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="22"/>
+      <c r="B34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="22"/>
+      <c r="B35" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3062,14 +4255,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="70.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="77.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="65.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="90.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="77.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="65.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50.6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,133 +4282,133 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
+        <v>122</v>
+      </c>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
+        <v>125</v>
+      </c>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
     </row>
     <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -3224,266 +4418,304 @@
         <v>26</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
+        <v>130</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
+        <v>132</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
     </row>
     <row r="10" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
+        <v>134</v>
+      </c>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+    </row>
+    <row r="12" s="54" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-    </row>
-    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-    </row>
-    <row r="13" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="E13" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+    </row>
+    <row r="14" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
+      <c r="D14" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+    </row>
+    <row r="15" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3494,474 +4726,474 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="28.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="17.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="30.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="18.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="25.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="33.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="24.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="26.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="28.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="30.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="18.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="25.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="26.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="24.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="57" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="17" t="s">
+    <row r="1" s="55" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="19"/>
+      <c r="H1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="21" t="n">
+      <c r="A2" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="22" t="n">
+      <c r="C2" s="24" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="D2" s="29" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="22" t="n">
+      <c r="E2" s="24" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="F2" s="29" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="53" t="n">
+      <c r="G2" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="21" t="n">
+      <c r="A3" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="24" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="27" t="n">
+      <c r="D3" s="29" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="24" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="27" t="n">
+      <c r="F3" s="29" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="53" t="n">
+      <c r="G3" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="21" t="n">
+      <c r="A4" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="24" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="D4" s="29" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="24" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="F4" s="29" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="53" t="n">
+      <c r="G4" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="A5" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="24" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="29" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="24" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="29" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="53" t="n">
+      <c r="G5" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="24" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="29" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="24" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="29" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="53" t="n">
+      <c r="G6" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="24" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="29" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="24" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="29" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="53" t="n">
+      <c r="G7" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="24" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="29" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="24" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="29" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="53" t="n">
+      <c r="G8" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="21" t="n">
+      <c r="A9" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="24" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="29" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="24" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="29" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="53" t="n">
+      <c r="G9" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="21" t="n">
+      <c r="A10" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="24" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="29" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="24" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="29" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="53" t="n">
+      <c r="G10" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" s="21" t="n">
+      <c r="A11" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="24" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="29" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="24" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="29" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="53" t="n">
+      <c r="G11" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B12" s="21" t="n">
+      <c r="A12" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="24" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="29" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="24" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="29" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="53" t="n">
+      <c r="G12" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="21" t="n">
+      <c r="A13" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="24" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="29" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="24" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="29" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="53" t="n">
+      <c r="G13" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B14" s="21" t="n">
+      <c r="A14" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="24" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="53" t="n">
+      <c r="G14" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="29" t="n">
+      <c r="A15" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="32" t="n">
+      <c r="G15" s="32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="34" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="17" t="n">
         <f aca="false">SUM(C2:C15)</f>
         <v>2438052</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="17" t="n">
         <f aca="false">SUM(D2:D15)</f>
         <v>2433747</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">SUM(E2:E15)</f>
         <v>1946997</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="17" t="n">
         <f aca="false">SUM(F2:F15)</f>
         <v>1943539</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="17" t="n">
         <f aca="false">SUM(G2:G15)</f>
         <v>140000</v>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="17" t="n">
         <f aca="false">SUM(H2:H15)</f>
         <v>140000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="33"/>
-      <c r="F18" s="21"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="15" t="n">
+      <c r="A19" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="17" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="24" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="17" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I34" s="22"/>
+      <c r="I34" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="185">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -169,25 +169,7 @@
     <t xml:space="preserve">CIC18__sin_balanceo__v1__RUS_SMOTE_v1.ipynb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Aplicar la técnica RUS/SMOTE. Todo lo que este por encima de 10000 hacemos RUS y lo que este por debajo hacemos SMOTE. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Hacemos dos test: uno con los datos que sobran (test_nuevo) y otro que sea el test original (test)</t>
-    </r>
+    <t xml:space="preserve">Aplicar la técnica RUS/SMOTE. Todo lo que este por encima de 10000 hacemos RUS y lo que este por debajo hacemos SMOTE. Hacemos dos test: uno con los datos que sobran (test_nuevo) y otro que sea el test original (test)</t>
   </si>
   <si>
     <t xml:space="preserve">CIC18__RUS_SMOTE__v1__train.csv
@@ -227,7 +209,7 @@
 precision=32,             
 max_epochs=10,             
 use_gpu=True,             
-dataloader_num_workers=24</t>
+dataloader_num_workers=16</t>
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__train__1.csv
@@ -238,6 +220,36 @@
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE + ENN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__RUS_SMOTE__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__RUS_SMOTE__v1__train.csv CIC18__RUS_SMOTE__v1__test.csv CIC18__RUS_SMOTE__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__RUS_SMOTE_ENN__v1__train.csv CIC18__RUS_SMOTE_ENN__v1__test.csv CIC18__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__RUS_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__train.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__test.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__test_nuevo.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__2.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__2.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__3.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__3.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__4.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__4.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">NearMiss/SMOTE</t>
@@ -276,6 +288,16 @@
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Entrenamiento con Simple T5. 2 horas por epoch
+source_max_token_len=150,              
+target_max_token_len=3,             
+batch_size=16,             
+precision=32,             
+max_epochs=10,             
+use_gpu=True,             
+dataloader_num_workers=16</t>
+  </si>
+  <si>
     <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__train__1.csv
 pd_CIC18__NearMiss_SMOTE__v1__train__2.csv
 pd_CIC18__NearMiss_SMOTE__v1__train__3.csv
@@ -284,6 +306,36 @@
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NearMiss/SMOTE + ENN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__NearMiss_SMOTE__v1__train.csv CIC18__NearMiss_SMOTE__v1__test.csv CIC18__NearMiss_SMOTE__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__NearMiss_SMOTE_ENN__v1__train.csv CIC18__NearMiss_SMOTE_ENN__v1__test.csv CIC18__NearMiss_SMOTE_ENN__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__NearMiss_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE_ENN__v1__train.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__test.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__test_nuevo.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">CLASE ORIGINAL</t>
@@ -474,6 +526,33 @@
     <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE__v1__train.csv CIC17__RUS_SMOTE__v1__test.csv CIC17__RUS_SMOTE__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE_ENN__v1__train.csv CIC17__RUS_SMOTE_ENN__v1__test.csv CIC17__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__train.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__test.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__test_nuevo.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__1.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__2.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__2.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__3.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__3.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__4.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__4.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
@@ -517,6 +596,33 @@
     <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">CIC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__NearMiss_SMOTE__v1__train.csv CIC17__NearMiss_SMOTE__v1__test.csv CIC17__NearMiss_SMOTE__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__NearMiss_SMOTE_ENN__v1__train.csv CIC17__NearMiss_SMOTE_ENN__v1__test.csv CIC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__NearMiss_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE_ENN__v1__train.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__test.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_CIC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">ORIGINAL (CIC17)</t>
   </si>
   <si>
@@ -647,9 +753,6 @@
   </si>
   <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__RUS_SMOTE_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar la técnica RUS/SMOTE. Todo lo que este por encima de 10000 hacemos RUS y lo que este por debajo hacemos SMOTE. Hacemos dos test: uno con los datos que sobran (test_nuevo) y otro que sea el test original (test)</t>
   </si>
   <si>
     <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__train.csv
@@ -778,8 +881,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -827,10 +931,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <u val="single"/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Cascadia Code PL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -841,7 +947,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -851,7 +957,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF81D41A"/>
-        <bgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FF77BC65"/>
       </patternFill>
     </fill>
     <fill>
@@ -862,26 +968,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EA6B"/>
-        <bgColor rgb="FFFFFF6D"/>
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77BC65"/>
+        <bgColor rgb="FF81D41A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF6D"/>
-        <bgColor rgb="FFD4EA6B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -922,13 +1022,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right/>
       <top/>
@@ -940,6 +1033,13 @@
       <right/>
       <top/>
       <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -975,7 +1075,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1016,74 +1116,50 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1113,15 +1189,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1132,140 +1204,120 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1314,11 +1366,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFDDDDDD"/>
-      <rgbColor rgb="FFFFFF6D"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFD4EA6B"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
@@ -1326,7 +1378,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF77BC65"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1517,15 +1569,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="105.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="67.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="68.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="61.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="60.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="113.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="48.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1613,200 +1665,272 @@
       <c r="F5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="17"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="219.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="17"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="262.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="17"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="17"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="17"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="16" t="s">
+      <c r="E13" s="15"/>
+      <c r="F13" s="17" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="24"/>
-    </row>
-    <row r="15" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="E16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="16" customFormat="false" ht="187.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="23" t="s">
+      <c r="D17" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="187.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="26" t="s">
-        <v>50</v>
-      </c>
+      <c r="B18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="17"/>
+    </row>
+    <row r="20" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="20"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1836,442 +1960,580 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="18.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="30.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="31.21"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="28" t="s">
+    <row r="1" s="24" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="XFD1" s="0"/>
-    </row>
-    <row r="2" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="32" t="n">
+      <c r="K1" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="XFD1" s="2"/>
+    </row>
+    <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="33" t="n">
+      <c r="C2" s="27" t="n">
         <v>13484658</v>
       </c>
-      <c r="D2" s="33" t="n">
+      <c r="D2" s="27" t="n">
         <v>13445443</v>
       </c>
-      <c r="E2" s="34" t="n">
-        <v>2354250</v>
-      </c>
-      <c r="F2" s="33" t="n">
-        <v>1883400</v>
-      </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD2" s="0"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="32" t="n">
+      <c r="E2" s="27" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>339865</v>
+      </c>
+      <c r="H2" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD2" s="2"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="33" t="n">
+      <c r="C3" s="27" t="n">
         <v>686012</v>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="27" t="n">
         <v>668461</v>
       </c>
-      <c r="E3" s="38" t="n">
-        <v>668461</v>
-      </c>
-      <c r="F3" s="33" t="n">
-        <v>534769</v>
-      </c>
-      <c r="H3" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD3" s="0"/>
-    </row>
-    <row r="4" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="32" t="n">
+      <c r="E3" s="27" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>359280</v>
+      </c>
+      <c r="H3" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="29" t="n">
+        <v>9840</v>
+      </c>
+      <c r="K3" s="29" t="n">
+        <v>9993</v>
+      </c>
+      <c r="XFD3" s="2"/>
+    </row>
+    <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="27" t="n">
         <v>576191</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="27" t="n">
         <v>576175</v>
       </c>
-      <c r="E4" s="38" t="n">
-        <v>576175</v>
-      </c>
-      <c r="F4" s="33" t="n">
-        <v>460940</v>
-      </c>
-      <c r="H4" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD4" s="0"/>
-    </row>
-    <row r="5" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="32" t="n">
+      <c r="E4" s="27" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>359369</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="29" t="n">
+        <v>9974</v>
+      </c>
+      <c r="K4" s="29" t="n">
+        <v>9968</v>
+      </c>
+      <c r="XFD4" s="2"/>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="27" t="n">
         <v>461912</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="27" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="31" t="n">
         <v>434873</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="27" t="n">
         <v>347898</v>
       </c>
-      <c r="H5" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD5" s="0"/>
-    </row>
-    <row r="6" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="32" t="n">
+      <c r="G5" s="27" t="n">
+        <v>346118</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>9855</v>
+      </c>
+      <c r="K5" s="29" t="n">
+        <v>9914</v>
+      </c>
+      <c r="XFD5" s="2"/>
+    </row>
+    <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="27" t="n">
         <v>286191</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="27" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="31" t="n">
         <v>282310</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="27" t="n">
         <v>225848</v>
       </c>
-      <c r="H6" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD6" s="0"/>
-    </row>
-    <row r="7" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="32" t="n">
+      <c r="G6" s="27" t="n">
+        <v>225602</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>9971</v>
+      </c>
+      <c r="K6" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD6" s="2"/>
+    </row>
+    <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="27" t="n">
         <v>161934</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="27" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="31" t="n">
         <v>161897</v>
       </c>
-      <c r="F7" s="33" t="n">
-        <v>129518</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD7" s="0"/>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="32" t="n">
+      <c r="F7" s="27" t="n">
+        <v>129517</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>108526</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>8820</v>
+      </c>
+      <c r="K7" s="29" t="n">
+        <v>9998</v>
+      </c>
+      <c r="XFD7" s="2"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="27" t="n">
         <v>187589</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="27" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="31" t="n">
         <v>117322</v>
       </c>
-      <c r="F8" s="33" t="n">
-        <v>93858</v>
-      </c>
-      <c r="H8" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD8" s="0"/>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="32" t="n">
+      <c r="F8" s="27" t="n">
+        <v>93857</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>93112</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>9896</v>
+      </c>
+      <c r="K8" s="29" t="n">
+        <v>9967</v>
+      </c>
+      <c r="XFD8" s="2"/>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="27" t="n">
         <v>41508</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="27" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="31" t="n">
         <v>41455</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="27" t="n">
         <v>33164</v>
       </c>
-      <c r="H9" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD9" s="0"/>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="32" t="n">
+      <c r="G9" s="27" t="n">
+        <v>31187</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>9533</v>
+      </c>
+      <c r="K9" s="29" t="n">
+        <v>9974</v>
+      </c>
+      <c r="XFD9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="27" t="n">
         <v>193360</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="27" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="38" t="n">
+      <c r="E10" s="31" t="n">
         <v>39352</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="27" t="n">
         <v>31482</v>
       </c>
-      <c r="H10" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD10" s="0"/>
-    </row>
-    <row r="11" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
+      <c r="G10" s="27" t="n">
+        <v>31432</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="29" t="n">
+        <v>9986</v>
+      </c>
+      <c r="K10" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>139890</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>19462</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>19462</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>15570</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>15570</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>10990</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>10285</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>10285</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>8228</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>7975</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>9838</v>
+      </c>
+      <c r="K12" s="29" t="n">
+        <v>9939</v>
+      </c>
+      <c r="XFD12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>1384</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>1378</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="29" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>611</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>611</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>611</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>489</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>211</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>9624</v>
+      </c>
+      <c r="K14" s="29" t="n">
+        <v>9593</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>230</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>230</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>230</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>184</v>
+      </c>
+      <c r="G15" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="B11" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="33" t="n">
-        <v>139890</v>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>19462</v>
-      </c>
-      <c r="E11" s="38" t="n">
-        <v>19462</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>15569</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD11" s="0"/>
-    </row>
-    <row r="12" s="3" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="33" t="n">
-        <v>10990</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>10285</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>10285</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>8228</v>
-      </c>
-      <c r="H12" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="33" t="n">
-        <v>1730</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <v>1730</v>
-      </c>
-      <c r="E13" s="38" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>1384</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="33" t="n">
-        <v>611</v>
-      </c>
-      <c r="D14" s="33" t="n">
-        <v>611</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>611</v>
-      </c>
-      <c r="F14" s="33" t="n">
-        <v>489</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="36" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
+      <c r="H15" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>9673</v>
+      </c>
+      <c r="K15" s="29" t="n">
+        <v>9655</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>87</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>87</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>87</v>
+      </c>
+      <c r="F16" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="B15" s="32" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="D15" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="E15" s="38" t="n">
-        <v>230</v>
-      </c>
-      <c r="F15" s="33" t="n">
-        <v>184</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="36" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="41" t="n">
-        <v>87</v>
-      </c>
-      <c r="D16" s="41" t="n">
-        <v>87</v>
-      </c>
-      <c r="E16" s="41" t="n">
-        <v>87</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>69</v>
-      </c>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>10000</v>
+      <c r="G16" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>9987</v>
+      </c>
+      <c r="K16" s="29" t="n">
+        <v>9986</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,15 +2547,15 @@
       </c>
       <c r="E17" s="3" t="n">
         <f aca="false">SUM(E2:E16)</f>
-        <v>4708500</v>
+        <v>2459614</v>
       </c>
       <c r="F17" s="3" t="n">
         <f aca="false">SUM(F2:F16)</f>
-        <v>3766800</v>
+        <v>1967691</v>
       </c>
       <c r="G17" s="3" t="n">
         <f aca="false">SUM(G2:G16)</f>
-        <v>0</v>
+        <v>1919761</v>
       </c>
       <c r="H17" s="3" t="n">
         <f aca="false">SUM(H2:H16)</f>
@@ -2303,24 +2565,32 @@
         <f aca="false">SUM(I2:I16)</f>
         <v>150000</v>
       </c>
+      <c r="J17" s="36" t="n">
+        <f aca="false">SUM(J2:J16)</f>
+        <v>146997</v>
+      </c>
+      <c r="K17" s="36" t="n">
+        <f aca="false">SUM(K2:K16)</f>
+        <v>148987</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="44"/>
-      <c r="F18" s="32"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="26"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="33"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="44"/>
-      <c r="F19" s="32"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="26"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>84</v>
@@ -2337,23 +2607,23 @@
       <c r="G20" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="33" t="n">
+      <c r="H20" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="33" t="n">
+      <c r="I20" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="XFD20" s="0"/>
+      <c r="XFD20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="3"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3"/>
@@ -2389,25 +2659,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="45" width="78.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="45" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="45" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="38" width="78.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="39" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="38" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="50" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="43" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -2416,370 +2686,440 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="F1" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
-      <c r="B2" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="52" t="s">
+      <c r="B2" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="51" t="s">
+      <c r="D2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
-      <c r="B3" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="55"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="B3" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
-      <c r="B4" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="52" t="s">
+      <c r="B4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="51" t="s">
+      <c r="D4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
-      <c r="B5" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="52" t="s">
+      <c r="B5" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="51" t="s">
+      <c r="D5" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
+      <c r="D6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="58" t="s">
+      <c r="B7" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="D7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="44"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="58" t="s">
+      <c r="B8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
+      <c r="D8" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="58" t="s">
+      <c r="B9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="55"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
+      <c r="D9" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
+      <c r="D10" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
+      <c r="D11" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="26" t="s">
+      <c r="D12" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+    </row>
+    <row r="13" s="47" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="17"/>
+    </row>
+    <row r="14" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-    </row>
-    <row r="13" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-    </row>
-    <row r="14" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="E15" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+    </row>
+    <row r="16" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-    </row>
-    <row r="15" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="D16" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-    </row>
-    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-    </row>
-    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-    </row>
-    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
+      <c r="D17" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+    </row>
+    <row r="18" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="20"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-    </row>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -2803,447 +3143,541 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="21.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="34.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="3" width="19.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="25.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="28.18"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="10" style="3" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="30.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="63" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="60" t="s">
+    <row r="1" s="51" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="H1" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="XFD1" s="0"/>
+      <c r="J1" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="50"/>
+      <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="65" t="n">
+      <c r="A2" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="65" t="n">
+      <c r="C2" s="53" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="66" t="n">
+      <c r="D2" s="54" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="33" t="n">
+      <c r="E2" s="27" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="38" t="n">
+      <c r="F2" s="31" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L2" s="0"/>
+      <c r="G2" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="65" t="n">
+      <c r="A3" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="65" t="n">
+      <c r="C3" s="53" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="66" t="n">
+      <c r="D3" s="54" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="33" t="n">
+      <c r="E3" s="27" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="38" t="n">
+      <c r="F3" s="31" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L3" s="0"/>
+      <c r="G3" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="29" t="n">
+        <v>9656</v>
+      </c>
+      <c r="J3" s="29" t="n">
+        <v>9968</v>
+      </c>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="65" t="n">
+      <c r="A4" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="65" t="n">
+      <c r="C4" s="53" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="66" t="n">
+      <c r="D4" s="54" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="27" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="38" t="n">
+      <c r="F4" s="31" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L4" s="0"/>
+      <c r="G4" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>9765</v>
+      </c>
+      <c r="J4" s="29" t="n">
+        <v>9995</v>
+      </c>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="65" t="n">
+      <c r="A5" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="53" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="66" t="n">
+      <c r="D5" s="54" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="27" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="38" t="n">
+      <c r="F5" s="31" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L5" s="0"/>
+      <c r="G5" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>9712</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>9960</v>
+      </c>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="65" t="n">
+      <c r="A6" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="65" t="n">
+      <c r="C6" s="53" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="66" t="n">
+      <c r="D6" s="54" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="27" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="31" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L6" s="0"/>
+      <c r="G6" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>9913</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>9958</v>
+      </c>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="65" t="n">
+      <c r="A7" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="53" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="54" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="27" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="38" t="n">
+      <c r="F7" s="31" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L7" s="0"/>
+      <c r="G7" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>9908</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>9923</v>
+      </c>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="65" t="n">
+      <c r="A8" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="65" t="n">
+      <c r="C8" s="53" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="54" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="27" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="38" t="n">
+      <c r="F8" s="31" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L8" s="0"/>
+      <c r="G8" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>9637</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>9785</v>
+      </c>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="65" t="n">
+      <c r="A9" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="65" t="n">
+      <c r="C9" s="53" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="54" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="27" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="38" t="n">
+      <c r="F9" s="31" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L9" s="0"/>
+      <c r="G9" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>9814</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>9872</v>
+      </c>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="65" t="n">
+      <c r="A10" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="65" t="n">
+      <c r="C10" s="53" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="54" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="27" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="38" t="n">
+      <c r="F10" s="31" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L10" s="0"/>
+      <c r="G10" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>9622</v>
+      </c>
+      <c r="J10" s="29" t="n">
+        <v>9637</v>
+      </c>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="65" t="n">
+      <c r="A11" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="65" t="n">
+      <c r="C11" s="53" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="54" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="27" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="38" t="n">
+      <c r="F11" s="31" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L11" s="0"/>
+      <c r="G11" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>9832</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>9979</v>
+      </c>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="65" t="n">
+      <c r="A12" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="65" t="n">
+      <c r="C12" s="53" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="54" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="27" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="38" t="n">
+      <c r="F12" s="31" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L12" s="0"/>
+      <c r="G12" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>5782</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>5793</v>
+      </c>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="65" t="n">
+      <c r="A13" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="53" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="65" t="n">
+      <c r="C13" s="53" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="54" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="27" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="38" t="n">
+      <c r="F13" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L13" s="0"/>
+      <c r="G13" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>5862</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>5871</v>
+      </c>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="65" t="n">
+      <c r="A14" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="65" t="n">
+      <c r="C14" s="53" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="54" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L14" s="0"/>
+      <c r="G14" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>9904</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>9934</v>
+      </c>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="65" t="n">
+      <c r="A15" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="65" t="n">
+      <c r="C15" s="53" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="54" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L15" s="0"/>
+      <c r="G15" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>9725</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>9727</v>
+      </c>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="69" t="n">
+      <c r="A16" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="69" t="n">
+      <c r="C16" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="69" t="n">
+      <c r="D16" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="41" t="n">
+      <c r="E16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="41" t="n">
+      <c r="F16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="41" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="70" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L16" s="0"/>
+      <c r="G16" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="3" t="n">
@@ -3270,26 +3704,34 @@
         <f aca="false">SUM(H2:H16)</f>
         <v>150000</v>
       </c>
-      <c r="L17" s="0"/>
+      <c r="I17" s="3" t="n">
+        <f aca="false">SUM(I2:I16)</f>
+        <v>139132</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <f aca="false">SUM(J2:J16)</f>
+        <v>140402</v>
+      </c>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="44"/>
-      <c r="F18" s="32"/>
-      <c r="L18" s="0"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="26"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="44"/>
-      <c r="F19" s="32"/>
-      <c r="L19" s="0"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="26"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="62" t="s">
-        <v>72</v>
+      <c r="A20" s="50" t="s">
+        <v>85</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="27" t="n">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -3304,57 +3746,57 @@
       <c r="H20" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="L20" s="0"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33"/>
-      <c r="L21" s="0"/>
+      <c r="B21" s="27"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="33"/>
-      <c r="L22" s="0"/>
+      <c r="B22" s="27"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="33"/>
-      <c r="L23" s="0"/>
+      <c r="B23" s="27"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="33"/>
-      <c r="L24" s="0"/>
+      <c r="B24" s="27"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="33"/>
-      <c r="L25" s="0"/>
+      <c r="B25" s="27"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="33"/>
+      <c r="B26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="33"/>
+      <c r="B27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="33"/>
+      <c r="B28" s="27"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="33"/>
+      <c r="B29" s="27"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="33"/>
+      <c r="B30" s="27"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="33"/>
+      <c r="B31" s="27"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="33"/>
+      <c r="B32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="33"/>
+      <c r="B33" s="27"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="33"/>
+      <c r="B34" s="27"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="33"/>
+      <c r="B35" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3400,420 +3842,420 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+        <v>141</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="58" t="s">
+      <c r="B7" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>130</v>
+      <c r="D7" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="52" t="s">
+      <c r="B8" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>132</v>
+      <c r="D8" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="58" t="s">
+      <c r="B9" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="58" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>134</v>
+      <c r="D9" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
+      <c r="B10" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
+      <c r="D11" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
+      <c r="D12" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
+      <c r="D13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="A14" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
+      <c r="D14" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="A15" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="54"/>
+      <c r="D15" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3845,411 +4287,411 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="71" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="28" t="s">
+    <row r="1" s="57" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="30"/>
-      <c r="XFD1" s="0"/>
+      <c r="H1" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="24"/>
+      <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="32" t="n">
+      <c r="A2" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="33" t="n">
+      <c r="C2" s="27" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="38" t="n">
+      <c r="D2" s="31" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="33" t="n">
+      <c r="E2" s="27" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="38" t="n">
+      <c r="F2" s="31" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="0"/>
+      <c r="G2" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="B3" s="32" t="n">
+      <c r="A3" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="33" t="n">
+      <c r="C3" s="27" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="38" t="n">
+      <c r="D3" s="31" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="33" t="n">
+      <c r="E3" s="27" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="38" t="n">
+      <c r="F3" s="31" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="0"/>
+      <c r="G3" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="32" t="n">
+      <c r="A4" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="27" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="38" t="n">
+      <c r="D4" s="31" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="27" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="38" t="n">
+      <c r="F4" s="31" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="0"/>
+      <c r="G4" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="32" t="n">
+      <c r="A5" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="27" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="31" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="27" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="38" t="n">
+      <c r="F5" s="31" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="0"/>
+      <c r="G5" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="32" t="n">
+      <c r="A6" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="27" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="31" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="27" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="31" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="0"/>
+      <c r="G6" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="32" t="n">
+      <c r="A7" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="27" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="31" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="27" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="38" t="n">
+      <c r="F7" s="31" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="0"/>
+      <c r="G7" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="32" t="n">
+      <c r="A8" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="27" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="31" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="27" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="38" t="n">
+      <c r="F8" s="31" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="0"/>
+      <c r="G8" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="32" t="n">
+      <c r="A9" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="27" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="31" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="27" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="38" t="n">
+      <c r="F9" s="31" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="0"/>
+      <c r="G9" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="32" t="n">
+      <c r="A10" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="27" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="31" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="27" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="38" t="n">
+      <c r="F10" s="31" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="0"/>
+      <c r="G10" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="32" t="n">
+      <c r="A11" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="27" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D11" s="31" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="27" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="38" t="n">
+      <c r="F11" s="31" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="0"/>
+      <c r="G11" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="32" t="n">
+      <c r="A12" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="27" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D12" s="31" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="27" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="38" t="n">
+      <c r="F12" s="31" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="0"/>
+      <c r="G12" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="32" t="n">
+      <c r="A13" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="27" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="31" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="27" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="38" t="n">
+      <c r="F13" s="31" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="0"/>
+      <c r="G13" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="32" t="n">
+      <c r="A14" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D14" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="38" t="n">
+      <c r="F14" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="0"/>
+      <c r="G14" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="40" t="n">
+      <c r="A15" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="41" t="n">
+      <c r="C15" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D15" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="41" t="n">
+      <c r="E15" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="41" t="n">
+      <c r="F15" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="41" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="43" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="0"/>
+      <c r="G15" s="34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="60" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="3" t="n">
@@ -4276,30 +4718,30 @@
         <f aca="false">SUM(H2:H15)</f>
         <v>140000</v>
       </c>
-      <c r="J16" s="0"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J17" s="0"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="44"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="27" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="32" t="n">
+      <c r="E19" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="26" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -4308,10 +4750,10 @@
       <c r="H19" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="I19" s="0"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="33"/>
+      <c r="J34" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="205">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -213,13 +213,41 @@
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__train__1.csv
+pd_CIC18__RUS_SMOTE__v1__val__1.csv
 pd_CIC18__RUS_SMOTE__v1__train__2.csv
+pd_CIC18__RUS_SMOTE__v1__val__2.csv
 pd_CIC18__RUS_SMOTE__v1__train__3.csv
+pd_CIC18__RUS_SMOTE__v1__val__3.csv
 pd_CIC18__RUS_SMOTE__v1__train__4.csv
-pd_CIC18__RUS_SMOTE__v1__train__5.csv</t>
+pd_CIC18__RUS_SMOTE__v1__val__4.csv
+pd_CIC18__RUS_SMOTE__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC18__RUS_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validación de cada epoch y elección del mejor epoch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC18__RUS_SMOTE__v1__train__1.csv
+pd_CIC18__RUS_SMOTE__v1__val__1.csv
+pd_CIC18__RUS_SMOTE__v1__train__2.csv
+pd_CIC18__RUS_SMOTE__v1__val__2.csv
+pd_CIC18__RUS_SMOTE__v1__train__3.csv
+pd_CIC18__RUS_SMOTE__v1__val__3.csv
+pd_CIC18__RUS_SMOTE__v1__train__4.csv
+pd_CIC18__RUS_SMOTE__v1__val__4.csv
+pd_CIC18__RUS_SMOTE__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">RUS/SMOTE + ENN</t>
@@ -299,13 +327,38 @@
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__train__1.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__1.csv
 pd_CIC18__NearMiss_SMOTE__v1__train__2.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__2.csv
 pd_CIC18__NearMiss_SMOTE__v1__train__3.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__3.csv
 pd_CIC18__NearMiss_SMOTE__v1__train__4.csv
-pd_CIC18__NearMiss_SMOTE__v1__train__5.csv</t>
+pd_CIC18__NearMiss_SMOTE__v1__val__4.csv
+pd_CIC18__NearMiss_SMOTE__v1__train__5.csv
+Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC18__NearMiss_SMOTE__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC18__NearMiss_SMOTE__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC18__NearMiss_SMOTE__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC18__NearMiss_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC18__NearMiss_SMOTE__v1__train__1.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__1.csv
+pd_CIC18__NearMiss_SMOTE__v1__train__2.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__2.csv
+pd_CIC18__NearMiss_SMOTE__v1__train__3.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__3.csv
+pd_CIC18__NearMiss_SMOTE__v1__train__4.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__4.csv
+pd_CIC18__NearMiss_SMOTE__v1__train__5.csv
+Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">NearMiss/SMOTE + ENN</t>
@@ -526,6 +579,26 @@
     <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC17__RUS_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC17__RUS_SMOTE__v1__train__1.csv
+pd_CIC17__RUS_SMOTE__v1__val__1.csv
+pd_CIC17__RUS_SMOTE__v1__train__2.csv
+pd_CIC17__RUS_SMOTE__v1__val__2.csv
+pd_CIC17__RUS_SMOTE__v1__train__3.csv
+pd_CIC17__RUS_SMOTE__v1__val__3.csv
+pd_CIC17__RUS_SMOTE__v1__train__4.csv
+pd_CIC17__RUS_SMOTE__v1__val__4.csv
+pd_CIC17__RUS_SMOTE__v1__train__5.csv
+Pd_CIC17__RUS_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -596,6 +669,26 @@
     <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC17__NearMiss_SMOTE__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC17__NearMiss_SMOTE__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC17__NearMiss_SMOTE__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC17__NearMiss_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC17__NearMiss_SMOTE__v1__train__1.csv
+pd_CIC17__NearMiss_SMOTE__v1__val__1.csv
+pd_CIC17__NearMiss_SMOTE__v1__train__2.csv
+pd_CIC17__NearMiss_SMOTE__v1__val__2.csv
+pd_CIC17__NearMiss_SMOTE__v1__train__3.csv
+pd_CIC17__NearMiss_SMOTE__v1__val__3.csv
+pd_CIC17__NearMiss_SMOTE__v1__train__4.csv
+pd_CIC17__NearMiss_SMOTE__v1__val__4.csv
+pd_CIC17__NearMiss_SMOTE__v1__train__5.csv
+Pd_CIC17__NearMiss_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -795,6 +888,366 @@
     <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__train.csv BCCC17__RUS_SMOTE__v1__test.csv BCCC17__RUS_SMOTE__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__RUS_SMOTE_ENN__v1__train.csv BCCC17__RUS_SMOTE_ENN__v1__test.csv BCCC17__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train.csv </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test.csv </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test_nuevo.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__1.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__2.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__2.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__3.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__3.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__4.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__4.csv
+pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BCCC17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__5.csv</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
@@ -838,6 +1291,33 @@
     <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__train.csv BCCC17__NearMiss_SMOTE__v1__test.csv BCCC17__NearMiss_SMOTE__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__NearMiss_SMOTE_ENN__v1__train.csv BCCC17__NearMiss_SMOTE_ENN__v1__test.csv BCCC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__NearMiss_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__train.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__test.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">ORIGINAL (BCCC17)</t>
   </si>
   <si>
@@ -881,11 +1361,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -945,6 +1424,12 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Cascadia Code PL"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1075,7 +1560,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1160,6 +1645,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1192,10 +1689,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1220,10 +1713,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1302,6 +1791,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1569,15 +2062,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="67.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="90.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="68.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="61.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="60.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="48.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="81.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="68.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1807,138 +2300,170 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="D14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="D15" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="B16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="20"/>
-    </row>
-    <row r="16" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="D16" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="14" t="s">
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="187.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="19" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="C19" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="D19" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="E19" s="19"/>
+      <c r="F19" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23"/>
+    </row>
+    <row r="21" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="17"/>
-    </row>
-    <row r="20" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="D21" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="17"/>
+    </row>
+    <row r="22" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="20"/>
+      <c r="D22" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1949,7 +2474,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD28"/>
-  <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="35.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="19.6"/>
@@ -1960,579 +2485,579 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="18.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="30.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="31.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="28.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.21"/>
   </cols>
   <sheetData>
-    <row r="1" s="24" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="22" t="s">
+    <row r="1" s="27" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="XFD1" s="2"/>
+    </row>
+    <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="30" t="n">
+        <v>13484658</v>
+      </c>
+      <c r="D2" s="30" t="n">
+        <v>13445443</v>
+      </c>
+      <c r="E2" s="30" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F2" s="30" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G2" s="30" t="n">
+        <v>339865</v>
+      </c>
+      <c r="H2" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD2" s="2"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="30" t="n">
+        <v>686012</v>
+      </c>
+      <c r="D3" s="30" t="n">
+        <v>668461</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F3" s="30" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G3" s="30" t="n">
+        <v>359280</v>
+      </c>
+      <c r="H3" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="30" t="n">
+        <v>9840</v>
+      </c>
+      <c r="K3" s="30" t="n">
+        <v>9993</v>
+      </c>
+      <c r="XFD3" s="2"/>
+    </row>
+    <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>576191</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>576175</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G4" s="30" t="n">
+        <v>359369</v>
+      </c>
+      <c r="H4" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="30" t="n">
+        <v>9974</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>9968</v>
+      </c>
+      <c r="XFD4" s="2"/>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>461912</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>434873</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>434873</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>347898</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>346118</v>
+      </c>
+      <c r="H5" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="30" t="n">
+        <v>9855</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>9914</v>
+      </c>
+      <c r="XFD5" s="2"/>
+    </row>
+    <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>286191</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>282310</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>282310</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>225848</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>225602</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>9971</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD6" s="2"/>
+    </row>
+    <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>161934</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>161897</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>161897</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>129517</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>108526</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <v>8820</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>9998</v>
+      </c>
+      <c r="XFD7" s="2"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>187589</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>117322</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>117322</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>93857</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>93112</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <v>9896</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>9967</v>
+      </c>
+      <c r="XFD8" s="2"/>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>41508</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>41455</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>41455</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>33164</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>31187</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="30" t="n">
+        <v>9533</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>9974</v>
+      </c>
+      <c r="XFD9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>193360</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>39352</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>39352</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>31482</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>31432</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>9986</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>139890</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>19462</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>19462</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>15570</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>15570</v>
+      </c>
+      <c r="H11" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>10990</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>10285</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>10285</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>8228</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>7975</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>9838</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>9939</v>
+      </c>
+      <c r="XFD12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>1384</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>1378</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>611</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>611</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>611</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>489</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>211</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>9624</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>9593</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>230</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>230</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>230</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>184</v>
+      </c>
+      <c r="G15" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="D1" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="XFD1" s="2"/>
-    </row>
-    <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
+      <c r="H15" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>9673</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>9655</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>87</v>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>87</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>87</v>
+      </c>
+      <c r="F16" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="B2" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="27" t="n">
-        <v>13484658</v>
-      </c>
-      <c r="D2" s="27" t="n">
-        <v>13445443</v>
-      </c>
-      <c r="E2" s="27" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>360000</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>339865</v>
-      </c>
-      <c r="H2" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD2" s="2"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27" t="n">
-        <v>686012</v>
-      </c>
-      <c r="D3" s="27" t="n">
-        <v>668461</v>
-      </c>
-      <c r="E3" s="27" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>360000</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>359280</v>
-      </c>
-      <c r="H3" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="29" t="n">
-        <v>9840</v>
-      </c>
-      <c r="K3" s="29" t="n">
-        <v>9993</v>
-      </c>
-      <c r="XFD3" s="2"/>
-    </row>
-    <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="27" t="n">
-        <v>576191</v>
-      </c>
-      <c r="D4" s="27" t="n">
-        <v>576175</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>360000</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>359369</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="29" t="n">
-        <v>9974</v>
-      </c>
-      <c r="K4" s="29" t="n">
-        <v>9968</v>
-      </c>
-      <c r="XFD4" s="2"/>
-    </row>
-    <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>461912</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>434873</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>434873</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>347898</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>346118</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>9855</v>
-      </c>
-      <c r="K5" s="29" t="n">
-        <v>9914</v>
-      </c>
-      <c r="XFD5" s="2"/>
-    </row>
-    <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>286191</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>282310</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>282310</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>225848</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>225602</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="29" t="n">
-        <v>9971</v>
-      </c>
-      <c r="K6" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD6" s="2"/>
-    </row>
-    <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>161934</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>161897</v>
-      </c>
-      <c r="E7" s="31" t="n">
-        <v>161897</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>129517</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>108526</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="29" t="n">
-        <v>8820</v>
-      </c>
-      <c r="K7" s="29" t="n">
-        <v>9998</v>
-      </c>
-      <c r="XFD7" s="2"/>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>187589</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>117322</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>117322</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>93857</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>93112</v>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="29" t="n">
-        <v>9896</v>
-      </c>
-      <c r="K8" s="29" t="n">
-        <v>9967</v>
-      </c>
-      <c r="XFD8" s="2"/>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>41508</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>41455</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>41455</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>33164</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>31187</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>9533</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <v>9974</v>
-      </c>
-      <c r="XFD9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="27" t="n">
-        <v>193360</v>
-      </c>
-      <c r="D10" s="27" t="n">
-        <v>39352</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>39352</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>31482</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>31432</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>9986</v>
-      </c>
-      <c r="K10" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="27" t="n">
-        <v>139890</v>
-      </c>
-      <c r="D11" s="27" t="n">
-        <v>19462</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>19462</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>15570</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>15570</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K11" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="27" t="n">
-        <v>10990</v>
-      </c>
-      <c r="D12" s="27" t="n">
-        <v>10285</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>10285</v>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>8228</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>7975</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="29" t="n">
-        <v>9838</v>
-      </c>
-      <c r="K12" s="29" t="n">
-        <v>9939</v>
-      </c>
-      <c r="XFD12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>1730</v>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>1730</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>1384</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>1378</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="27" t="n">
-        <v>611</v>
-      </c>
-      <c r="D14" s="27" t="n">
-        <v>611</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>611</v>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>489</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>211</v>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>9624</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>9593</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="27" t="n">
-        <v>230</v>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>230</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>230</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>184</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>66</v>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>9673</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>9655</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="34" t="n">
-        <v>87</v>
-      </c>
-      <c r="D16" s="34" t="n">
-        <v>87</v>
-      </c>
-      <c r="E16" s="34" t="n">
-        <v>87</v>
-      </c>
-      <c r="F16" s="27" t="n">
+      <c r="G16" s="37" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="35" t="n">
-        <v>70</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="29" t="n">
+      <c r="H16" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="30" t="n">
         <v>9987</v>
       </c>
-      <c r="K16" s="29" t="n">
+      <c r="K16" s="30" t="n">
         <v>9986</v>
       </c>
     </row>
@@ -2565,32 +3090,32 @@
         <f aca="false">SUM(I2:I16)</f>
         <v>150000</v>
       </c>
-      <c r="J17" s="36" t="n">
+      <c r="J17" s="3" t="n">
         <f aca="false">SUM(J2:J16)</f>
         <v>146997</v>
       </c>
-      <c r="K17" s="36" t="n">
+      <c r="K17" s="3" t="n">
         <f aca="false">SUM(K2:K16)</f>
         <v>148987</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="37"/>
-      <c r="F18" s="26"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="29"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="27"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="30"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="37"/>
-      <c r="F19" s="26"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>84</v>
@@ -2607,23 +3132,23 @@
       <c r="G20" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="30" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="27" t="n">
+      <c r="I20" s="30" t="n">
         <v>56</v>
       </c>
       <c r="XFD20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="3"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3"/>
@@ -2648,8 +3173,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2659,25 +3184,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="38" width="78.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="39" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="38" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="39" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="40" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="39" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="39" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="44" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -2686,119 +3211,119 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="F1" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="10" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
+        <v>96</v>
+      </c>
+      <c r="F3" s="47"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
+        <v>100</v>
+      </c>
+      <c r="F6" s="47"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
     </row>
     <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="44"/>
+        <v>102</v>
+      </c>
+      <c r="F7" s="45"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
@@ -2807,326 +3332,360 @@
         <v>27</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
+        <v>104</v>
+      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
+        <v>106</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
     </row>
     <row r="10" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
+        <v>108</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
+        <v>110</v>
+      </c>
+      <c r="F11" s="45"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-    </row>
-    <row r="13" s="47" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+    </row>
+    <row r="13" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+    </row>
+    <row r="14" s="48" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="20"/>
-    </row>
-    <row r="15" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-    </row>
-    <row r="16" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+    </row>
+    <row r="17" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-    </row>
-    <row r="17" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="D17" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+    </row>
+    <row r="18" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-    </row>
-    <row r="18" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="D18" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+    </row>
+    <row r="19" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="22"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+    </row>
+    <row r="20" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-    </row>
-    <row r="19" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="D20" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+    </row>
+    <row r="21" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-    </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
+      <c r="D21" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3137,7 +3696,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD35"/>
-  <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="45.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.01"/>
@@ -3150,531 +3709,531 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="51" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F1" s="48" t="s">
+    <row r="1" s="52" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" s="50"/>
+      <c r="H1" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="51"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="53" t="n">
+      <c r="A2" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="53" t="n">
+      <c r="C2" s="54" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="54" t="n">
+      <c r="D2" s="55" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="27" t="n">
+      <c r="E2" s="30" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="33" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="29" t="n">
+      <c r="G2" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="30" t="n">
         <v>10000</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="53" t="n">
+      <c r="A3" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="53" t="n">
+      <c r="C3" s="54" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="54" t="n">
+      <c r="D3" s="55" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="27" t="n">
+      <c r="E3" s="30" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="33" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="29" t="n">
+      <c r="G3" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="30" t="n">
         <v>9656</v>
       </c>
-      <c r="J3" s="29" t="n">
+      <c r="J3" s="30" t="n">
         <v>9968</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="53" t="n">
+      <c r="A4" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="53" t="n">
+      <c r="C4" s="54" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="54" t="n">
+      <c r="D4" s="55" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="30" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="33" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="29" t="n">
+      <c r="G4" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="30" t="n">
         <v>9765</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="30" t="n">
         <v>9995</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="52" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="53" t="n">
+      <c r="A5" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="53" t="n">
+      <c r="C5" s="54" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="54" t="n">
+      <c r="D5" s="55" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="30" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="33" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="29" t="n">
+      <c r="G5" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="30" t="n">
         <v>9712</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="30" t="n">
         <v>9960</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="53" t="n">
+      <c r="A6" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="53" t="n">
+      <c r="C6" s="54" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="55" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="30" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="33" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="29" t="n">
+      <c r="G6" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="30" t="n">
         <v>9913</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="30" t="n">
         <v>9958</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="53" t="n">
+      <c r="A7" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="54" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="55" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="30" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="G7" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="30" t="n">
         <v>9908</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="30" t="n">
         <v>9923</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="52" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="53" t="n">
+      <c r="A8" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="53" t="n">
+      <c r="C8" s="54" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="54" t="n">
+      <c r="D8" s="55" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="30" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="33" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="29" t="n">
+      <c r="G8" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="30" t="n">
         <v>9637</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="30" t="n">
         <v>9785</v>
       </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="53" t="n">
+      <c r="A9" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="54" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="53" t="n">
+      <c r="C9" s="54" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="55" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="33" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="29" t="n">
+      <c r="G9" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="30" t="n">
         <v>9814</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="30" t="n">
         <v>9872</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="53" t="n">
+      <c r="A10" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="53" t="n">
+      <c r="C10" s="54" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="54" t="n">
+      <c r="D10" s="55" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="F10" s="33" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="29" t="n">
+      <c r="G10" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="30" t="n">
         <v>9622</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="30" t="n">
         <v>9637</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="53" t="n">
+      <c r="A11" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="53" t="n">
+      <c r="C11" s="54" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="55" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="30" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="31" t="n">
+      <c r="F11" s="33" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="29" t="n">
+      <c r="G11" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="30" t="n">
         <v>9832</v>
       </c>
-      <c r="J11" s="29" t="n">
+      <c r="J11" s="30" t="n">
         <v>9979</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="53" t="n">
+      <c r="A12" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="53" t="n">
+      <c r="C12" s="54" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="55" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="30" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="F12" s="33" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="29" t="n">
+      <c r="G12" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="30" t="n">
         <v>5782</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="30" t="n">
         <v>5793</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="53" t="n">
+      <c r="A13" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="54" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="53" t="n">
+      <c r="C13" s="54" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="55" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="30" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="31" t="n">
+      <c r="F13" s="33" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="29" t="n">
+      <c r="G13" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="30" t="n">
         <v>5862</v>
       </c>
-      <c r="J13" s="29" t="n">
+      <c r="J13" s="30" t="n">
         <v>5871</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="53" t="n">
+      <c r="A14" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="53" t="n">
+      <c r="C14" s="54" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="55" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="29" t="n">
+      <c r="G14" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="30" t="n">
         <v>9904</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="30" t="n">
         <v>9934</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="53" t="n">
+      <c r="A15" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="53" t="n">
+      <c r="C15" s="54" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="54" t="n">
+      <c r="D15" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="29" t="n">
+      <c r="G15" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="30" t="n">
         <v>9725</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="30" t="n">
         <v>9727</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="56" t="n">
+      <c r="A16" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="57" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="56" t="n">
+      <c r="C16" s="57" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="56" t="n">
+      <c r="D16" s="57" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="29" t="n">
+      <c r="G16" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="30" t="n">
         <v>10000</v>
       </c>
       <c r="L16" s="2"/>
@@ -3715,23 +4274,23 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="37"/>
-      <c r="F18" s="26"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="29"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="37"/>
-      <c r="F19" s="26"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="29"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="50" t="s">
-        <v>85</v>
+      <c r="A20" s="51" t="s">
+        <v>90</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="30" t="n">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -3749,62 +4308,62 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27"/>
+      <c r="B21" s="30"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27"/>
+      <c r="B22" s="30"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27"/>
+      <c r="B23" s="30"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="27"/>
+      <c r="B24" s="30"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="27"/>
+      <c r="B25" s="30"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="27"/>
+      <c r="B26" s="30"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="27"/>
+      <c r="B27" s="30"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="27"/>
+      <c r="B28" s="30"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="27"/>
+      <c r="B29" s="30"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="27"/>
+      <c r="B30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="27"/>
+      <c r="B31" s="30"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="27"/>
+      <c r="B32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="27"/>
+      <c r="B33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="27"/>
+      <c r="B34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="27"/>
+      <c r="B35" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3814,15 +4373,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="90.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="77.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="65.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="50.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="50.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3842,134 +4401,134 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
+        <v>150</v>
+      </c>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
     </row>
     <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -3980,290 +4539,368 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
     </row>
     <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
     </row>
     <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F11" s="16"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-    </row>
-    <row r="13" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C13" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+    </row>
+    <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F13" s="20"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+    </row>
+    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+    </row>
+    <row r="15" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-    </row>
-    <row r="14" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="D15" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+    </row>
+    <row r="16" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-    </row>
-    <row r="15" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="D16" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+    </row>
+    <row r="17" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-    </row>
-    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-    </row>
-    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-    </row>
-    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
+      <c r="D17" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+    </row>
+    <row r="18" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" s="20"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+    </row>
+    <row r="19" customFormat="false" ht="196" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F19" s="23"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -4274,7 +4911,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD34"/>
-  <sheetFormatPr defaultColWidth="10.17578125" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="28.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="17.66"/>
@@ -4287,408 +4924,408 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="57" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="22" t="s">
+    <row r="1" s="59" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="24"/>
+      <c r="H1" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="27"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="26" t="n">
+      <c r="A2" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="30" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="31" t="n">
+      <c r="D2" s="33" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="27" t="n">
+      <c r="E2" s="30" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="33" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="58" t="n">
+      <c r="G2" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="26" t="n">
+      <c r="A3" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C3" s="30" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="33" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="27" t="n">
+      <c r="E3" s="30" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="33" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="58" t="n">
+      <c r="G3" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="26" t="n">
+      <c r="A4" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="30" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="33" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="30" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="33" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="58" t="n">
+      <c r="G4" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="26" t="n">
+      <c r="A5" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="30" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="33" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="30" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="33" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="58" t="n">
+      <c r="G5" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="26" t="n">
+      <c r="A6" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="33" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="30" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="33" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="58" t="n">
+      <c r="G6" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="26" t="n">
+      <c r="A7" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="30" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="33" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="30" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="58" t="n">
+      <c r="G7" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="26" t="n">
+      <c r="A8" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="33" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="30" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="33" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="58" t="n">
+      <c r="G8" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" s="26" t="n">
+      <c r="A9" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="30" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="33" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="33" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="58" t="n">
+      <c r="G9" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="26" t="n">
+      <c r="A10" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="30" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="33" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="F10" s="33" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="58" t="n">
+      <c r="G10" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="26" t="n">
+      <c r="A11" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="30" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="33" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="30" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="31" t="n">
+      <c r="F11" s="33" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="58" t="n">
+      <c r="G11" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="26" t="n">
+      <c r="A12" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="30" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="33" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="30" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="F12" s="33" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="58" t="n">
+      <c r="G12" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="26" t="n">
+      <c r="A13" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="30" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="33" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="30" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="31" t="n">
+      <c r="F13" s="33" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="58" t="n">
+      <c r="G13" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="26" t="n">
+      <c r="A14" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="31" t="n">
+      <c r="F14" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="58" t="n">
+      <c r="G14" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="J14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="59" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="33" t="n">
+      <c r="A15" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C15" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="60" t="n">
+      <c r="G15" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="62" t="n">
         <v>10000</v>
       </c>
       <c r="J15" s="2"/>
@@ -4724,24 +5361,24 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="37"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="29" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -4753,15 +5390,15 @@
       <c r="I19" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="27"/>
+      <c r="J34" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="218">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -280,6 +280,48 @@
 Pd_CIC18__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__training_v1__3_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__training_v1__4_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__train__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__2.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__2.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__3.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__3.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__4.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__4.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC18__RUS_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC18__RUS_SMOTE_ENN__v1__train__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__2.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__2.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__3.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__3.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__4.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__4.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE</t>
   </si>
   <si>
@@ -391,6 +433,48 @@
 Pd_CIC18__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__training_v1__2_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__training_v1__3_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__training_v1__4_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE_ENN__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC18__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_CIC18__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLASE ORIGINAL</t>
   </si>
   <si>
@@ -888,6 +972,26 @@
     <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__1_5.ipynb
+pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__2_5.ipynb
+pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__3_5.ipynb
+pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__4_5.ipynb
+pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_BCCC17__RUS_SMOTE__v1__train__1.csv
+pd_BCCC17__RUS_SMOTE__v1__val__1.csv
+pd_BCCC17__RUS_SMOTE__v1__train__2.csv
+pd_BCCC17__RUS_SMOTE__v1__val__2.csv
+pd_BCCC17__RUS_SMOTE__v1__train__3.csv
+pd_BCCC17__RUS_SMOTE__v1__val__3.csv
+pd_BCCC17__RUS_SMOTE__v1__train__4.csv
+pd_BCCC17__RUS_SMOTE__v1__val__4.csv
+pd_BCCC17__RUS_SMOTE__v1__train__5.csv
+Pd_BCCC17__RUS_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -897,355 +1001,22 @@
     <t xml:space="preserve">BCCC17__RUS_SMOTE_ENN__v1__train.csv BCCC17__RUS_SMOTE_ENN__v1__test.csv BCCC17__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__transformar_v1.ipynb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train.csv </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test.csv </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__test_nuevo.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__1.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__1.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__2.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__2.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__3.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__3.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__4.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__4.csv
-pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__train__5.csv
-Pd_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BCCC17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">__RUS_SMOTE_ENN__v1__val__5.csv</t>
-    </r>
+    <t xml:space="preserve">BCCC17__RUS_SMOTE_ENN__v1__transformar_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__train.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__test.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__test_nuevo.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__1.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__2.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__2.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__3.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__3.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__4.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
@@ -1291,6 +1062,26 @@
     <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__outputs</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__1_5.ipynb
+pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__2_5.ipynb
+pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__3_5.ipynb
+pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__4_5.ipynb
+pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__1.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__2.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__2.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__3.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__3.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__4.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__4.csv
+pd_BCCC17__NearMiss_SMOTE__v1__train__5.csv
+Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -1364,7 +1155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1425,12 +1216,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Cascadia Code PL"/>
-      <family val="0"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1459,23 +1244,86 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF77BC65"/>
         <bgColor rgb="FF81D41A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="hair"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="hair"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -1515,13 +1363,6 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
       <right style="thin"/>
       <top/>
       <bottom/>
@@ -1560,7 +1401,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="87">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1629,10 +1470,218 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1645,123 +1694,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1773,7 +1710,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1785,31 +1722,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2062,7 +1999,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.05"/>
@@ -2246,25 +2183,25 @@
       <c r="F10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="8"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="14" t="s">
@@ -2279,10 +2216,10 @@
       <c r="E12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="16"/>
+      <c r="F12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
@@ -2295,175 +2232,275 @@
         <v>41</v>
       </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="23" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B16" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C16" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D16" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E16" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="F16" s="31"/>
+    </row>
+    <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D17" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="F17" s="33"/>
+    </row>
+    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="E18" s="35"/>
+      <c r="F18" s="36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39"/>
+    </row>
+    <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="40"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="E21" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="19" t="s">
+      <c r="D22" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="22" t="s">
+      <c r="B23" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="23"/>
-    </row>
-    <row r="21" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="D24" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+    </row>
+    <row r="25" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+    </row>
+    <row r="26" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="17"/>
-    </row>
-    <row r="22" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="D26" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="D27" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="33"/>
+    </row>
+    <row r="28" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="9"/>
+      <c r="B28" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="35"/>
+      <c r="F28" s="36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="163.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="39"/>
+    </row>
+    <row r="30" customFormat="false" ht="163.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2489,575 +2526,575 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.21"/>
   </cols>
   <sheetData>
-    <row r="1" s="27" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="24" t="s">
+    <row r="1" s="45" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="XFD1" s="2"/>
+    </row>
+    <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48" t="n">
+        <v>13484658</v>
+      </c>
+      <c r="D2" s="48" t="n">
+        <v>13445443</v>
+      </c>
+      <c r="E2" s="48" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F2" s="48" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>339865</v>
+      </c>
+      <c r="H2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD2" s="2"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48" t="n">
+        <v>686012</v>
+      </c>
+      <c r="D3" s="48" t="n">
+        <v>668461</v>
+      </c>
+      <c r="E3" s="48" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F3" s="48" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>359280</v>
+      </c>
+      <c r="H3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="48" t="n">
+        <v>9840</v>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>9993</v>
+      </c>
+      <c r="XFD3" s="2"/>
+    </row>
+    <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="48" t="n">
+        <v>576191</v>
+      </c>
+      <c r="D4" s="48" t="n">
+        <v>576175</v>
+      </c>
+      <c r="E4" s="48" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F4" s="48" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>359369</v>
+      </c>
+      <c r="H4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="48" t="n">
+        <v>9974</v>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>9968</v>
+      </c>
+      <c r="XFD4" s="2"/>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="48" t="n">
+        <v>461912</v>
+      </c>
+      <c r="D5" s="48" t="n">
+        <v>434873</v>
+      </c>
+      <c r="E5" s="51" t="n">
+        <v>434873</v>
+      </c>
+      <c r="F5" s="48" t="n">
+        <v>347898</v>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>346118</v>
+      </c>
+      <c r="H5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="48" t="n">
+        <v>9855</v>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>9914</v>
+      </c>
+      <c r="XFD5" s="2"/>
+    </row>
+    <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="48" t="n">
+        <v>286191</v>
+      </c>
+      <c r="D6" s="48" t="n">
+        <v>282310</v>
+      </c>
+      <c r="E6" s="51" t="n">
+        <v>282310</v>
+      </c>
+      <c r="F6" s="48" t="n">
+        <v>225848</v>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>225602</v>
+      </c>
+      <c r="H6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="48" t="n">
+        <v>9971</v>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD6" s="2"/>
+    </row>
+    <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="48" t="n">
+        <v>161934</v>
+      </c>
+      <c r="D7" s="48" t="n">
+        <v>161897</v>
+      </c>
+      <c r="E7" s="51" t="n">
+        <v>161897</v>
+      </c>
+      <c r="F7" s="48" t="n">
+        <v>129517</v>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>108526</v>
+      </c>
+      <c r="H7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="48" t="n">
+        <v>8820</v>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>9998</v>
+      </c>
+      <c r="XFD7" s="2"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="48" t="n">
+        <v>187589</v>
+      </c>
+      <c r="D8" s="48" t="n">
+        <v>117322</v>
+      </c>
+      <c r="E8" s="51" t="n">
+        <v>117322</v>
+      </c>
+      <c r="F8" s="48" t="n">
+        <v>93857</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>93112</v>
+      </c>
+      <c r="H8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="48" t="n">
+        <v>9896</v>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>9967</v>
+      </c>
+      <c r="XFD8" s="2"/>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="48" t="n">
+        <v>41508</v>
+      </c>
+      <c r="D9" s="48" t="n">
+        <v>41455</v>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>41455</v>
+      </c>
+      <c r="F9" s="48" t="n">
+        <v>33164</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>31187</v>
+      </c>
+      <c r="H9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="48" t="n">
+        <v>9533</v>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>9974</v>
+      </c>
+      <c r="XFD9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="48" t="n">
+        <v>193360</v>
+      </c>
+      <c r="D10" s="48" t="n">
+        <v>39352</v>
+      </c>
+      <c r="E10" s="51" t="n">
+        <v>39352</v>
+      </c>
+      <c r="F10" s="48" t="n">
+        <v>31482</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>31432</v>
+      </c>
+      <c r="H10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <v>9986</v>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="48" t="n">
+        <v>139890</v>
+      </c>
+      <c r="D11" s="48" t="n">
+        <v>19462</v>
+      </c>
+      <c r="E11" s="51" t="n">
+        <v>19462</v>
+      </c>
+      <c r="F11" s="48" t="n">
+        <v>15570</v>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>15570</v>
+      </c>
+      <c r="H11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="XFD11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="48" t="n">
+        <v>10990</v>
+      </c>
+      <c r="D12" s="48" t="n">
+        <v>10285</v>
+      </c>
+      <c r="E12" s="51" t="n">
+        <v>10285</v>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>8228</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>7975</v>
+      </c>
+      <c r="H12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="48" t="n">
+        <v>9838</v>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>9939</v>
+      </c>
+      <c r="XFD12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="48" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D13" s="48" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E13" s="51" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F13" s="48" t="n">
+        <v>1384</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>1378</v>
+      </c>
+      <c r="H13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="48" t="n">
+        <v>611</v>
+      </c>
+      <c r="D14" s="48" t="n">
+        <v>611</v>
+      </c>
+      <c r="E14" s="51" t="n">
+        <v>611</v>
+      </c>
+      <c r="F14" s="48" t="n">
+        <v>489</v>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>211</v>
+      </c>
+      <c r="H14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="48" t="n">
+        <v>9624</v>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>9593</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="48" t="n">
+        <v>230</v>
+      </c>
+      <c r="D15" s="48" t="n">
+        <v>230</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <v>230</v>
+      </c>
+      <c r="F15" s="48" t="n">
+        <v>184</v>
+      </c>
+      <c r="G15" s="48" t="n">
+        <v>66</v>
+      </c>
+      <c r="H15" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="48" t="n">
+        <v>9673</v>
+      </c>
+      <c r="K15" s="48" t="n">
+        <v>9655</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="53" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="54" t="n">
+        <v>87</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>87</v>
+      </c>
+      <c r="E16" s="54" t="n">
+        <v>87</v>
+      </c>
+      <c r="F16" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="C1" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="XFD1" s="2"/>
-    </row>
-    <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="30" t="n">
-        <v>13484658</v>
-      </c>
-      <c r="D2" s="30" t="n">
-        <v>13445443</v>
-      </c>
-      <c r="E2" s="30" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F2" s="30" t="n">
-        <v>360000</v>
-      </c>
-      <c r="G2" s="30" t="n">
-        <v>339865</v>
-      </c>
-      <c r="H2" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD2" s="2"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="30" t="n">
-        <v>686012</v>
-      </c>
-      <c r="D3" s="30" t="n">
-        <v>668461</v>
-      </c>
-      <c r="E3" s="30" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F3" s="30" t="n">
-        <v>360000</v>
-      </c>
-      <c r="G3" s="30" t="n">
-        <v>359280</v>
-      </c>
-      <c r="H3" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="30" t="n">
-        <v>9840</v>
-      </c>
-      <c r="K3" s="30" t="n">
-        <v>9993</v>
-      </c>
-      <c r="XFD3" s="2"/>
-    </row>
-    <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="30" t="n">
-        <v>576191</v>
-      </c>
-      <c r="D4" s="30" t="n">
-        <v>576175</v>
-      </c>
-      <c r="E4" s="30" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F4" s="30" t="n">
-        <v>360000</v>
-      </c>
-      <c r="G4" s="30" t="n">
-        <v>359369</v>
-      </c>
-      <c r="H4" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="30" t="n">
-        <v>9974</v>
-      </c>
-      <c r="K4" s="30" t="n">
-        <v>9968</v>
-      </c>
-      <c r="XFD4" s="2"/>
-    </row>
-    <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="30" t="n">
-        <v>461912</v>
-      </c>
-      <c r="D5" s="30" t="n">
-        <v>434873</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>434873</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <v>347898</v>
-      </c>
-      <c r="G5" s="30" t="n">
-        <v>346118</v>
-      </c>
-      <c r="H5" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="30" t="n">
-        <v>9855</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>9914</v>
-      </c>
-      <c r="XFD5" s="2"/>
-    </row>
-    <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="30" t="n">
-        <v>286191</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>282310</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>282310</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>225848</v>
-      </c>
-      <c r="G6" s="30" t="n">
-        <v>225602</v>
-      </c>
-      <c r="H6" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="30" t="n">
-        <v>9971</v>
-      </c>
-      <c r="K6" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD6" s="2"/>
-    </row>
-    <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>161934</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>161897</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>161897</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>129517</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <v>108526</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="30" t="n">
-        <v>8820</v>
-      </c>
-      <c r="K7" s="30" t="n">
-        <v>9998</v>
-      </c>
-      <c r="XFD7" s="2"/>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>187589</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>117322</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>117322</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>93857</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <v>93112</v>
-      </c>
-      <c r="H8" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="30" t="n">
-        <v>9896</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>9967</v>
-      </c>
-      <c r="XFD8" s="2"/>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>41508</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>41455</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>41455</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>33164</v>
-      </c>
-      <c r="G9" s="30" t="n">
-        <v>31187</v>
-      </c>
-      <c r="H9" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="30" t="n">
-        <v>9533</v>
-      </c>
-      <c r="K9" s="30" t="n">
-        <v>9974</v>
-      </c>
-      <c r="XFD9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>193360</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>39352</v>
-      </c>
-      <c r="E10" s="33" t="n">
-        <v>39352</v>
-      </c>
-      <c r="F10" s="30" t="n">
-        <v>31482</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <v>31432</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="30" t="n">
-        <v>9986</v>
-      </c>
-      <c r="K10" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>139890</v>
-      </c>
-      <c r="D11" s="30" t="n">
-        <v>19462</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>19462</v>
-      </c>
-      <c r="F11" s="30" t="n">
-        <v>15570</v>
-      </c>
-      <c r="G11" s="30" t="n">
-        <v>15570</v>
-      </c>
-      <c r="H11" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K11" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="XFD11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>10990</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>10285</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>10285</v>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>8228</v>
-      </c>
-      <c r="G12" s="30" t="n">
-        <v>7975</v>
-      </c>
-      <c r="H12" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="30" t="n">
-        <v>9838</v>
-      </c>
-      <c r="K12" s="30" t="n">
-        <v>9939</v>
-      </c>
-      <c r="XFD12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>1730</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>1730</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F13" s="30" t="n">
-        <v>1384</v>
-      </c>
-      <c r="G13" s="30" t="n">
-        <v>1378</v>
-      </c>
-      <c r="H13" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="30" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>611</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>611</v>
-      </c>
-      <c r="E14" s="33" t="n">
-        <v>611</v>
-      </c>
-      <c r="F14" s="30" t="n">
-        <v>489</v>
-      </c>
-      <c r="G14" s="30" t="n">
-        <v>211</v>
-      </c>
-      <c r="H14" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>9624</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>9593</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>230</v>
-      </c>
-      <c r="D15" s="30" t="n">
-        <v>230</v>
-      </c>
-      <c r="E15" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="F15" s="30" t="n">
-        <v>184</v>
-      </c>
-      <c r="G15" s="30" t="n">
-        <v>66</v>
-      </c>
-      <c r="H15" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="30" t="n">
-        <v>9673</v>
-      </c>
-      <c r="K15" s="30" t="n">
-        <v>9655</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>87</v>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>87</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>87</v>
-      </c>
-      <c r="F16" s="30" t="n">
+      <c r="G16" s="55" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="37" t="n">
-        <v>70</v>
-      </c>
-      <c r="H16" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="30" t="n">
+      <c r="H16" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="48" t="n">
         <v>9987</v>
       </c>
-      <c r="K16" s="30" t="n">
+      <c r="K16" s="48" t="n">
         <v>9986</v>
       </c>
     </row>
@@ -3100,22 +3137,22 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="38"/>
-      <c r="F18" s="29"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="47"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="30"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="48"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="38"/>
-      <c r="F19" s="29"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="47"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>84</v>
@@ -3132,23 +3169,23 @@
       <c r="G20" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="30" t="n">
+      <c r="H20" s="48" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="30" t="n">
+      <c r="I20" s="48" t="n">
         <v>56</v>
       </c>
       <c r="XFD20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="3"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3"/>
@@ -3173,8 +3210,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3188,21 +3225,21 @@
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="39" width="92.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="40" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="39" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="39" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="57" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="58" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="57" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="57" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="44" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="62" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="59" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -3211,119 +3248,119 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="F1" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+        <v>106</v>
+      </c>
+      <c r="F3" s="65"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="47"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
+        <v>110</v>
+      </c>
+      <c r="F6" s="65"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
     </row>
     <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="45"/>
+        <v>112</v>
+      </c>
+      <c r="F7" s="63"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
@@ -3332,360 +3369,360 @@
         <v>27</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
+        <v>114</v>
+      </c>
+      <c r="F8" s="63"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
     </row>
     <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
+        <v>116</v>
+      </c>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
     </row>
     <row r="10" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
+        <v>118</v>
+      </c>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
+        <v>120</v>
+      </c>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
+      <c r="F12" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
     </row>
     <row r="13" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-    </row>
-    <row r="14" s="48" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+    </row>
+    <row r="14" s="67" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="F14" s="66"/>
     </row>
     <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
+        <v>132</v>
+      </c>
+      <c r="F16" s="63"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
     </row>
     <row r="17" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
+        <v>134</v>
+      </c>
+      <c r="F17" s="63"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
     </row>
     <row r="18" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="A18" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
+      <c r="D18" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="35"/>
+      <c r="F18" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
     </row>
     <row r="19" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="A19" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
+      <c r="D19" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="71"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
     </row>
     <row r="20" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
+        <v>142</v>
+      </c>
+      <c r="F20" s="66"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
     </row>
     <row r="21" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F21" s="9"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="46"/>
-      <c r="H41" s="46"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3709,531 +3746,531 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="52" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="F1" s="49" t="s">
+    <row r="1" s="76" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="50" t="s">
+      <c r="H1" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="K1" s="51"/>
+      <c r="J1" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="75"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="54" t="n">
+      <c r="A2" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="54" t="n">
+      <c r="C2" s="78" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="55" t="n">
+      <c r="D2" s="79" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="30" t="n">
+      <c r="E2" s="48" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="33" t="n">
+      <c r="F2" s="51" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="30" t="n">
+      <c r="G2" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="48" t="n">
         <v>10000</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="54" t="n">
+      <c r="A3" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="54" t="n">
+      <c r="C3" s="78" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="55" t="n">
+      <c r="D3" s="79" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="30" t="n">
+      <c r="E3" s="48" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="33" t="n">
+      <c r="F3" s="51" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="30" t="n">
+      <c r="G3" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="48" t="n">
         <v>9656</v>
       </c>
-      <c r="J3" s="30" t="n">
+      <c r="J3" s="48" t="n">
         <v>9968</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="54" t="n">
+      <c r="A4" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="54" t="n">
+      <c r="C4" s="78" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="55" t="n">
+      <c r="D4" s="79" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="48" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="51" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="30" t="n">
+      <c r="G4" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="48" t="n">
         <v>9765</v>
       </c>
-      <c r="J4" s="30" t="n">
+      <c r="J4" s="48" t="n">
         <v>9995</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="54" t="n">
+      <c r="A5" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="54" t="n">
+      <c r="C5" s="78" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="55" t="n">
+      <c r="D5" s="79" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="48" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="51" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="30" t="n">
+      <c r="G5" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="48" t="n">
         <v>9712</v>
       </c>
-      <c r="J5" s="30" t="n">
+      <c r="J5" s="48" t="n">
         <v>9960</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="54" t="n">
+      <c r="A6" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="78" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="79" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="48" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="51" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="30" t="n">
+      <c r="G6" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="48" t="n">
         <v>9913</v>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J6" s="48" t="n">
         <v>9958</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="54" t="n">
+      <c r="A7" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="78" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="79" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="48" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="51" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="30" t="n">
+      <c r="G7" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="48" t="n">
         <v>9908</v>
       </c>
-      <c r="J7" s="30" t="n">
+      <c r="J7" s="48" t="n">
         <v>9923</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="54" t="n">
+      <c r="A8" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="78" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="79" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="48" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="51" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="30" t="n">
+      <c r="G8" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="48" t="n">
         <v>9637</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="48" t="n">
         <v>9785</v>
       </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="54" t="n">
+      <c r="A9" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="78" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="55" t="n">
+      <c r="D9" s="79" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="48" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="51" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="30" t="n">
+      <c r="G9" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="48" t="n">
         <v>9814</v>
       </c>
-      <c r="J9" s="30" t="n">
+      <c r="J9" s="48" t="n">
         <v>9872</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="54" t="n">
+      <c r="A10" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="54" t="n">
+      <c r="C10" s="78" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="55" t="n">
+      <c r="D10" s="79" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="48" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="51" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="30" t="n">
+      <c r="G10" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="48" t="n">
         <v>9622</v>
       </c>
-      <c r="J10" s="30" t="n">
+      <c r="J10" s="48" t="n">
         <v>9637</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="54" t="n">
+      <c r="A11" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="54" t="n">
+      <c r="C11" s="78" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="55" t="n">
+      <c r="D11" s="79" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="48" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="51" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="30" t="n">
+      <c r="G11" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="48" t="n">
         <v>9832</v>
       </c>
-      <c r="J11" s="30" t="n">
+      <c r="J11" s="48" t="n">
         <v>9979</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="54" t="n">
+      <c r="A12" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="54" t="n">
+      <c r="C12" s="78" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="79" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="48" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="51" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="30" t="n">
+      <c r="G12" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="48" t="n">
         <v>5782</v>
       </c>
-      <c r="J12" s="30" t="n">
+      <c r="J12" s="48" t="n">
         <v>5793</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="54" t="n">
+      <c r="A13" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="78" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="78" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="55" t="n">
+      <c r="D13" s="79" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="48" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="51" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="30" t="n">
+      <c r="G13" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="48" t="n">
         <v>5862</v>
       </c>
-      <c r="J13" s="30" t="n">
+      <c r="J13" s="48" t="n">
         <v>5871</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="54" t="n">
+      <c r="A14" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="78" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="54" t="n">
+      <c r="C14" s="78" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="55" t="n">
+      <c r="D14" s="79" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="48" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="31" t="n">
+      <c r="F14" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="30" t="n">
+      <c r="G14" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="48" t="n">
         <v>9904</v>
       </c>
-      <c r="J14" s="30" t="n">
+      <c r="J14" s="48" t="n">
         <v>9934</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="53" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="54" t="n">
+      <c r="A15" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="78" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="54" t="n">
+      <c r="C15" s="78" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="55" t="n">
+      <c r="D15" s="79" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="48" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="31" t="n">
+      <c r="F15" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="30" t="n">
+      <c r="G15" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="48" t="n">
         <v>9725</v>
       </c>
-      <c r="J15" s="30" t="n">
+      <c r="J15" s="48" t="n">
         <v>9727</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" s="57" t="n">
+      <c r="A16" s="80" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="57" t="n">
+      <c r="C16" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="57" t="n">
+      <c r="D16" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="36" t="n">
+      <c r="E16" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F16" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="30" t="n">
+      <c r="G16" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="48" t="n">
         <v>10000</v>
       </c>
       <c r="L16" s="2"/>
@@ -4274,23 +4311,23 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="38"/>
-      <c r="F18" s="29"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="47"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="38"/>
-      <c r="F19" s="29"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="47"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="s">
-        <v>90</v>
+      <c r="A20" s="75" t="s">
+        <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="48" t="n">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -4308,62 +4345,62 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30"/>
+      <c r="B21" s="48"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30"/>
+      <c r="B22" s="48"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30"/>
+      <c r="B23" s="48"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30"/>
+      <c r="B24" s="48"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30"/>
+      <c r="B25" s="48"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30"/>
+      <c r="B28" s="48"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30"/>
+      <c r="B29" s="48"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="30"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="30"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="30"/>
+      <c r="B32" s="48"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="30"/>
+      <c r="B33" s="48"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="30"/>
+      <c r="B34" s="48"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="30"/>
+      <c r="B35" s="48"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -4373,7 +4410,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.52"/>
@@ -4401,134 +4438,134 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
+        <v>160</v>
+      </c>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -4539,368 +4576,410 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
     </row>
     <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
     </row>
     <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F11" s="16"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+    </row>
+    <row r="13" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+    </row>
+    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" s="66"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+    </row>
+    <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="69"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+    </row>
+    <row r="16" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="E16" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+    </row>
+    <row r="17" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+    </row>
+    <row r="18" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-    </row>
-    <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="D18" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" s="35"/>
+      <c r="F18" s="69" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+    </row>
+    <row r="19" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="71" t="s">
+        <v>199</v>
+      </c>
+      <c r="E19" s="71"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+    </row>
+    <row r="20" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-    </row>
-    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="22" t="s">
+      <c r="D20" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="66"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+    </row>
+    <row r="21" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-    </row>
-    <row r="15" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-    </row>
-    <row r="16" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-    </row>
-    <row r="17" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-    </row>
-    <row r="18" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-    </row>
-    <row r="19" customFormat="false" ht="196" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-    </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
+      <c r="D21" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="69"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -4924,411 +5003,486 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="59" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="25" t="s">
+    <row r="1" s="82" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="27"/>
+      <c r="H1" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>68</v>
+      </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="29" t="n">
+      <c r="A2" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="30" t="n">
+      <c r="C2" s="48" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="33" t="n">
+      <c r="D2" s="51" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="30" t="n">
+      <c r="E2" s="48" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="33" t="n">
+      <c r="F2" s="51" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="2"/>
+      <c r="G2" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="83" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="29" t="n">
+      <c r="A3" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C3" s="48" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="51" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="30" t="n">
+      <c r="E3" s="48" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="33" t="n">
+      <c r="F3" s="51" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="2"/>
+      <c r="G3" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="84" t="n">
+        <v>9549</v>
+      </c>
+      <c r="J3" s="83" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="29" t="n">
+      <c r="A4" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="48" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="51" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="48" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="51" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="2"/>
+      <c r="G4" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="84" t="n">
+        <v>9994</v>
+      </c>
+      <c r="J4" s="84" t="n">
+        <v>9992</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="29" t="n">
+      <c r="A5" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="48" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="51" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="48" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="51" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="2"/>
+      <c r="G5" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="84" t="n">
+        <v>9593</v>
+      </c>
+      <c r="J5" s="84" t="n">
+        <v>9989</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" s="29" t="n">
+      <c r="A6" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="48" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="51" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="48" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="51" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="2"/>
+      <c r="G6" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="84" t="n">
+        <v>9990</v>
+      </c>
+      <c r="J6" s="84" t="n">
+        <v>9999</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="29" t="n">
+      <c r="A7" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="48" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="51" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="48" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="51" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="2"/>
+      <c r="G7" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="84" t="n">
+        <v>9781</v>
+      </c>
+      <c r="J7" s="84" t="n">
+        <v>9944</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="29" t="n">
+      <c r="A8" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="48" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="51" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="48" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="51" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="2"/>
+      <c r="G8" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="84" t="n">
+        <v>9873</v>
+      </c>
+      <c r="J8" s="84" t="n">
+        <v>9880</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="29" t="n">
+      <c r="A9" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="48" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="51" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="48" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="51" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="2"/>
+      <c r="G9" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="84" t="n">
+        <v>9983</v>
+      </c>
+      <c r="J9" s="84" t="n">
+        <v>9992</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="29" t="n">
+      <c r="A10" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="48" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="51" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="48" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="51" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="2"/>
+      <c r="G10" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="84" t="n">
+        <v>9995</v>
+      </c>
+      <c r="J10" s="84" t="n">
+        <v>9995</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="29" t="n">
+      <c r="A11" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="48" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="51" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="48" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="51" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="2"/>
+      <c r="G11" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="84" t="n">
+        <v>9868</v>
+      </c>
+      <c r="J11" s="84" t="n">
+        <v>9881</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="29" t="n">
+      <c r="A12" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="48" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="51" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="48" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="51" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="2"/>
+      <c r="G12" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="84" t="n">
+        <v>9971</v>
+      </c>
+      <c r="J12" s="84" t="n">
+        <v>9971</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="29" t="n">
+      <c r="A13" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="48" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="51" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="48" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="51" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="2"/>
+      <c r="G13" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="84" t="n">
+        <v>9971</v>
+      </c>
+      <c r="J13" s="84" t="n">
+        <v>9971</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="B14" s="29" t="n">
+      <c r="A14" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="48" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="48" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="60" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="2"/>
+      <c r="G14" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="83" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="84" t="n">
+        <v>9998</v>
+      </c>
+      <c r="J14" s="84" t="n">
+        <v>9998</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="35" t="n">
+      <c r="A15" s="85" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="36" t="n">
+      <c r="C15" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="36" t="n">
+      <c r="E15" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="62" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="2"/>
+      <c r="G15" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="86" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="84" t="n">
+        <v>9995</v>
+      </c>
+      <c r="J15" s="84" t="n">
+        <v>9995</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="3" t="n">
@@ -5355,30 +5509,37 @@
         <f aca="false">SUM(H2:H15)</f>
         <v>140000</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="I16" s="3" t="n">
+        <f aca="false">SUM(I2:I15)</f>
+        <v>138561</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <f aca="false">SUM(J2:J15)</f>
+        <v>139607</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="38"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="48" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="47" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="47" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -5390,15 +5551,15 @@
       <c r="I19" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="30"/>
+      <c r="J34" s="48"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -1401,7 +1401,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1735,10 +1735,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2392,7 +2388,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
         <v>57</v>
       </c>
@@ -2408,7 +2404,7 @@
       <c r="E24" s="38"/>
       <c r="F24" s="39"/>
     </row>
-    <row r="25" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="26"/>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -2486,7 +2482,7 @@
       <c r="E29" s="38"/>
       <c r="F29" s="39"/>
     </row>
-    <row r="30" customFormat="false" ht="163.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="127.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26"/>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -5093,7 +5089,7 @@
       <c r="H3" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I3" s="84" t="n">
+      <c r="I3" s="48" t="n">
         <v>9549</v>
       </c>
       <c r="J3" s="83" t="n">
@@ -5125,10 +5121,10 @@
       <c r="H4" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I4" s="84" t="n">
+      <c r="I4" s="48" t="n">
         <v>9994</v>
       </c>
-      <c r="J4" s="84" t="n">
+      <c r="J4" s="48" t="n">
         <v>9992</v>
       </c>
     </row>
@@ -5157,10 +5153,10 @@
       <c r="H5" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="84" t="n">
+      <c r="I5" s="48" t="n">
         <v>9593</v>
       </c>
-      <c r="J5" s="84" t="n">
+      <c r="J5" s="48" t="n">
         <v>9989</v>
       </c>
     </row>
@@ -5189,10 +5185,10 @@
       <c r="H6" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I6" s="84" t="n">
+      <c r="I6" s="48" t="n">
         <v>9990</v>
       </c>
-      <c r="J6" s="84" t="n">
+      <c r="J6" s="48" t="n">
         <v>9999</v>
       </c>
     </row>
@@ -5221,10 +5217,10 @@
       <c r="H7" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I7" s="84" t="n">
+      <c r="I7" s="48" t="n">
         <v>9781</v>
       </c>
-      <c r="J7" s="84" t="n">
+      <c r="J7" s="48" t="n">
         <v>9944</v>
       </c>
     </row>
@@ -5253,10 +5249,10 @@
       <c r="H8" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I8" s="84" t="n">
+      <c r="I8" s="48" t="n">
         <v>9873</v>
       </c>
-      <c r="J8" s="84" t="n">
+      <c r="J8" s="48" t="n">
         <v>9880</v>
       </c>
     </row>
@@ -5285,10 +5281,10 @@
       <c r="H9" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I9" s="84" t="n">
+      <c r="I9" s="48" t="n">
         <v>9983</v>
       </c>
-      <c r="J9" s="84" t="n">
+      <c r="J9" s="48" t="n">
         <v>9992</v>
       </c>
     </row>
@@ -5317,10 +5313,10 @@
       <c r="H10" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I10" s="84" t="n">
+      <c r="I10" s="48" t="n">
         <v>9995</v>
       </c>
-      <c r="J10" s="84" t="n">
+      <c r="J10" s="48" t="n">
         <v>9995</v>
       </c>
     </row>
@@ -5349,10 +5345,10 @@
       <c r="H11" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I11" s="84" t="n">
+      <c r="I11" s="48" t="n">
         <v>9868</v>
       </c>
-      <c r="J11" s="84" t="n">
+      <c r="J11" s="48" t="n">
         <v>9881</v>
       </c>
     </row>
@@ -5381,10 +5377,10 @@
       <c r="H12" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I12" s="84" t="n">
+      <c r="I12" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="J12" s="84" t="n">
+      <c r="J12" s="48" t="n">
         <v>9971</v>
       </c>
     </row>
@@ -5413,10 +5409,10 @@
       <c r="H13" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I13" s="84" t="n">
+      <c r="I13" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="J13" s="84" t="n">
+      <c r="J13" s="48" t="n">
         <v>9971</v>
       </c>
     </row>
@@ -5445,15 +5441,15 @@
       <c r="H14" s="83" t="n">
         <v>10000</v>
       </c>
-      <c r="I14" s="84" t="n">
+      <c r="I14" s="48" t="n">
         <v>9998</v>
       </c>
-      <c r="J14" s="84" t="n">
+      <c r="J14" s="48" t="n">
         <v>9998</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="84" t="s">
         <v>159</v>
       </c>
       <c r="B15" s="53" t="n">
@@ -5474,13 +5470,13 @@
       <c r="G15" s="54" t="n">
         <v>10000</v>
       </c>
-      <c r="H15" s="86" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="84" t="n">
+      <c r="H15" s="85" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="48" t="n">
         <v>9995</v>
       </c>
-      <c r="J15" s="84" t="n">
+      <c r="J15" s="48" t="n">
         <v>9995</v>
       </c>
     </row>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="223">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -710,6 +710,43 @@
 Pd_CIC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__training_v1__3_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__training_v1__4_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__train__1.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__2.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__3.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__4.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC17__RUS_SMOTE_ENN__v1__train__1.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__2.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__2.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__3.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__3.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__4.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__4.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
@@ -1155,7 +1192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1213,6 +1250,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFC9211E"/>
+      <name val="Cascadia Code PL"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFC9211E"/>
+      <name val="Cascadia Code PL"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -1401,7 +1453,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="99">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1666,23 +1718,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1691,7 +1743,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1728,6 +1792,46 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1809,7 +1913,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -2404,13 +2508,15 @@
       <c r="E24" s="38"/>
       <c r="F24" s="39"/>
     </row>
-    <row r="25" customFormat="false" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" s="2" customFormat="true" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="26"/>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
       <c r="F25" s="28"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
     </row>
     <row r="26" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
@@ -2430,7 +2536,7 @@
       </c>
       <c r="F26" s="31"/>
     </row>
-    <row r="27" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
         <v>68</v>
       </c>
@@ -2447,6 +2553,8 @@
         <v>73</v>
       </c>
       <c r="F27" s="33"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="34" t="s">
@@ -2466,7 +2574,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="163.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="37" t="s">
         <v>68</v>
       </c>
@@ -3217,7 +3325,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
@@ -3401,27 +3509,27 @@
       <c r="H9" s="64"/>
     </row>
     <row r="10" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="F10" s="63"/>
+      <c r="F10" s="67"/>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -3436,12 +3544,12 @@
       <c r="E11" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="63"/>
+      <c r="F11" s="68"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -3454,14 +3562,14 @@
         <v>122</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="23" t="s">
         <v>123</v>
       </c>
       <c r="G12" s="64"/>
       <c r="H12" s="64"/>
     </row>
     <row r="13" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
@@ -3474,193 +3582,253 @@
         <v>125</v>
       </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="66"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="64"/>
       <c r="H13" s="64"/>
     </row>
-    <row r="14" s="67" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+    <row r="14" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+    </row>
+    <row r="15" s="69" customFormat="true" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B15" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="F14" s="66"/>
-    </row>
-    <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="F15" s="31"/>
+    </row>
+    <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B16" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="F16" s="33"/>
+    </row>
+    <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="35"/>
+      <c r="F17" s="36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="71"/>
+      <c r="F18" s="39"/>
+    </row>
+    <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+    </row>
+    <row r="20" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="B20" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D20" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-    </row>
-    <row r="17" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="F17" s="63"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-    </row>
-    <row r="18" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="69" t="s">
+      <c r="E20" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-    </row>
-    <row r="19" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="71" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="71" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-    </row>
-    <row r="20" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" s="66"/>
+      <c r="F20" s="67"/>
       <c r="G20" s="64"/>
       <c r="H20" s="64"/>
     </row>
-    <row r="21" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="11" t="s">
+    <row r="21" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" s="9"/>
+      <c r="D21" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="68"/>
       <c r="G21" s="64"/>
       <c r="H21" s="64"/>
     </row>
-    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36" t="s">
+        <v>142</v>
+      </c>
       <c r="G22" s="64"/>
       <c r="H22" s="64"/>
     </row>
-    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="71" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="71"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="64"/>
       <c r="H23" s="64"/>
     </row>
-    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
       <c r="G24" s="64"/>
       <c r="H24" s="64"/>
     </row>
-    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="31"/>
       <c r="G25" s="64"/>
       <c r="H25" s="64"/>
     </row>
-    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="33"/>
       <c r="G26" s="64"/>
       <c r="H26" s="64"/>
     </row>
-    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="70"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73"/>
       <c r="G27" s="64"/>
       <c r="H27" s="64"/>
     </row>
-    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="70"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73"/>
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
     </row>
-    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="75"/>
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
     </row>
@@ -3711,6 +3879,26 @@
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G41" s="64"/>
       <c r="H41" s="64"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3742,7 +3930,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="76" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="79" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
@@ -3750,43 +3938,43 @@
         <v>80</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="73" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="76" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="74" t="s">
+      <c r="J1" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="75"/>
+      <c r="K1" s="78"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="78" t="n">
+      <c r="B2" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="78" t="n">
+      <c r="C2" s="81" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="79" t="n">
+      <c r="D2" s="82" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="48" t="n">
@@ -3810,16 +3998,16 @@
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="77" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="78" t="n">
+      <c r="A3" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="78" t="n">
+      <c r="C3" s="81" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="79" t="n">
+      <c r="D3" s="82" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="48" t="n">
@@ -3843,16 +4031,16 @@
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="77" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="78" t="n">
+      <c r="A4" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="78" t="n">
+      <c r="C4" s="81" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="79" t="n">
+      <c r="D4" s="82" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="48" t="n">
@@ -3876,16 +4064,16 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="77" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="78" t="n">
+      <c r="A5" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="78" t="n">
+      <c r="C5" s="81" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="79" t="n">
+      <c r="D5" s="82" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="48" t="n">
@@ -3909,16 +4097,16 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="77" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="78" t="n">
+      <c r="A6" s="80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="78" t="n">
+      <c r="C6" s="81" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="79" t="n">
+      <c r="D6" s="82" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="48" t="n">
@@ -3942,16 +4130,16 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="77" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="78" t="n">
+      <c r="A7" s="80" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="78" t="n">
+      <c r="C7" s="81" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="79" t="n">
+      <c r="D7" s="82" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="48" t="n">
@@ -3975,16 +4163,16 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="77" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="78" t="n">
+      <c r="A8" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="78" t="n">
+      <c r="C8" s="81" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="79" t="n">
+      <c r="D8" s="82" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="48" t="n">
@@ -4008,16 +4196,16 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="77" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="78" t="n">
+      <c r="A9" s="80" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="78" t="n">
+      <c r="C9" s="81" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="79" t="n">
+      <c r="D9" s="82" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="48" t="n">
@@ -4041,16 +4229,16 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="77" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="78" t="n">
+      <c r="A10" s="80" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="78" t="n">
+      <c r="C10" s="81" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="79" t="n">
+      <c r="D10" s="82" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="48" t="n">
@@ -4074,16 +4262,16 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="78" t="n">
+      <c r="B11" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="78" t="n">
+      <c r="C11" s="81" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="79" t="n">
+      <c r="D11" s="82" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="48" t="n">
@@ -4107,16 +4295,16 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="78" t="n">
+      <c r="A12" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="78" t="n">
+      <c r="C12" s="81" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="79" t="n">
+      <c r="D12" s="82" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="48" t="n">
@@ -4140,16 +4328,16 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="B13" s="78" t="n">
+      <c r="A13" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="78" t="n">
+      <c r="C13" s="81" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="79" t="n">
+      <c r="D13" s="82" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="48" t="n">
@@ -4173,16 +4361,16 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="78" t="n">
+      <c r="A14" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="78" t="n">
+      <c r="C14" s="81" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="79" t="n">
+      <c r="D14" s="82" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="48" t="n">
@@ -4206,16 +4394,16 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="B15" s="78" t="n">
+      <c r="A15" s="80" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="81" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="78" t="n">
+      <c r="C15" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="79" t="n">
+      <c r="D15" s="82" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="48" t="n">
@@ -4239,16 +4427,16 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="80" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" s="81" t="n">
+      <c r="A16" s="83" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="84" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="81" t="n">
+      <c r="C16" s="84" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="81" t="n">
+      <c r="D16" s="84" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="54" t="n">
@@ -4317,7 +4505,7 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="78" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
@@ -4406,7 +4594,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.52"/>
@@ -4434,7 +4622,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G1" s="64"/>
       <c r="H1" s="64"/>
@@ -4445,13 +4633,13 @@
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
@@ -4466,13 +4654,13 @@
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
@@ -4487,16 +4675,16 @@
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="64"/>
@@ -4508,13 +4696,13 @@
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
@@ -4529,16 +4717,16 @@
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="64"/>
@@ -4552,16 +4740,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -4572,16 +4760,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="64"/>
@@ -4595,16 +4783,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="64"/>
@@ -4614,22 +4802,22 @@
       <c r="K9" s="64"/>
     </row>
     <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="8"/>
+      <c r="D10" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="20"/>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
@@ -4637,22 +4825,22 @@
       <c r="K10" s="64"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="F11" s="16"/>
+        <v>185</v>
+      </c>
+      <c r="F11" s="22"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
@@ -4660,21 +4848,21 @@
       <c r="K11" s="64"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="66" t="s">
-        <v>183</v>
+      <c r="F12" s="23" t="s">
+        <v>188</v>
       </c>
       <c r="G12" s="64"/>
       <c r="H12" s="64"/>
@@ -4683,43 +4871,33 @@
       <c r="K12" s="64"/>
     </row>
     <row r="13" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="34" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E13" s="35"/>
-      <c r="F13" s="69"/>
+      <c r="F13" s="36"/>
       <c r="G13" s="64"/>
       <c r="H13" s="64"/>
       <c r="I13" s="64"/>
       <c r="J13" s="64"/>
       <c r="K13" s="64"/>
     </row>
-    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="F14" s="66"/>
+    <row r="14" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="64"/>
       <c r="H14" s="64"/>
       <c r="I14" s="64"/>
@@ -4727,214 +4905,272 @@
       <c r="K14" s="64"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="F15" s="69"/>
+      <c r="B15" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="31"/>
       <c r="G15" s="64"/>
       <c r="H15" s="64"/>
       <c r="I15" s="64"/>
       <c r="J15" s="64"/>
       <c r="K15" s="64"/>
     </row>
-    <row r="16" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="F16" s="8"/>
+    <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="23"/>
       <c r="G16" s="64"/>
       <c r="H16" s="64"/>
       <c r="I16" s="64"/>
       <c r="J16" s="64"/>
       <c r="K16" s="64"/>
     </row>
-    <row r="17" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="16"/>
+    <row r="17" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="85"/>
+      <c r="B17" s="86"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="87"/>
       <c r="G17" s="64"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
       <c r="J17" s="64"/>
       <c r="K17" s="64"/>
     </row>
-    <row r="18" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="69" t="s">
-        <v>197</v>
-      </c>
+    <row r="18" customFormat="false" ht="131.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="85"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="64"/>
       <c r="H18" s="64"/>
       <c r="I18" s="64"/>
       <c r="J18" s="64"/>
       <c r="K18" s="64"/>
     </row>
-    <row r="19" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="C19" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="71" t="s">
-        <v>199</v>
-      </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
+    <row r="19" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="88"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="90"/>
       <c r="G19" s="64"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
       <c r="J19" s="64"/>
       <c r="K19" s="64"/>
     </row>
-    <row r="20" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="F20" s="66"/>
+    <row r="20" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20" s="20"/>
       <c r="G20" s="64"/>
       <c r="H20" s="64"/>
       <c r="I20" s="64"/>
       <c r="J20" s="64"/>
       <c r="K20" s="64"/>
     </row>
-    <row r="21" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="C21" s="35" t="s">
+    <row r="21" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="F21" s="69"/>
+      <c r="D21" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="22"/>
       <c r="G21" s="64"/>
       <c r="H21" s="64"/>
       <c r="I21" s="64"/>
       <c r="J21" s="64"/>
       <c r="K21" s="64"/>
     </row>
-    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="23" t="s">
+        <v>202</v>
+      </c>
       <c r="G22" s="64"/>
       <c r="H22" s="64"/>
       <c r="I22" s="64"/>
       <c r="J22" s="64"/>
       <c r="K22" s="64"/>
     </row>
-    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="71"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="64"/>
       <c r="H23" s="64"/>
       <c r="I23" s="64"/>
       <c r="J23" s="64"/>
       <c r="K23" s="64"/>
     </row>
-    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
       <c r="G24" s="64"/>
       <c r="H24" s="64"/>
       <c r="I24" s="64"/>
       <c r="J24" s="64"/>
       <c r="K24" s="64"/>
     </row>
-    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="31"/>
       <c r="G25" s="64"/>
       <c r="H25" s="64"/>
       <c r="I25" s="64"/>
       <c r="J25" s="64"/>
       <c r="K25" s="64"/>
     </row>
-    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="194.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F26" s="23"/>
       <c r="G26" s="64"/>
       <c r="H26" s="64"/>
       <c r="I26" s="64"/>
       <c r="J26" s="64"/>
       <c r="K26" s="64"/>
     </row>
-    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="133.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="70"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="92"/>
       <c r="G27" s="64"/>
       <c r="H27" s="64"/>
       <c r="I27" s="64"/>
       <c r="J27" s="64"/>
       <c r="K27" s="64"/>
     </row>
-    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="111.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="70"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="92"/>
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
       <c r="I28" s="64"/>
       <c r="J28" s="64"/>
       <c r="K28" s="64"/>
     </row>
-    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="102.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="94"/>
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
       <c r="I29" s="64"/>
@@ -4968,6 +5204,41 @@
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
       <c r="K33" s="64"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="64"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="64"/>
+      <c r="K36" s="64"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="64"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="64"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4999,7 +5270,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="82" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="95" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
@@ -5007,13 +5278,13 @@
         <v>80</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F1" s="43" t="s">
         <v>27</v>
@@ -5034,7 +5305,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B2" s="47" t="n">
         <v>0</v>
@@ -5054,19 +5325,19 @@
       <c r="G2" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H2" s="83" t="n">
+      <c r="H2" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I2" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="J2" s="83" t="n">
+      <c r="J2" s="96" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B3" s="47" t="n">
         <v>1</v>
@@ -5086,19 +5357,19 @@
       <c r="G3" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H3" s="83" t="n">
+      <c r="H3" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I3" s="48" t="n">
         <v>9549</v>
       </c>
-      <c r="J3" s="83" t="n">
+      <c r="J3" s="96" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B4" s="47" t="n">
         <v>2</v>
@@ -5118,7 +5389,7 @@
       <c r="G4" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H4" s="83" t="n">
+      <c r="H4" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I4" s="48" t="n">
@@ -5130,7 +5401,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="46" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B5" s="47" t="n">
         <v>3</v>
@@ -5150,7 +5421,7 @@
       <c r="G5" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H5" s="83" t="n">
+      <c r="H5" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I5" s="48" t="n">
@@ -5162,7 +5433,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="46" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B6" s="47" t="n">
         <v>4</v>
@@ -5182,7 +5453,7 @@
       <c r="G6" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="83" t="n">
+      <c r="H6" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I6" s="48" t="n">
@@ -5194,7 +5465,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="46" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B7" s="47" t="n">
         <v>5</v>
@@ -5214,7 +5485,7 @@
       <c r="G7" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H7" s="83" t="n">
+      <c r="H7" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I7" s="48" t="n">
@@ -5226,7 +5497,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B8" s="47" t="n">
         <v>6</v>
@@ -5246,7 +5517,7 @@
       <c r="G8" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="83" t="n">
+      <c r="H8" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I8" s="48" t="n">
@@ -5258,7 +5529,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="46" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B9" s="47" t="n">
         <v>7</v>
@@ -5278,7 +5549,7 @@
       <c r="G9" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="83" t="n">
+      <c r="H9" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I9" s="48" t="n">
@@ -5290,7 +5561,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B10" s="47" t="n">
         <v>8</v>
@@ -5310,7 +5581,7 @@
       <c r="G10" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="83" t="n">
+      <c r="H10" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I10" s="48" t="n">
@@ -5322,7 +5593,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B11" s="47" t="n">
         <v>9</v>
@@ -5342,7 +5613,7 @@
       <c r="G11" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H11" s="83" t="n">
+      <c r="H11" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I11" s="48" t="n">
@@ -5354,7 +5625,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B12" s="47" t="n">
         <v>10</v>
@@ -5374,7 +5645,7 @@
       <c r="G12" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="83" t="n">
+      <c r="H12" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I12" s="48" t="n">
@@ -5386,7 +5657,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B13" s="47" t="n">
         <v>11</v>
@@ -5406,7 +5677,7 @@
       <c r="G13" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H13" s="83" t="n">
+      <c r="H13" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I13" s="48" t="n">
@@ -5418,7 +5689,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B14" s="47" t="n">
         <v>12</v>
@@ -5438,7 +5709,7 @@
       <c r="G14" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H14" s="83" t="n">
+      <c r="H14" s="96" t="n">
         <v>10000</v>
       </c>
       <c r="I14" s="48" t="n">
@@ -5449,8 +5720,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="84" t="s">
-        <v>159</v>
+      <c r="A15" s="97" t="s">
+        <v>164</v>
       </c>
       <c r="B15" s="53" t="n">
         <v>13</v>
@@ -5470,7 +5741,7 @@
       <c r="G15" s="54" t="n">
         <v>10000</v>
       </c>
-      <c r="H15" s="85" t="n">
+      <c r="H15" s="98" t="n">
         <v>10000</v>
       </c>
       <c r="I15" s="48" t="n">

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="237">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -351,11 +351,31 @@
 Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__2_5.ipynb
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__3_5.ipynb
-pd_CIC18__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Entrenamiento con Simple T5. 2 horas por epoch
@@ -773,11 +793,31 @@
 Pd_CIC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
 pd_CIC17__NearMiss_SMOTE__v1__training_v1__2_5.ipynb
 pd_CIC17__NearMiss_SMOTE__v1__training_v1__3_5.ipynb
-pd_CIC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
 pd_CIC17__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__train__1.csv
@@ -837,6 +877,43 @@
 Pd_CIC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__training_v1__2_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__training_v1__3_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__training_v1__4_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE_ENN__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
+pd_CIC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_CIC17__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_CIC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">ORIGINAL (CIC17)</t>
   </si>
   <si>
@@ -883,9 +960,6 @@
   </si>
   <si>
     <t xml:space="preserve">MODELOS GENERADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17_eda_v1.ipynb</t>
   </si>
   <si>
     <t xml:space="preserve">BCCC17</t>
@@ -1056,6 +1130,43 @@
 Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__3_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__4_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__2.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__3.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__1.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__2.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__2.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__3.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__3.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__4.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
   </si>
   <si>
@@ -1082,11 +1193,31 @@
 Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
 pd_BCCC17__NearMiss_SMOTE__v1__training_v1__2_5.ipynb
 pd_BCCC17__NearMiss_SMOTE__v1__training_v1__3_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
 pd_BCCC17__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
@@ -1134,6 +1265,43 @@
     <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__train.csv
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__test.csv
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__1.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__2.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__3.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__4.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv
+Pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__2_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__3_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__4_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__3.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__4.csv
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
+pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__1.csv
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
@@ -1407,17 +1575,17 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -1453,7 +1621,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="94">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1558,6 +1726,18 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1602,18 +1782,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1654,6 +1822,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1662,7 +1834,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1674,7 +1846,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1730,26 +1910,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1786,7 +1958,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1794,16 +1966,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1818,14 +1982,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1839,15 +1995,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2099,7 +2247,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.05"/>
@@ -2361,242 +2509,272 @@
       <c r="F15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>49</v>
-      </c>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="33"/>
-    </row>
-    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="36" t="s">
-        <v>54</v>
-      </c>
+      <c r="F18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C20" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D20" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39"/>
-    </row>
-    <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="40"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
+      <c r="E20" s="27"/>
       <c r="F20" s="28"/>
     </row>
-    <row r="21" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+    <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="28"/>
+    </row>
+    <row r="22" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="40"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="31"/>
+    </row>
+    <row r="23" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B23" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C23" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D23" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E23" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B24" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C24" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="22"/>
-    </row>
-    <row r="23" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="s">
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B25" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C25" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D25" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="36" t="s">
+      <c r="E25" s="38"/>
+      <c r="F25" s="39" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
+    <row r="26" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B26" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C26" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D26" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-    </row>
-    <row r="25" s="2" customFormat="true" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29" t="s">
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+    </row>
+    <row r="27" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
+    </row>
+    <row r="28" s="2" customFormat="true" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="31"/>
+    </row>
+    <row r="29" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B29" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C29" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D29" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E29" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="F26" s="31"/>
-    </row>
-    <row r="27" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="s">
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B30" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="33"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="s">
+      <c r="F30" s="36"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B31" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C31" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D31" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="36" t="s">
+      <c r="E31" s="38"/>
+      <c r="F31" s="39" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37" t="s">
+    <row r="32" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="38" t="s">
+      <c r="B32" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C32" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D32" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39"/>
-    </row>
-    <row r="30" customFormat="false" ht="127.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="28"/>
+    </row>
+    <row r="33" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" customFormat="false" ht="127.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2697,13 +2875,13 @@
       <c r="J2" s="48" t="n">
         <v>10000</v>
       </c>
-      <c r="K2" s="48" t="n">
+      <c r="K2" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD2" s="2"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="47" t="n">
@@ -2733,13 +2911,13 @@
       <c r="J3" s="48" t="n">
         <v>9840</v>
       </c>
-      <c r="K3" s="48" t="n">
+      <c r="K3" s="50" t="n">
         <v>9993</v>
       </c>
       <c r="XFD3" s="2"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="51" t="s">
         <v>87</v>
       </c>
       <c r="B4" s="47" t="n">
@@ -2769,13 +2947,13 @@
       <c r="J4" s="48" t="n">
         <v>9974</v>
       </c>
-      <c r="K4" s="48" t="n">
+      <c r="K4" s="50" t="n">
         <v>9968</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="51" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="47" t="n">
@@ -2787,7 +2965,7 @@
       <c r="D5" s="48" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="51" t="n">
+      <c r="E5" s="52" t="n">
         <v>434873</v>
       </c>
       <c r="F5" s="48" t="n">
@@ -2805,13 +2983,13 @@
       <c r="J5" s="48" t="n">
         <v>9855</v>
       </c>
-      <c r="K5" s="48" t="n">
+      <c r="K5" s="50" t="n">
         <v>9914</v>
       </c>
       <c r="XFD5" s="2"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="51" t="s">
         <v>89</v>
       </c>
       <c r="B6" s="47" t="n">
@@ -2823,7 +3001,7 @@
       <c r="D6" s="48" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="52" t="n">
         <v>282310</v>
       </c>
       <c r="F6" s="48" t="n">
@@ -2841,13 +3019,13 @@
       <c r="J6" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="K6" s="48" t="n">
+      <c r="K6" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD6" s="2"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="51" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="47" t="n">
@@ -2859,7 +3037,7 @@
       <c r="D7" s="48" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="51" t="n">
+      <c r="E7" s="52" t="n">
         <v>161897</v>
       </c>
       <c r="F7" s="48" t="n">
@@ -2877,13 +3055,13 @@
       <c r="J7" s="48" t="n">
         <v>8820</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="50" t="n">
         <v>9998</v>
       </c>
       <c r="XFD7" s="2"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>91</v>
       </c>
       <c r="B8" s="47" t="n">
@@ -2895,7 +3073,7 @@
       <c r="D8" s="48" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="51" t="n">
+      <c r="E8" s="52" t="n">
         <v>117322</v>
       </c>
       <c r="F8" s="48" t="n">
@@ -2913,13 +3091,13 @@
       <c r="J8" s="48" t="n">
         <v>9896</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="50" t="n">
         <v>9967</v>
       </c>
       <c r="XFD8" s="2"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="51" t="s">
         <v>92</v>
       </c>
       <c r="B9" s="47" t="n">
@@ -2931,7 +3109,7 @@
       <c r="D9" s="48" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="51" t="n">
+      <c r="E9" s="52" t="n">
         <v>41455</v>
       </c>
       <c r="F9" s="48" t="n">
@@ -2949,13 +3127,13 @@
       <c r="J9" s="48" t="n">
         <v>9533</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="50" t="n">
         <v>9974</v>
       </c>
       <c r="XFD9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="51" t="s">
         <v>93</v>
       </c>
       <c r="B10" s="47" t="n">
@@ -2967,7 +3145,7 @@
       <c r="D10" s="48" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="51" t="n">
+      <c r="E10" s="52" t="n">
         <v>39352</v>
       </c>
       <c r="F10" s="48" t="n">
@@ -2985,13 +3163,13 @@
       <c r="J10" s="48" t="n">
         <v>9986</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="51" t="s">
         <v>94</v>
       </c>
       <c r="B11" s="47" t="n">
@@ -3003,7 +3181,7 @@
       <c r="D11" s="48" t="n">
         <v>19462</v>
       </c>
-      <c r="E11" s="51" t="n">
+      <c r="E11" s="52" t="n">
         <v>19462</v>
       </c>
       <c r="F11" s="48" t="n">
@@ -3021,13 +3199,13 @@
       <c r="J11" s="48" t="n">
         <v>10000</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="51" t="s">
         <v>95</v>
       </c>
       <c r="B12" s="47" t="n">
@@ -3039,7 +3217,7 @@
       <c r="D12" s="48" t="n">
         <v>10285</v>
       </c>
-      <c r="E12" s="51" t="n">
+      <c r="E12" s="52" t="n">
         <v>10285</v>
       </c>
       <c r="F12" s="48" t="n">
@@ -3057,13 +3235,13 @@
       <c r="J12" s="48" t="n">
         <v>9838</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="50" t="n">
         <v>9939</v>
       </c>
       <c r="XFD12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="51" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="47" t="n">
@@ -3075,7 +3253,7 @@
       <c r="D13" s="48" t="n">
         <v>1730</v>
       </c>
-      <c r="E13" s="51" t="n">
+      <c r="E13" s="52" t="n">
         <v>1730</v>
       </c>
       <c r="F13" s="48" t="n">
@@ -3093,12 +3271,12 @@
       <c r="J13" s="48" t="n">
         <v>10000</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B14" s="47" t="n">
@@ -3110,7 +3288,7 @@
       <c r="D14" s="48" t="n">
         <v>611</v>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="52" t="n">
         <v>611</v>
       </c>
       <c r="F14" s="48" t="n">
@@ -3128,12 +3306,12 @@
       <c r="J14" s="48" t="n">
         <v>9624</v>
       </c>
-      <c r="K14" s="48" t="n">
+      <c r="K14" s="50" t="n">
         <v>9593</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="51" t="s">
         <v>98</v>
       </c>
       <c r="B15" s="47" t="n">
@@ -3145,7 +3323,7 @@
       <c r="D15" s="48" t="n">
         <v>230</v>
       </c>
-      <c r="E15" s="51" t="n">
+      <c r="E15" s="52" t="n">
         <v>230</v>
       </c>
       <c r="F15" s="48" t="n">
@@ -3163,42 +3341,42 @@
       <c r="J15" s="48" t="n">
         <v>9673</v>
       </c>
-      <c r="K15" s="48" t="n">
+      <c r="K15" s="50" t="n">
         <v>9655</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="53" t="n">
+      <c r="B16" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="54" t="n">
+      <c r="C16" s="55" t="n">
         <v>87</v>
       </c>
-      <c r="D16" s="54" t="n">
+      <c r="D16" s="55" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="54" t="n">
+      <c r="E16" s="55" t="n">
         <v>87</v>
       </c>
-      <c r="F16" s="48" t="n">
+      <c r="F16" s="55" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="55" t="n">
+      <c r="G16" s="56" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="48" t="n">
+      <c r="H16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="55" t="n">
         <v>9987</v>
       </c>
-      <c r="K16" s="48" t="n">
+      <c r="K16" s="58" t="n">
         <v>9986</v>
       </c>
     </row>
@@ -3241,14 +3419,14 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="56"/>
+      <c r="E18" s="59"/>
       <c r="F18" s="47"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="56"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="48"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="56"/>
+      <c r="E19" s="59"/>
       <c r="F19" s="47"/>
       <c r="G19" s="3"/>
       <c r="H19" s="48"/>
@@ -3325,25 +3503,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="57" width="92.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="58" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="57" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="57" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="62" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="65" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -3352,11 +3530,11 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
@@ -3372,9 +3550,9 @@
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="63"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
@@ -3390,9 +3568,9 @@
       <c r="E3" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="65"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -3408,9 +3586,9 @@
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="65"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
@@ -3426,9 +3604,9 @@
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="65"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
@@ -3444,9 +3622,9 @@
       <c r="E6" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F6" s="65"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
     </row>
     <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -3464,7 +3642,7 @@
       <c r="E7" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="63"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
@@ -3484,9 +3662,9 @@
       <c r="E8" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
     </row>
     <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
@@ -3504,29 +3682,29 @@
       <c r="E9" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="63"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
     </row>
     <row r="10" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="F10" s="67"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
@@ -3544,9 +3722,9 @@
       <c r="E11" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
@@ -3565,8 +3743,8 @@
       <c r="F12" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
     </row>
     <row r="13" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
@@ -3583,322 +3761,378 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
     </row>
     <row r="14" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-    </row>
-    <row r="15" s="69" customFormat="true" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>128</v>
-      </c>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+    </row>
+    <row r="15" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-    </row>
-    <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+    </row>
+    <row r="16" s="74" customFormat="true" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" s="34"/>
+    </row>
+    <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D17" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F16" s="33"/>
-    </row>
-    <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
+      <c r="F17" s="36"/>
+    </row>
+    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B18" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C18" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D18" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="36" t="s">
+      <c r="E18" s="38"/>
+      <c r="F18" s="39" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="70" t="s">
+    <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B19" s="73" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C19" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D19" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="71"/>
-      <c r="F18" s="39"/>
-    </row>
-    <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="28"/>
     </row>
-    <row r="20" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="s">
+    <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B22" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D22" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E22" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="F20" s="67"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-    </row>
-    <row r="21" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="F22" s="70"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+    </row>
+    <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B23" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D23" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E23" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-    </row>
-    <row r="22" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
+      <c r="F23" s="71"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+    </row>
+    <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B24" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C24" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D24" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="36" t="s">
+      <c r="E24" s="38"/>
+      <c r="F24" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-    </row>
-    <row r="23" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="70" t="s">
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+    </row>
+    <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="71" t="s">
+      <c r="B25" s="73" t="s">
         <v>143</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C25" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="D25" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="E23" s="71"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-    </row>
-    <row r="24" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-    </row>
-    <row r="25" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="s">
+      <c r="E25" s="73"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+    </row>
+    <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="72"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+    </row>
+    <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+    </row>
+    <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B28" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D28" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E28" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-    </row>
-    <row r="26" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
+      <c r="F28" s="34"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+    </row>
+    <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B29" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D29" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F26" s="33"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-    </row>
-    <row r="27" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="70"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-    </row>
-    <row r="28" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="70"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-    </row>
-    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-    </row>
-    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-    </row>
-    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+    </row>
+    <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+    </row>
+    <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" s="73"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+    </row>
+    <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="72"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+    </row>
+    <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="67"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="64"/>
-      <c r="H46" s="64"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="67"/>
+    </row>
+    <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
+    </row>
+    <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
+    </row>
+    <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G49" s="67"/>
+      <c r="H49" s="67"/>
+    </row>
+    <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G50" s="67"/>
+      <c r="H50" s="67"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3930,7 +4164,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="79" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="80" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
@@ -3938,439 +4172,439 @@
         <v>80</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="76" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="77" t="s">
+      <c r="H1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="77" t="s">
+      <c r="I1" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="77" t="s">
+      <c r="J1" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="78"/>
+      <c r="K1" s="79"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="81" t="n">
+      <c r="B2" s="82" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="81" t="n">
+      <c r="C2" s="82" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="82" t="n">
+      <c r="D2" s="83" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="48" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="51" t="n">
+      <c r="F2" s="52" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="51" t="n">
+      <c r="G2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I2" s="48" t="n">
         <v>10000</v>
       </c>
-      <c r="J2" s="48" t="n">
+      <c r="J2" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="80" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="81" t="n">
+      <c r="A3" s="81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="81" t="n">
+      <c r="C3" s="82" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="82" t="n">
+      <c r="D3" s="83" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="48" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="51" t="n">
+      <c r="F3" s="52" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="51" t="n">
+      <c r="G3" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I3" s="48" t="n">
         <v>9656</v>
       </c>
-      <c r="J3" s="48" t="n">
+      <c r="J3" s="50" t="n">
         <v>9968</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="80" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="81" t="n">
+      <c r="A4" s="81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="81" t="n">
+      <c r="C4" s="82" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="82" t="n">
+      <c r="D4" s="83" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="48" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="51" t="n">
+      <c r="F4" s="52" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="51" t="n">
+      <c r="G4" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I4" s="48" t="n">
         <v>9765</v>
       </c>
-      <c r="J4" s="48" t="n">
+      <c r="J4" s="50" t="n">
         <v>9995</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="80" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="81" t="n">
+      <c r="A5" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="81" t="n">
+      <c r="C5" s="82" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="82" t="n">
+      <c r="D5" s="83" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="48" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="52" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="51" t="n">
+      <c r="G5" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I5" s="48" t="n">
         <v>9712</v>
       </c>
-      <c r="J5" s="48" t="n">
+      <c r="J5" s="50" t="n">
         <v>9960</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="80" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="81" t="n">
+      <c r="A6" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="81" t="n">
+      <c r="C6" s="82" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="82" t="n">
+      <c r="D6" s="83" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="48" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="52" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="51" t="n">
+      <c r="G6" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I6" s="48" t="n">
         <v>9913</v>
       </c>
-      <c r="J6" s="48" t="n">
+      <c r="J6" s="50" t="n">
         <v>9958</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="80" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="81" t="n">
+      <c r="A7" s="81" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="81" t="n">
+      <c r="C7" s="82" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="82" t="n">
+      <c r="D7" s="83" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="48" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="51" t="n">
+      <c r="F7" s="52" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="51" t="n">
+      <c r="G7" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I7" s="48" t="n">
         <v>9908</v>
       </c>
-      <c r="J7" s="48" t="n">
+      <c r="J7" s="50" t="n">
         <v>9923</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="81" t="n">
+      <c r="A8" s="81" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="82" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="81" t="n">
+      <c r="C8" s="82" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="82" t="n">
+      <c r="D8" s="83" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="48" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="52" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="51" t="n">
+      <c r="G8" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I8" s="48" t="n">
         <v>9637</v>
       </c>
-      <c r="J8" s="48" t="n">
+      <c r="J8" s="50" t="n">
         <v>9785</v>
       </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="80" t="s">
-        <v>158</v>
-      </c>
-      <c r="B9" s="81" t="n">
+      <c r="A9" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="81" t="n">
+      <c r="C9" s="82" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="82" t="n">
+      <c r="D9" s="83" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="48" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="51" t="n">
+      <c r="F9" s="52" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="51" t="n">
+      <c r="G9" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I9" s="48" t="n">
         <v>9814</v>
       </c>
-      <c r="J9" s="48" t="n">
+      <c r="J9" s="50" t="n">
         <v>9872</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="80" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="81" t="n">
+      <c r="A10" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="82" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="81" t="n">
+      <c r="C10" s="82" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="82" t="n">
+      <c r="D10" s="83" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="48" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="51" t="n">
+      <c r="F10" s="52" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="51" t="n">
+      <c r="G10" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I10" s="48" t="n">
         <v>9622</v>
       </c>
-      <c r="J10" s="48" t="n">
+      <c r="J10" s="50" t="n">
         <v>9637</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="81" t="n">
+      <c r="B11" s="82" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="81" t="n">
+      <c r="C11" s="82" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="82" t="n">
+      <c r="D11" s="83" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="48" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="52" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="51" t="n">
+      <c r="G11" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I11" s="48" t="n">
         <v>9832</v>
       </c>
-      <c r="J11" s="48" t="n">
+      <c r="J11" s="50" t="n">
         <v>9979</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="80" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="81" t="n">
+      <c r="A12" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="82" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="81" t="n">
+      <c r="C12" s="82" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="82" t="n">
+      <c r="D12" s="83" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="48" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="51" t="n">
+      <c r="F12" s="52" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="51" t="n">
+      <c r="G12" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I12" s="48" t="n">
         <v>5782</v>
       </c>
-      <c r="J12" s="48" t="n">
+      <c r="J12" s="50" t="n">
         <v>5793</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="80" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="81" t="n">
+      <c r="A13" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="82" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="81" t="n">
+      <c r="C13" s="82" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="82" t="n">
+      <c r="D13" s="83" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="48" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="52" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="51" t="n">
+      <c r="G13" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I13" s="48" t="n">
         <v>5862</v>
       </c>
-      <c r="J13" s="48" t="n">
+      <c r="J13" s="50" t="n">
         <v>5871</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="81" t="n">
+      <c r="A14" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="82" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="81" t="n">
+      <c r="C14" s="82" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="82" t="n">
+      <c r="D14" s="83" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="48" t="n">
@@ -4379,31 +4613,31 @@
       <c r="F14" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="51" t="n">
+      <c r="G14" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I14" s="48" t="n">
         <v>9904</v>
       </c>
-      <c r="J14" s="48" t="n">
+      <c r="J14" s="50" t="n">
         <v>9934</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="80" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="81" t="n">
+      <c r="A15" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" s="82" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="81" t="n">
+      <c r="C15" s="82" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="82" t="n">
+      <c r="D15" s="83" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="48" t="n">
@@ -4412,49 +4646,49 @@
       <c r="F15" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="51" t="n">
+      <c r="G15" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I15" s="48" t="n">
         <v>9725</v>
       </c>
-      <c r="J15" s="48" t="n">
+      <c r="J15" s="50" t="n">
         <v>9727</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="83" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="84" t="n">
+      <c r="A16" s="84" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="84" t="n">
+      <c r="C16" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="84" t="n">
+      <c r="D16" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="54" t="n">
+      <c r="E16" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="54" t="n">
+      <c r="F16" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="48" t="n">
+      <c r="G16" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="58" t="n">
         <v>10000</v>
       </c>
       <c r="L16" s="2"/>
@@ -4495,17 +4729,17 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="56"/>
+      <c r="E18" s="59"/>
       <c r="F18" s="47"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="56"/>
+      <c r="E19" s="59"/>
       <c r="F19" s="47"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="79" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
@@ -4594,7 +4828,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.52"/>
@@ -4622,134 +4856,132 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+        <v>170</v>
+      </c>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
-        <v>166</v>
-      </c>
+      <c r="B2" s="7"/>
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
     </row>
     <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
     </row>
     <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -4760,485 +4992,573 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
     </row>
     <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
     </row>
     <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
+      <c r="D10" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="86"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
     </row>
     <row r="11" s="2" customFormat="true" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F11" s="22"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
+        <v>192</v>
+      </c>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
     </row>
     <row r="13" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C13" s="35" t="s">
+      <c r="B13" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
+      <c r="D13" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
     </row>
     <row r="14" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-    </row>
-    <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="s">
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+    </row>
+    <row r="15" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+    </row>
+    <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C15" s="30" t="s">
+      <c r="B16" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-    </row>
-    <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="D16" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+    </row>
+    <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="B17" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-    </row>
-    <row r="17" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="85"/>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-    </row>
-    <row r="18" customFormat="false" ht="131.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="85"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-    </row>
-    <row r="19" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="88"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-    </row>
-    <row r="20" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="D17" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+    </row>
+    <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+    </row>
+    <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="73" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="73"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+    </row>
+    <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+    </row>
+    <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="87"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+    </row>
+    <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="B22" s="69" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-    </row>
-    <row r="21" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="D22" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="F22" s="86"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+    </row>
+    <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="B23" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-    </row>
-    <row r="22" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="D23" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+    </row>
+    <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="B24" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-    </row>
-    <row r="23" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="70" t="s">
+      <c r="D24" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+    </row>
+    <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="C23" s="71" t="s">
+      <c r="B25" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="71"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-    </row>
-    <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-    </row>
-    <row r="25" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="s">
+      <c r="D25" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="E25" s="73"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+    </row>
+    <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="72"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+    </row>
+    <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+    </row>
+    <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C25" s="30" t="s">
+      <c r="B28" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-    </row>
-    <row r="26" customFormat="false" ht="194.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="D28" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+    </row>
+    <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26" s="15" t="s">
+      <c r="B29" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="F26" s="23"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-    </row>
-    <row r="27" customFormat="false" ht="133.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="70"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="92"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
-    </row>
-    <row r="28" customFormat="false" ht="111.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="70"/>
-      <c r="B28" s="91"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-    </row>
-    <row r="29" customFormat="false" ht="102.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-    </row>
-    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-    </row>
-    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-    </row>
-    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-    </row>
-    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
+      <c r="D29" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" s="23"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+    </row>
+    <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+    </row>
+    <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>223</v>
+      </c>
+      <c r="E31" s="73"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+    </row>
+    <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="72"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="67"/>
+    </row>
+    <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="67"/>
+      <c r="K33" s="67"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="67"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5270,7 +5590,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="95" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="92" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
@@ -5278,13 +5598,13 @@
         <v>80</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F1" s="43" t="s">
         <v>27</v>
@@ -5292,7 +5612,7 @@
       <c r="G1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>57</v>
       </c>
       <c r="I1" s="43" t="s">
@@ -5305,7 +5625,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B2" s="47" t="n">
         <v>0</v>
@@ -5313,31 +5633,31 @@
       <c r="C2" s="48" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="51" t="n">
+      <c r="D2" s="52" t="n">
         <v>1785037</v>
       </c>
       <c r="E2" s="48" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="51" t="n">
+      <c r="F2" s="52" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="96" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="96" t="n">
+      <c r="G2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B3" s="47" t="n">
         <v>1</v>
@@ -5345,31 +5665,31 @@
       <c r="C3" s="48" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="51" t="n">
+      <c r="D3" s="52" t="n">
         <v>346201</v>
       </c>
       <c r="E3" s="48" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="51" t="n">
+      <c r="F3" s="52" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="96" t="n">
+      <c r="G3" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I3" s="48" t="n">
         <v>9549</v>
       </c>
-      <c r="J3" s="96" t="n">
+      <c r="J3" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B4" s="47" t="n">
         <v>2</v>
@@ -5377,31 +5697,31 @@
       <c r="C4" s="48" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="51" t="n">
+      <c r="D4" s="52" t="n">
         <v>161323</v>
       </c>
       <c r="E4" s="48" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="51" t="n">
+      <c r="F4" s="52" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="96" t="n">
+      <c r="G4" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I4" s="48" t="n">
         <v>9994</v>
       </c>
-      <c r="J4" s="48" t="n">
+      <c r="J4" s="50" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="46" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B5" s="47" t="n">
         <v>3</v>
@@ -5409,31 +5729,31 @@
       <c r="C5" s="48" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="51" t="n">
+      <c r="D5" s="52" t="n">
         <v>95729</v>
       </c>
       <c r="E5" s="48" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="52" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="96" t="n">
+      <c r="G5" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I5" s="48" t="n">
         <v>9593</v>
       </c>
-      <c r="J5" s="48" t="n">
+      <c r="J5" s="50" t="n">
         <v>9989</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="46" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B6" s="47" t="n">
         <v>4</v>
@@ -5441,31 +5761,31 @@
       <c r="C6" s="48" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="52" t="n">
         <v>9531</v>
       </c>
       <c r="E6" s="48" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="52" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="96" t="n">
+      <c r="G6" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I6" s="48" t="n">
         <v>9990</v>
       </c>
-      <c r="J6" s="48" t="n">
+      <c r="J6" s="50" t="n">
         <v>9999</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="46" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B7" s="47" t="n">
         <v>5</v>
@@ -5473,31 +5793,31 @@
       <c r="C7" s="48" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="52" t="n">
         <v>8364</v>
       </c>
       <c r="E7" s="48" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="51" t="n">
+      <c r="F7" s="52" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="96" t="n">
+      <c r="G7" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I7" s="48" t="n">
         <v>9781</v>
       </c>
-      <c r="J7" s="48" t="n">
+      <c r="J7" s="50" t="n">
         <v>9944</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B8" s="47" t="n">
         <v>6</v>
@@ -5505,31 +5825,31 @@
       <c r="C8" s="48" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="51" t="n">
+      <c r="D8" s="52" t="n">
         <v>6856</v>
       </c>
       <c r="E8" s="48" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="52" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="96" t="n">
+      <c r="G8" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I8" s="48" t="n">
         <v>9873</v>
       </c>
-      <c r="J8" s="48" t="n">
+      <c r="J8" s="50" t="n">
         <v>9880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="46" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B9" s="47" t="n">
         <v>7</v>
@@ -5537,31 +5857,31 @@
       <c r="C9" s="48" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="51" t="n">
+      <c r="D9" s="52" t="n">
         <v>5949</v>
       </c>
       <c r="E9" s="48" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="51" t="n">
+      <c r="F9" s="52" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="96" t="n">
+      <c r="G9" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I9" s="48" t="n">
         <v>9983</v>
       </c>
-      <c r="J9" s="48" t="n">
+      <c r="J9" s="50" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B10" s="47" t="n">
         <v>8</v>
@@ -5569,31 +5889,31 @@
       <c r="C10" s="48" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="51" t="n">
+      <c r="D10" s="52" t="n">
         <v>5508</v>
       </c>
       <c r="E10" s="48" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="51" t="n">
+      <c r="F10" s="52" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="96" t="n">
+      <c r="G10" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I10" s="48" t="n">
         <v>9995</v>
       </c>
-      <c r="J10" s="48" t="n">
+      <c r="J10" s="50" t="n">
         <v>9995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B11" s="47" t="n">
         <v>9</v>
@@ -5601,31 +5921,31 @@
       <c r="C11" s="48" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="51" t="n">
+      <c r="D11" s="52" t="n">
         <v>5123</v>
       </c>
       <c r="E11" s="48" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="52" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="96" t="n">
+      <c r="G11" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I11" s="48" t="n">
         <v>9868</v>
       </c>
-      <c r="J11" s="48" t="n">
+      <c r="J11" s="50" t="n">
         <v>9881</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B12" s="47" t="n">
         <v>10</v>
@@ -5633,31 +5953,31 @@
       <c r="C12" s="48" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="52" t="n">
         <v>2733</v>
       </c>
       <c r="E12" s="48" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="51" t="n">
+      <c r="F12" s="52" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="96" t="n">
+      <c r="G12" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I12" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="J12" s="48" t="n">
+      <c r="J12" s="50" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B13" s="47" t="n">
         <v>11</v>
@@ -5665,31 +5985,31 @@
       <c r="C13" s="48" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="52" t="n">
         <v>1357</v>
       </c>
       <c r="E13" s="48" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="52" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="96" t="n">
+      <c r="G13" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I13" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="J13" s="48" t="n">
+      <c r="J13" s="50" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B14" s="47" t="n">
         <v>12</v>
@@ -5697,57 +6017,57 @@
       <c r="C14" s="48" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="52" t="n">
         <v>24</v>
       </c>
       <c r="E14" s="48" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="96" t="n">
+      <c r="G14" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="I14" s="48" t="n">
         <v>9998</v>
       </c>
-      <c r="J14" s="48" t="n">
+      <c r="J14" s="50" t="n">
         <v>9998</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="B15" s="53" t="n">
+      <c r="A15" s="93" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="54" t="n">
+      <c r="C15" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="54" t="n">
+      <c r="D15" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="54" t="n">
+      <c r="E15" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="54" t="n">
+      <c r="F15" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="98" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="48" t="n">
+      <c r="G15" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="55" t="n">
         <v>9995</v>
       </c>
-      <c r="J15" s="48" t="n">
+      <c r="J15" s="58" t="n">
         <v>9995</v>
       </c>
     </row>
@@ -5789,7 +6109,7 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="56"/>
+      <c r="E18" s="59"/>
       <c r="F18" s="47"/>
       <c r="G18" s="47"/>
     </row>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,15 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="CIC18" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Scripts-CIC17" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="CIC17" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Scripts-BCCC17" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="BCCC17" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Análisis estadístico CIC18" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Scripts-CIC17" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="CIC17" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Análisis estadístico CIC17" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Scripts-BCCC17" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="BCCC17" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="249">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -561,6 +563,17 @@
     <t xml:space="preserve">COLUMNAS:</t>
   </si>
   <si>
+    <t xml:space="preserve">CIC18__clean_dataset_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza inicial de los datos:
+- duplicados
+- nulos
+- tipos
+- codificación categórica
+- columnas problemáticas</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARPETA MODELOS GENERADOS</t>
   </si>
   <si>
@@ -957,6 +970,38 @@
   </si>
   <si>
     <t xml:space="preserve">Heartbleed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__clean_dataset_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__cleanning__v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__cleanning__v1__split_dataset__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split estratificado 80/20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__split__v1__train
+CIC17__split__v1__test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__split__v1__scale__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalizar y escalar los datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__scaled__v1__train
+CIC17__scaled__v1__test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__scaled__v1__pca_analisis__v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis del dataset usando PCA. ¿Cuántas características reales tiene el dataset?</t>
   </si>
   <si>
     <t xml:space="preserve">MODELOS GENERADOS</t>
@@ -1621,7 +1666,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="105">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1770,6 +1815,26 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1778,18 +1843,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1862,6 +1915,18 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1910,6 +1975,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1918,10 +1987,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1964,6 +2029,30 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2553,38 +2642,38 @@
       <c r="F18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39" t="s">
+      <c r="E19" s="15"/>
+      <c r="F19" s="23" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26"/>
@@ -2602,7 +2691,7 @@
       <c r="E22" s="41"/>
       <c r="F22" s="31"/>
     </row>
-    <row r="23" customFormat="false" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" s="2" customFormat="true" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
         <v>57</v>
       </c>
@@ -2620,7 +2709,7 @@
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" customFormat="false" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" s="2" customFormat="true" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
         <v>57</v>
       </c>
@@ -2639,19 +2728,19 @@
       <c r="F24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="38"/>
+      <c r="E25" s="43"/>
       <c r="F25" s="39" t="s">
         <v>65</v>
       </c>
@@ -2680,15 +2769,17 @@
       <c r="E27" s="27"/>
       <c r="F27" s="28"/>
     </row>
-    <row r="28" s="2" customFormat="true" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29"/>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
       <c r="D28" s="30"/>
       <c r="E28" s="30"/>
       <c r="F28" s="31"/>
-    </row>
-    <row r="29" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
         <v>68</v>
       </c>
@@ -2705,6 +2796,8 @@
         <v>71</v>
       </c>
       <c r="F29" s="34"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="35" t="s">
@@ -2727,19 +2820,19 @@
       <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="38"/>
+      <c r="E31" s="43"/>
       <c r="F31" s="39" t="s">
         <v>76</v>
       </c>
@@ -2760,7 +2853,7 @@
       <c r="E32" s="27"/>
       <c r="F32" s="28"/>
     </row>
-    <row r="33" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26"/>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
@@ -2808,575 +2901,576 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.21"/>
   </cols>
   <sheetData>
-    <row r="1" s="45" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="47" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="J1" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="46" t="s">
         <v>68</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="47" t="n">
+      <c r="B2" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="n">
+      <c r="C2" s="50" t="n">
         <v>13484658</v>
       </c>
-      <c r="D2" s="48" t="n">
+      <c r="D2" s="50" t="n">
         <v>13445443</v>
       </c>
-      <c r="E2" s="48" t="n">
+      <c r="E2" s="50" t="n">
         <v>450000</v>
       </c>
-      <c r="F2" s="48" t="n">
+      <c r="F2" s="50" t="n">
         <v>360000</v>
       </c>
-      <c r="G2" s="48" t="n">
+      <c r="G2" s="50" t="n">
         <v>339865</v>
       </c>
-      <c r="H2" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" s="50" t="n">
+      <c r="H2" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="XFD2" s="2"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="47" t="n">
+      <c r="B3" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="48" t="n">
+      <c r="C3" s="50" t="n">
         <v>686012</v>
       </c>
-      <c r="D3" s="48" t="n">
+      <c r="D3" s="50" t="n">
         <v>668461</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="50" t="n">
         <v>450000</v>
       </c>
-      <c r="F3" s="48" t="n">
+      <c r="F3" s="50" t="n">
         <v>360000</v>
       </c>
-      <c r="G3" s="48" t="n">
+      <c r="G3" s="50" t="n">
         <v>359280</v>
       </c>
-      <c r="H3" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="48" t="n">
+      <c r="H3" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="50" t="n">
         <v>9840</v>
       </c>
-      <c r="K3" s="50" t="n">
+      <c r="K3" s="52" t="n">
         <v>9993</v>
       </c>
       <c r="XFD3" s="2"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="47" t="n">
+      <c r="B4" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="50" t="n">
         <v>576191</v>
       </c>
-      <c r="D4" s="48" t="n">
+      <c r="D4" s="50" t="n">
         <v>576175</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="50" t="n">
         <v>450000</v>
       </c>
-      <c r="F4" s="48" t="n">
+      <c r="F4" s="50" t="n">
         <v>360000</v>
       </c>
-      <c r="G4" s="48" t="n">
+      <c r="G4" s="50" t="n">
         <v>359369</v>
       </c>
-      <c r="H4" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="48" t="n">
+      <c r="H4" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="50" t="n">
         <v>9974</v>
       </c>
-      <c r="K4" s="50" t="n">
+      <c r="K4" s="52" t="n">
         <v>9968</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="50" t="n">
         <v>461912</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="50" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="54" t="n">
         <v>434873</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="50" t="n">
         <v>347898</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G5" s="50" t="n">
         <v>346118</v>
       </c>
-      <c r="H5" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="48" t="n">
+      <c r="H5" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="50" t="n">
         <v>9855</v>
       </c>
-      <c r="K5" s="50" t="n">
+      <c r="K5" s="52" t="n">
         <v>9914</v>
       </c>
       <c r="XFD5" s="2"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="50" t="n">
         <v>286191</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="50" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="54" t="n">
         <v>282310</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="50" t="n">
         <v>225848</v>
       </c>
-      <c r="G6" s="48" t="n">
+      <c r="G6" s="50" t="n">
         <v>225602</v>
       </c>
-      <c r="H6" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="48" t="n">
+      <c r="H6" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="50" t="n">
         <v>9971</v>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="XFD6" s="2"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="50" t="n">
         <v>161934</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="50" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="54" t="n">
         <v>161897</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="50" t="n">
         <v>129517</v>
       </c>
-      <c r="G7" s="48" t="n">
+      <c r="G7" s="50" t="n">
         <v>108526</v>
       </c>
-      <c r="H7" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="48" t="n">
+      <c r="H7" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="50" t="n">
         <v>8820</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="52" t="n">
         <v>9998</v>
       </c>
       <c r="XFD7" s="2"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="50" t="n">
         <v>187589</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="50" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="54" t="n">
         <v>117322</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="50" t="n">
         <v>93857</v>
       </c>
-      <c r="G8" s="48" t="n">
+      <c r="G8" s="50" t="n">
         <v>93112</v>
       </c>
-      <c r="H8" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="48" t="n">
+      <c r="H8" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="50" t="n">
         <v>9896</v>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="52" t="n">
         <v>9967</v>
       </c>
       <c r="XFD8" s="2"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="50" t="n">
         <v>41508</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="50" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="54" t="n">
         <v>41455</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="50" t="n">
         <v>33164</v>
       </c>
-      <c r="G9" s="48" t="n">
+      <c r="G9" s="50" t="n">
         <v>31187</v>
       </c>
-      <c r="H9" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="48" t="n">
+      <c r="H9" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="50" t="n">
         <v>9533</v>
       </c>
-      <c r="K9" s="50" t="n">
+      <c r="K9" s="52" t="n">
         <v>9974</v>
       </c>
       <c r="XFD9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="50" t="n">
         <v>193360</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="50" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="54" t="n">
         <v>39352</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="50" t="n">
         <v>31482</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G10" s="50" t="n">
         <v>31432</v>
       </c>
-      <c r="H10" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="48" t="n">
+      <c r="H10" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="50" t="n">
         <v>9986</v>
       </c>
-      <c r="K10" s="50" t="n">
+      <c r="K10" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="XFD10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="50" t="n">
         <v>139890</v>
       </c>
-      <c r="D11" s="48" t="n">
+      <c r="D11" s="50" t="n">
         <v>19462</v>
       </c>
-      <c r="E11" s="52" t="n">
+      <c r="E11" s="54" t="n">
         <v>19462</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="50" t="n">
         <v>15570</v>
       </c>
-      <c r="G11" s="48" t="n">
+      <c r="G11" s="50" t="n">
         <v>15570</v>
       </c>
-      <c r="H11" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K11" s="50" t="n">
+      <c r="H11" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="XFD11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="50" t="n">
         <v>10990</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="50" t="n">
         <v>10285</v>
       </c>
-      <c r="E12" s="52" t="n">
+      <c r="E12" s="54" t="n">
         <v>10285</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="50" t="n">
         <v>8228</v>
       </c>
-      <c r="G12" s="48" t="n">
+      <c r="G12" s="50" t="n">
         <v>7975</v>
       </c>
-      <c r="H12" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="48" t="n">
+      <c r="H12" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="50" t="n">
         <v>9838</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="52" t="n">
         <v>9939</v>
       </c>
       <c r="XFD12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="50" t="n">
         <v>1730</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="50" t="n">
         <v>1730</v>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="54" t="n">
         <v>1730</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="50" t="n">
         <v>1384</v>
       </c>
-      <c r="G13" s="48" t="n">
+      <c r="G13" s="50" t="n">
         <v>1378</v>
       </c>
-      <c r="H13" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="50" t="n">
+      <c r="H13" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="52" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="50" t="n">
         <v>611</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="50" t="n">
         <v>611</v>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E14" s="54" t="n">
         <v>611</v>
       </c>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="50" t="n">
         <v>489</v>
       </c>
-      <c r="G14" s="48" t="n">
+      <c r="G14" s="50" t="n">
         <v>211</v>
       </c>
-      <c r="H14" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="48" t="n">
+      <c r="H14" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="50" t="n">
         <v>9624</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="52" t="n">
         <v>9593</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="50" t="n">
         <v>230</v>
       </c>
-      <c r="D15" s="48" t="n">
+      <c r="D15" s="50" t="n">
         <v>230</v>
       </c>
-      <c r="E15" s="52" t="n">
+      <c r="E15" s="54" t="n">
         <v>230</v>
       </c>
-      <c r="F15" s="48" t="n">
+      <c r="F15" s="50" t="n">
         <v>184</v>
       </c>
-      <c r="G15" s="48" t="n">
+      <c r="G15" s="50" t="n">
         <v>66</v>
       </c>
-      <c r="H15" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="48" t="n">
+      <c r="H15" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="50" t="n">
         <v>9673</v>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="52" t="n">
         <v>9655</v>
       </c>
+      <c r="XFD15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="54" t="n">
+      <c r="B16" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="55" t="n">
+      <c r="C16" s="57" t="n">
         <v>87</v>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="57" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="57" t="n">
         <v>87</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="56" t="n">
+      <c r="G16" s="58" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="55" t="n">
+      <c r="H16" s="59" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="59" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="57" t="n">
         <v>9987</v>
       </c>
-      <c r="K16" s="58" t="n">
+      <c r="K16" s="60" t="n">
         <v>9986</v>
       </c>
     </row>
@@ -3419,18 +3513,18 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="59"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="49"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="48"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="50"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="59"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="49"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -3451,23 +3545,23 @@
       <c r="G20" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="50" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="50" t="n">
         <v>56</v>
       </c>
       <c r="XFD20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="3"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3"/>
@@ -3503,25 +3597,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="92.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="68.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="45.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="52.63"/>
   </cols>
   <sheetData>
-    <row r="1" s="65" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -3530,610 +3623,27 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="63" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-    </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6"/>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-    </row>
-    <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-    </row>
-    <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="68"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-    </row>
-    <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="68"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-    </row>
-    <row r="6" customFormat="false" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-    </row>
-    <row r="7" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="66"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-    </row>
-    <row r="9" customFormat="false" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="66"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-    </row>
-    <row r="10" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-    </row>
-    <row r="11" s="2" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="71"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-    </row>
-    <row r="12" s="2" customFormat="true" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-    </row>
-    <row r="13" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-    </row>
-    <row r="14" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-    </row>
-    <row r="15" s="2" customFormat="true" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-    </row>
-    <row r="16" s="74" customFormat="true" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="34"/>
-    </row>
-    <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="36"/>
-    </row>
-    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="73" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="73" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="28"/>
-    </row>
-    <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="72"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="28"/>
-    </row>
-    <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-    </row>
-    <row r="22" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="F22" s="70"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-    </row>
-    <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F23" s="71"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-    </row>
-    <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-    </row>
-    <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="73" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>144</v>
-      </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-    </row>
-    <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="72"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-    </row>
-    <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-    </row>
-    <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-    </row>
-    <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="36"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-    </row>
-    <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-    </row>
-    <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="73" t="s">
-        <v>153</v>
-      </c>
-      <c r="C31" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="73" t="s">
-        <v>154</v>
-      </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-    </row>
-    <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="72"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-    </row>
-    <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-    </row>
-    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
-    </row>
-    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
-    </row>
-    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-    </row>
-    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-    </row>
-    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-    </row>
-    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-    </row>
-    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-    </row>
-    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-    </row>
-    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-    </row>
-    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
-    </row>
-    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="67"/>
-      <c r="H44" s="67"/>
-    </row>
-    <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="67"/>
-      <c r="H45" s="67"/>
-    </row>
-    <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="67"/>
-      <c r="H46" s="67"/>
-    </row>
-    <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-    </row>
-    <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="67"/>
-      <c r="H48" s="67"/>
-    </row>
-    <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-    </row>
-    <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="67"/>
-      <c r="H50" s="67"/>
-    </row>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -4146,6 +3656,655 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="65" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="66" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="65" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="65" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="70" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+    </row>
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6"/>
+      <c r="B2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="71"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+    </row>
+    <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6"/>
+      <c r="B3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="73"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+    </row>
+    <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6"/>
+      <c r="B4" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="73"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+    </row>
+    <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="73"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+    </row>
+    <row r="6" s="2" customFormat="true" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="73"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+    </row>
+    <row r="7" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="71"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" s="2" customFormat="true" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="71"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+    </row>
+    <row r="9" s="2" customFormat="true" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="71"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+    </row>
+    <row r="10" s="2" customFormat="true" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="75"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+    </row>
+    <row r="11" s="77" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="76"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+    </row>
+    <row r="12" customFormat="false" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+    </row>
+    <row r="13" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+    </row>
+    <row r="14" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="78"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+    </row>
+    <row r="15" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+    </row>
+    <row r="16" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+    </row>
+    <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="36"/>
+    </row>
+    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="43"/>
+      <c r="F18" s="39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="79"/>
+      <c r="F19" s="28"/>
+    </row>
+    <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="78"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+    </row>
+    <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="76"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+    </row>
+    <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="43"/>
+      <c r="F24" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+    </row>
+    <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="79"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+    </row>
+    <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="78"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+    </row>
+    <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+    </row>
+    <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+    </row>
+    <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="36"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+    </row>
+    <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="43"/>
+      <c r="F30" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+    </row>
+    <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="79" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="E31" s="79"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+    </row>
+    <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="78"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+    </row>
+    <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G37" s="72"/>
+      <c r="H37" s="72"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G38" s="72"/>
+      <c r="H38" s="72"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G39" s="72"/>
+      <c r="H39" s="72"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G41" s="72"/>
+      <c r="H41" s="72"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G43" s="72"/>
+      <c r="H43" s="72"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G44" s="72"/>
+      <c r="H44" s="72"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G45" s="72"/>
+      <c r="H45" s="72"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G46" s="72"/>
+      <c r="H46" s="72"/>
+    </row>
+    <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G47" s="72"/>
+      <c r="H47" s="72"/>
+    </row>
+    <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G48" s="72"/>
+      <c r="H48" s="72"/>
+    </row>
+    <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G49" s="72"/>
+      <c r="H49" s="72"/>
+    </row>
+    <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G50" s="72"/>
+      <c r="H50" s="72"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4164,531 +4323,531 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="80" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="85" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="78" t="s">
+      <c r="I1" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="78" t="s">
+      <c r="J1" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="79"/>
+      <c r="K1" s="84"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="82" t="n">
+      <c r="B2" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="82" t="n">
+      <c r="C2" s="87" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="83" t="n">
+      <c r="D2" s="88" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="48" t="n">
+      <c r="E2" s="50" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="52" t="n">
+      <c r="F2" s="54" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="50" t="n">
+      <c r="G2" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="81" t="s">
-        <v>157</v>
-      </c>
-      <c r="B3" s="82" t="n">
+      <c r="A3" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="82" t="n">
+      <c r="C3" s="87" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="83" t="n">
+      <c r="D3" s="88" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="50" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="52" t="n">
+      <c r="F3" s="54" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="48" t="n">
+      <c r="G3" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="50" t="n">
         <v>9656</v>
       </c>
-      <c r="J3" s="50" t="n">
+      <c r="J3" s="52" t="n">
         <v>9968</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="81" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="82" t="n">
+      <c r="A4" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="82" t="n">
+      <c r="C4" s="87" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="83" t="n">
+      <c r="D4" s="88" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="50" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="52" t="n">
+      <c r="F4" s="54" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="48" t="n">
+      <c r="G4" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="50" t="n">
         <v>9765</v>
       </c>
-      <c r="J4" s="50" t="n">
+      <c r="J4" s="52" t="n">
         <v>9995</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="82" t="n">
+      <c r="A5" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="82" t="n">
+      <c r="C5" s="87" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="83" t="n">
+      <c r="D5" s="88" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="50" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="54" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="48" t="n">
+      <c r="G5" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="50" t="n">
         <v>9712</v>
       </c>
-      <c r="J5" s="50" t="n">
+      <c r="J5" s="52" t="n">
         <v>9960</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="82" t="n">
+      <c r="A6" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="82" t="n">
+      <c r="C6" s="87" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="83" t="n">
+      <c r="D6" s="88" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="50" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="52" t="n">
+      <c r="F6" s="54" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="48" t="n">
+      <c r="G6" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="50" t="n">
         <v>9913</v>
       </c>
-      <c r="J6" s="50" t="n">
+      <c r="J6" s="52" t="n">
         <v>9958</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="81" t="s">
-        <v>161</v>
-      </c>
-      <c r="B7" s="82" t="n">
+      <c r="A7" s="86" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="82" t="n">
+      <c r="C7" s="87" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="83" t="n">
+      <c r="D7" s="88" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="50" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="54" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="48" t="n">
+      <c r="G7" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="50" t="n">
         <v>9908</v>
       </c>
-      <c r="J7" s="50" t="n">
+      <c r="J7" s="52" t="n">
         <v>9923</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="81" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="82" t="n">
+      <c r="A8" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="82" t="n">
+      <c r="C8" s="87" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="83" t="n">
+      <c r="D8" s="88" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="50" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="52" t="n">
+      <c r="F8" s="54" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="48" t="n">
+      <c r="G8" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="50" t="n">
         <v>9637</v>
       </c>
-      <c r="J8" s="50" t="n">
+      <c r="J8" s="52" t="n">
         <v>9785</v>
       </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="82" t="n">
+      <c r="A9" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="82" t="n">
+      <c r="C9" s="87" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="83" t="n">
+      <c r="D9" s="88" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="50" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="54" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="48" t="n">
+      <c r="G9" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="50" t="n">
         <v>9814</v>
       </c>
-      <c r="J9" s="50" t="n">
+      <c r="J9" s="52" t="n">
         <v>9872</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="82" t="n">
+      <c r="A10" s="86" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="82" t="n">
+      <c r="C10" s="87" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="83" t="n">
+      <c r="D10" s="88" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="50" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="54" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="48" t="n">
+      <c r="G10" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="50" t="n">
         <v>9622</v>
       </c>
-      <c r="J10" s="50" t="n">
+      <c r="J10" s="52" t="n">
         <v>9637</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="82" t="n">
+      <c r="B11" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="82" t="n">
+      <c r="C11" s="87" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="83" t="n">
+      <c r="D11" s="88" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="50" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="52" t="n">
+      <c r="F11" s="54" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="48" t="n">
+      <c r="G11" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="50" t="n">
         <v>9832</v>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="52" t="n">
         <v>9979</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="81" t="s">
-        <v>165</v>
-      </c>
-      <c r="B12" s="82" t="n">
+      <c r="A12" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="82" t="n">
+      <c r="C12" s="87" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="83" t="n">
+      <c r="D12" s="88" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="50" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="54" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="48" t="n">
+      <c r="G12" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="50" t="n">
         <v>5782</v>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="52" t="n">
         <v>5793</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="81" t="s">
-        <v>166</v>
-      </c>
-      <c r="B13" s="82" t="n">
+      <c r="A13" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="82" t="n">
+      <c r="C13" s="87" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="83" t="n">
+      <c r="D13" s="88" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="50" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="54" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="48" t="n">
+      <c r="G13" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="50" t="n">
         <v>5862</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="52" t="n">
         <v>5871</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="81" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="82" t="n">
+      <c r="A14" s="86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="82" t="n">
+      <c r="C14" s="87" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="83" t="n">
+      <c r="D14" s="88" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="48" t="n">
+      <c r="E14" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="48" t="n">
+      <c r="G14" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="50" t="n">
         <v>9904</v>
       </c>
-      <c r="J14" s="50" t="n">
+      <c r="J14" s="52" t="n">
         <v>9934</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="81" t="s">
-        <v>168</v>
-      </c>
-      <c r="B15" s="82" t="n">
+      <c r="A15" s="86" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="82" t="n">
+      <c r="C15" s="87" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="83" t="n">
+      <c r="D15" s="88" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="48" t="n">
+      <c r="E15" s="50" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="48" t="n">
+      <c r="G15" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="50" t="n">
         <v>9725</v>
       </c>
-      <c r="J15" s="50" t="n">
+      <c r="J15" s="52" t="n">
         <v>9727</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="84" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="85" t="n">
+      <c r="A16" s="89" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="90" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="85" t="n">
+      <c r="C16" s="90" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="85" t="n">
+      <c r="D16" s="90" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="58" t="n">
+      <c r="G16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="60" t="n">
         <v>10000</v>
       </c>
       <c r="L16" s="2"/>
@@ -4729,23 +4888,23 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="59"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="49"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="59"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="49"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="84" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="48" t="n">
+      <c r="D20" s="50" t="n">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -4763,54 +4922,54 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="48"/>
+      <c r="B21" s="50"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="48"/>
+      <c r="B22" s="50"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="48"/>
+      <c r="B23" s="50"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="48"/>
+      <c r="B24" s="50"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="48"/>
+      <c r="B25" s="50"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="48"/>
+      <c r="B26" s="50"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="48"/>
+      <c r="B27" s="50"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="48"/>
+      <c r="B28" s="50"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="48"/>
+      <c r="B29" s="50"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="48"/>
+      <c r="B30" s="50"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="48"/>
+      <c r="B31" s="50"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="48"/>
+      <c r="B32" s="50"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="48"/>
+      <c r="B33" s="50"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="48"/>
+      <c r="B34" s="50"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="48"/>
+      <c r="B35" s="50"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4823,7 +4982,108 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="91" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="91" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="91" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="91" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="91" width="52.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="92" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="92" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="92" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="93"/>
+      <c r="B2" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="95" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="94"/>
+      <c r="B3" s="94" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="94" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="95" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="95" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="94"/>
+      <c r="B4" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="94" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="95" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="96"/>
+      <c r="B5" s="96" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="96"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4856,13 +5116,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
+        <v>182</v>
+      </c>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
@@ -4871,502 +5131,502 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-    </row>
-    <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+    </row>
+    <row r="6" s="2" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-    </row>
-    <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+    </row>
+    <row r="7" s="2" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" s="2" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-    </row>
-    <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+    </row>
+    <row r="9" s="2" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-    </row>
-    <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+    </row>
+    <row r="10" s="2" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="69" t="s">
-        <v>186</v>
+      <c r="B10" s="74" t="s">
+        <v>198</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="86"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-    </row>
-    <row r="11" s="2" customFormat="true" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>199</v>
+      </c>
+      <c r="F10" s="97"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+    </row>
+    <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F11" s="22"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-    </row>
-    <row r="12" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+    </row>
+    <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-    </row>
-    <row r="13" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>204</v>
+      </c>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+    </row>
+    <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-    </row>
-    <row r="14" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+    </row>
+    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="78"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-    </row>
-    <row r="15" s="2" customFormat="true" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+    </row>
+    <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F17" s="23"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="B18" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="38"/>
+      <c r="D18" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="43"/>
       <c r="F18" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
+        <v>214</v>
+      </c>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="73" t="s">
+      <c r="B19" s="79" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>204</v>
-      </c>
-      <c r="E19" s="73"/>
+      <c r="D19" s="79" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" s="79"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="72"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
       <c r="F20" s="28"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="87"/>
-      <c r="B21" s="88"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="69" t="s">
-        <v>205</v>
+      <c r="B22" s="74" t="s">
+        <v>217</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="F22" s="86"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
+        <v>218</v>
+      </c>
+      <c r="F22" s="97"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F23" s="22"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="C24" s="38" t="s">
+      <c r="B24" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="38"/>
+      <c r="D24" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="43"/>
       <c r="F24" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="67"/>
+        <v>223</v>
+      </c>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="72" t="s">
+      <c r="A25" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="73" t="s">
-        <v>212</v>
-      </c>
-      <c r="C25" s="73" t="s">
+      <c r="B25" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="73" t="s">
-        <v>213</v>
-      </c>
-      <c r="E25" s="73"/>
+      <c r="D25" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" s="79"/>
       <c r="F25" s="28"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="72"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="67"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -5375,190 +5635,190 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F29" s="23"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="67"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="38" t="s">
+      <c r="B30" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="E30" s="38"/>
+      <c r="D30" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="43"/>
       <c r="F30" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
+        <v>233</v>
+      </c>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="72" t="s">
+      <c r="A31" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="73" t="s">
+      <c r="B31" s="79" t="s">
+        <v>234</v>
+      </c>
+      <c r="C31" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="73" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="73"/>
+      <c r="D31" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" s="79"/>
       <c r="F31" s="28"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="72"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="67"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-      <c r="I33" s="67"/>
-      <c r="J33" s="67"/>
-      <c r="K33" s="67"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="101"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="67"/>
-      <c r="J34" s="67"/>
-      <c r="K34" s="67"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="67"/>
-      <c r="J35" s="67"/>
-      <c r="K35" s="67"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="72"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="67"/>
+      <c r="G37" s="72"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="72"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="72"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="72"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="72"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="67"/>
-      <c r="K42" s="67"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="72"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5571,7 +5831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5590,484 +5850,484 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="92" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="103" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="43" t="s">
-        <v>225</v>
-      </c>
-      <c r="F1" s="43" t="s">
+      <c r="E1" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="46" t="s">
         <v>68</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="47" t="n">
+      <c r="A2" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="n">
+      <c r="C2" s="50" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="52" t="n">
+      <c r="D2" s="54" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="48" t="n">
+      <c r="E2" s="50" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="52" t="n">
+      <c r="F2" s="54" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="50" t="n">
+      <c r="G2" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="52" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="B3" s="47" t="n">
+      <c r="A3" s="48" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="48" t="n">
+      <c r="C3" s="50" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="52" t="n">
+      <c r="D3" s="54" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="50" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="52" t="n">
+      <c r="F3" s="54" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="48" t="n">
+      <c r="G3" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="50" t="n">
         <v>9549</v>
       </c>
-      <c r="J3" s="50" t="n">
+      <c r="J3" s="52" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="B4" s="47" t="n">
+      <c r="A4" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="50" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="52" t="n">
+      <c r="D4" s="54" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="50" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="52" t="n">
+      <c r="F4" s="54" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="48" t="n">
+      <c r="G4" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="50" t="n">
         <v>9994</v>
       </c>
-      <c r="J4" s="50" t="n">
+      <c r="J4" s="52" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="47" t="n">
+      <c r="A5" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="50" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="54" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="50" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="54" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="48" t="n">
+      <c r="G5" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="50" t="n">
         <v>9593</v>
       </c>
-      <c r="J5" s="50" t="n">
+      <c r="J5" s="52" t="n">
         <v>9989</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="47" t="n">
+      <c r="A6" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="50" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="54" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="50" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="52" t="n">
+      <c r="F6" s="54" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="48" t="n">
+      <c r="G6" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="50" t="n">
         <v>9990</v>
       </c>
-      <c r="J6" s="50" t="n">
+      <c r="J6" s="52" t="n">
         <v>9999</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="47" t="n">
+      <c r="A7" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="50" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="54" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="50" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="54" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="48" t="n">
+      <c r="G7" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="50" t="n">
         <v>9781</v>
       </c>
-      <c r="J7" s="50" t="n">
+      <c r="J7" s="52" t="n">
         <v>9944</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="47" t="n">
+      <c r="A8" s="48" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="50" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="54" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="50" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="52" t="n">
+      <c r="F8" s="54" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="48" t="n">
+      <c r="G8" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="50" t="n">
         <v>9873</v>
       </c>
-      <c r="J8" s="50" t="n">
+      <c r="J8" s="52" t="n">
         <v>9880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="47" t="n">
+      <c r="A9" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="50" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="54" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="50" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="54" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="48" t="n">
+      <c r="G9" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="50" t="n">
         <v>9983</v>
       </c>
-      <c r="J9" s="50" t="n">
+      <c r="J9" s="52" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="47" t="n">
+      <c r="A10" s="48" t="s">
+        <v>244</v>
+      </c>
+      <c r="B10" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="50" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="54" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="50" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="54" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="48" t="n">
+      <c r="G10" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="50" t="n">
         <v>9995</v>
       </c>
-      <c r="J10" s="50" t="n">
+      <c r="J10" s="52" t="n">
         <v>9995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" s="47" t="n">
+      <c r="A11" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="50" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="54" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="50" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="52" t="n">
+      <c r="F11" s="54" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="48" t="n">
+      <c r="G11" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="50" t="n">
         <v>9868</v>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="52" t="n">
         <v>9881</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="B12" s="47" t="n">
+      <c r="A12" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="50" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="52" t="n">
+      <c r="D12" s="54" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="50" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="54" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="48" t="n">
+      <c r="G12" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="50" t="n">
         <v>9971</v>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="52" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="B13" s="47" t="n">
+      <c r="A13" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="50" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="54" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="50" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="54" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="48" t="n">
+      <c r="G13" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="50" t="n">
         <v>9971</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="52" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="47" t="n">
+      <c r="A14" s="48" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="50" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="54" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="48" t="n">
+      <c r="E14" s="50" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="52" t="n">
+      <c r="F14" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="48" t="n">
+      <c r="G14" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="50" t="n">
         <v>9998</v>
       </c>
-      <c r="J14" s="50" t="n">
+      <c r="J14" s="52" t="n">
         <v>9998</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="93" t="s">
-        <v>169</v>
-      </c>
-      <c r="B15" s="54" t="n">
+      <c r="A15" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="56" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="55" t="n">
+      <c r="C15" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="55" t="n">
+      <c r="D15" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="55" t="n">
+      <c r="G15" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="59" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="57" t="n">
         <v>9995</v>
       </c>
-      <c r="J15" s="58" t="n">
+      <c r="J15" s="60" t="n">
         <v>9995</v>
       </c>
     </row>
@@ -6109,9 +6369,9 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="59"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
@@ -6120,13 +6380,13 @@
       <c r="C19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="48" t="n">
+      <c r="D19" s="50" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="49" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="49" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -6138,7 +6398,7 @@
       <c r="I19" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="48"/>
+      <c r="J34" s="50"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,7 @@
     <sheet name="Análisis estadístico CIC17" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Scripts-BCCC17" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="BCCC17" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Análisis estadístico BCCC17" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="265">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -574,6 +575,35 @@
 - columnas problemáticas</t>
   </si>
   <si>
+    <t xml:space="preserve">CIC18__cleanning__v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__cleanning__v1__split_dataset__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split estratificado 80/20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__split__v1__train
+CIC18__split__v1__test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__split__v1__scale__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalizar y escalar los datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__scaled__v1__train
+CIC18__scaled__v1__test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC18__scaled__v1__pca_analisis__v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis del dataset usando PCA. ¿Cuántas características reales tiene el dataset?</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARPETA MODELOS GENERADOS</t>
   </si>
   <si>
@@ -981,9 +1011,6 @@
     <t xml:space="preserve">CIC17__cleanning__v1__split_dataset__v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">Split estratificado 80/20.</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIC17__split__v1__train
 CIC17__split__v1__test</t>
   </si>
@@ -991,17 +1018,11 @@
     <t xml:space="preserve">CIC17__split__v1__scale__v1.ipynb</t>
   </si>
   <si>
-    <t xml:space="preserve">Normalizar y escalar los datos</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIC17__scaled__v1__train
 CIC17__scaled__v1__test</t>
   </si>
   <si>
     <t xml:space="preserve">CIC17__scaled__v1__pca_analisis__v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análisis del dataset usando PCA. ¿Cuántas características reales tiene el dataset?</t>
   </si>
   <si>
     <t xml:space="preserve">MODELOS GENERADOS</t>
@@ -1396,6 +1417,43 @@
   </si>
   <si>
     <t xml:space="preserve">Web_SQL_Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__clean_dataset_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__cleanning__v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__cleanning__v1__split_dataset__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__split__v1__train
+BCCC17__split__v1__test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__split__v1__scale__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__scaled__v1__train
+BCCC17__scaled__v1__test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__scaled__v1__pca_analisis__v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__clean_dataset_v2.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza inicial de los datos:
+- duplicados
+- nulos
+- tipos
+- codificación NORMAL NO CATEGÓRICA
+- columnas problemáticas (TIMESTAMP INCLUIDO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCCC17__cleanning__v2</t>
   </si>
 </sst>
 </file>
@@ -1915,12 +1973,32 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2032,26 +2110,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3608,36 +3666,79 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="64" t="s">
-        <v>9</v>
-      </c>
+      <c r="E2" s="65" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="66"/>
+      <c r="B3" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="68"/>
+      <c r="B4" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="68"/>
+      <c r="B5" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="68"/>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3664,21 +3765,21 @@
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="65" width="92.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="66" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="65" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="65" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="70" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="71" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="70" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="70" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="70" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="75" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="72" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -3687,119 +3788,119 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="F1" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="10" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="10" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="73"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+        <v>117</v>
+      </c>
+      <c r="F3" s="78"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="10" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="10" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
     </row>
     <row r="6" s="2" customFormat="true" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="73"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
+        <v>121</v>
+      </c>
+      <c r="F6" s="78"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
     </row>
     <row r="7" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="71"/>
+        <v>123</v>
+      </c>
+      <c r="F7" s="76"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
@@ -3808,128 +3909,128 @@
         <v>27</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="71"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
+        <v>125</v>
+      </c>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="71"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
+        <v>127</v>
+      </c>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="74" t="s">
-        <v>119</v>
+      <c r="B10" s="79" t="s">
+        <v>128</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" s="75"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-    </row>
-    <row r="11" s="77" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+      <c r="F10" s="80"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+    </row>
+    <row r="11" s="82" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="76"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
+        <v>131</v>
+      </c>
+      <c r="F11" s="81"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" customFormat="false" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
+        <v>134</v>
+      </c>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
     </row>
     <row r="13" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
     </row>
     <row r="14" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
@@ -3938,44 +4039,44 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
     </row>
     <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F17" s="36"/>
     </row>
@@ -3984,41 +4085,41 @@
         <v>46</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E18" s="43"/>
       <c r="F18" s="39" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="79" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="79" t="s">
+      <c r="B19" s="84" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19" s="79"/>
+      <c r="D19" s="84" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="84"/>
       <c r="F19" s="28"/>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
       <c r="F20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4033,89 +4134,89 @@
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="74" t="s">
-        <v>138</v>
+      <c r="B22" s="79" t="s">
+        <v>147</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" s="75"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
+        <v>148</v>
+      </c>
+      <c r="F22" s="80"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
     </row>
     <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F23" s="76"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
+        <v>150</v>
+      </c>
+      <c r="F23" s="81"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
     </row>
     <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C24" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
+        <v>153</v>
+      </c>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="79" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="79" t="s">
+      <c r="B25" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25" s="79"/>
+      <c r="D25" s="84" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="84"/>
       <c r="F25" s="28"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="78"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
+      <c r="A26" s="83"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -4124,174 +4225,174 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="35" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F29" s="36"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="42" t="s">
         <v>68</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C30" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E30" s="43"/>
       <c r="F30" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
+        <v>163</v>
+      </c>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="79" t="s">
+      <c r="B31" s="84" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="79" t="s">
-        <v>156</v>
-      </c>
-      <c r="E31" s="79"/>
+      <c r="D31" s="84" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" s="84"/>
       <c r="F31" s="28"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="78"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
     </row>
     <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="80"/>
+      <c r="B33" s="85"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="72"/>
-      <c r="H43" s="72"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="72"/>
-      <c r="H45" s="72"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="77"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="72"/>
-      <c r="H46" s="72"/>
+      <c r="G46" s="77"/>
+      <c r="H46" s="77"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="72"/>
-      <c r="H47" s="72"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="72"/>
-      <c r="H48" s="72"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="72"/>
-      <c r="H49" s="72"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="77"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="72"/>
-      <c r="H50" s="72"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4323,7 +4424,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="85" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="90" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
         <v>79</v>
       </c>
@@ -4331,43 +4432,43 @@
         <v>80</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D1" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="82" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="82" t="s">
+      <c r="E1" s="87" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="83" t="s">
+      <c r="G1" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="83" t="s">
+      <c r="H1" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="83" t="s">
+      <c r="J1" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="84"/>
+      <c r="K1" s="89"/>
       <c r="XFD1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="86" t="s">
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="87" t="n">
+      <c r="B2" s="92" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="87" t="n">
+      <c r="C2" s="92" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="88" t="n">
+      <c r="D2" s="93" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="50" t="n">
@@ -4390,17 +4491,17 @@
       </c>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="86" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="87" t="n">
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="91" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="87" t="n">
+      <c r="C3" s="92" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="88" t="n">
+      <c r="D3" s="93" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="50" t="n">
@@ -4423,17 +4524,17 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="86" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="87" t="n">
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="87" t="n">
+      <c r="C4" s="92" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="88" t="n">
+      <c r="D4" s="93" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="50" t="n">
@@ -4456,17 +4557,17 @@
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="86" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" s="87" t="n">
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="87" t="n">
+      <c r="C5" s="92" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="88" t="n">
+      <c r="D5" s="93" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="50" t="n">
@@ -4489,17 +4590,17 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="86" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="87" t="n">
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="91" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="92" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="87" t="n">
+      <c r="C6" s="92" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="88" t="n">
+      <c r="D6" s="93" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="50" t="n">
@@ -4522,17 +4623,17 @@
       </c>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="86" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="87" t="n">
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="91" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="92" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="87" t="n">
+      <c r="C7" s="92" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="88" t="n">
+      <c r="D7" s="93" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="50" t="n">
@@ -4555,17 +4656,17 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="86" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="87" t="n">
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="91" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="92" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="87" t="n">
+      <c r="C8" s="92" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="88" t="n">
+      <c r="D8" s="93" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="50" t="n">
@@ -4588,17 +4689,17 @@
       </c>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="86" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="87" t="n">
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="91" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="92" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="87" t="n">
+      <c r="C9" s="92" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="88" t="n">
+      <c r="D9" s="93" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="50" t="n">
@@ -4621,17 +4722,17 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="86" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="87" t="n">
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="91" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="92" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="87" t="n">
+      <c r="C10" s="92" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="88" t="n">
+      <c r="D10" s="93" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="50" t="n">
@@ -4654,17 +4755,17 @@
       </c>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="86" t="s">
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="87" t="n">
+      <c r="B11" s="92" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="87" t="n">
+      <c r="C11" s="92" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="88" t="n">
+      <c r="D11" s="93" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="50" t="n">
@@ -4687,17 +4788,17 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="86" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="87" t="n">
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="91" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="92" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="87" t="n">
+      <c r="C12" s="92" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="88" t="n">
+      <c r="D12" s="93" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="50" t="n">
@@ -4720,17 +4821,17 @@
       </c>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="86" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="87" t="n">
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="91" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" s="92" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="87" t="n">
+      <c r="C13" s="92" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="88" t="n">
+      <c r="D13" s="93" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="50" t="n">
@@ -4753,17 +4854,17 @@
       </c>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="86" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="87" t="n">
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="91" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="92" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="87" t="n">
+      <c r="C14" s="92" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="88" t="n">
+      <c r="D14" s="93" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="50" t="n">
@@ -4786,17 +4887,17 @@
       </c>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="86" t="s">
-        <v>170</v>
-      </c>
-      <c r="B15" s="87" t="n">
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="91" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="92" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="87" t="n">
+      <c r="C15" s="92" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="88" t="n">
+      <c r="D15" s="93" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="50" t="n">
@@ -4819,17 +4920,17 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="89" t="s">
-        <v>171</v>
-      </c>
-      <c r="B16" s="90" t="n">
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="94" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="95" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="90" t="n">
+      <c r="C16" s="95" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="90" t="n">
+      <c r="D16" s="95" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="57" t="n">
@@ -4897,8 +4998,8 @@
       <c r="F19" s="49"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="84" t="s">
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="89" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
@@ -4987,91 +5088,92 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="91" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="91" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="91" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="91" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="91" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="52.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="95" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="95" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="94"/>
-      <c r="B3" s="94" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="94" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" s="95" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" s="95" t="s">
-        <v>176</v>
+      <c r="D3" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="94"/>
-      <c r="B4" s="94" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="94" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="95" t="s">
-        <v>179</v>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="96"/>
-      <c r="B5" s="96" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="E5" s="96"/>
-    </row>
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="64"/>
+    </row>
+    <row r="6" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5116,13 +5218,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+        <v>188</v>
+      </c>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
@@ -5131,117 +5233,117 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
     </row>
     <row r="6" s="2" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
     </row>
     <row r="7" s="2" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -5252,149 +5354,149 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="74" t="s">
-        <v>198</v>
+      <c r="B10" s="79" t="s">
+        <v>204</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F10" s="97"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F11" s="22"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
+        <v>210</v>
+      </c>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
@@ -5403,114 +5505,114 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F17" s="23"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="42" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E18" s="43"/>
       <c r="F18" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
+        <v>220</v>
+      </c>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="77"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="79" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" s="79" t="s">
+      <c r="B19" s="84" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="79" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="79"/>
+      <c r="D19" s="84" t="s">
+        <v>222</v>
+      </c>
+      <c r="E19" s="84"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
       <c r="F20" s="28"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="72"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="98"/>
@@ -5519,114 +5621,114 @@
       <c r="D21" s="99"/>
       <c r="E21" s="99"/>
       <c r="F21" s="100"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="74" t="s">
-        <v>217</v>
+      <c r="B22" s="79" t="s">
+        <v>223</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F22" s="97"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F23" s="22"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C24" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
+        <v>229</v>
+      </c>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="79" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="79" t="s">
+      <c r="B25" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="E25" s="79"/>
+      <c r="D25" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" s="84"/>
       <c r="F25" s="28"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="78"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
+      <c r="A26" s="83"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -5635,114 +5737,114 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F29" s="23"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="42" t="s">
         <v>68</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C30" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E30" s="43"/>
       <c r="F30" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
+        <v>239</v>
+      </c>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="79" t="s">
-        <v>234</v>
-      </c>
-      <c r="C31" s="79" t="s">
+      <c r="B31" s="84" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="79" t="s">
-        <v>235</v>
-      </c>
-      <c r="E31" s="79"/>
+      <c r="D31" s="84" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" s="84"/>
       <c r="F31" s="28"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="78"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
@@ -5751,74 +5853,74 @@
       <c r="D33" s="101"/>
       <c r="E33" s="101"/>
       <c r="F33" s="102"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="72"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="72"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="77"/>
+      <c r="K37" s="77"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="77"/>
+      <c r="K38" s="77"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="72"/>
-      <c r="K41" s="72"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="72"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="72"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="77"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5858,13 +5960,13 @@
         <v>80</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D1" s="45" t="s">
         <v>82</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F1" s="45" t="s">
         <v>27</v>
@@ -5885,7 +5987,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="48" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B2" s="49" t="n">
         <v>0</v>
@@ -5917,7 +6019,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B3" s="49" t="n">
         <v>1</v>
@@ -5949,7 +6051,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="48" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B4" s="49" t="n">
         <v>2</v>
@@ -5981,7 +6083,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B5" s="49" t="n">
         <v>3</v>
@@ -6013,7 +6115,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="48" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B6" s="49" t="n">
         <v>4</v>
@@ -6045,7 +6147,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B7" s="49" t="n">
         <v>5</v>
@@ -6077,7 +6179,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B8" s="49" t="n">
         <v>6</v>
@@ -6109,7 +6211,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B9" s="49" t="n">
         <v>7</v>
@@ -6141,7 +6243,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B10" s="49" t="n">
         <v>8</v>
@@ -6173,7 +6275,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B11" s="49" t="n">
         <v>9</v>
@@ -6205,7 +6307,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B12" s="49" t="n">
         <v>10</v>
@@ -6237,7 +6339,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B13" s="49" t="n">
         <v>11</v>
@@ -6269,7 +6371,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B14" s="49" t="n">
         <v>12</v>
@@ -6301,7 +6403,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="104" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B15" s="56" t="n">
         <v>13</v>
@@ -6400,6 +6502,170 @@
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J34" s="50"/>
     </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="45.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="52.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="64"/>
+    </row>
+    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="63"/>
+      <c r="B6" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="66"/>
+      <c r="B8" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="68"/>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,9 +14,10 @@
     <sheet name="Scripts-CIC17" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="CIC17" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Análisis estadístico CIC17" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Scripts-BCCC17" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="BCCC17" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Análisis estadístico BCCC17" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Modelos simples CIC17" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Scripts-BCCC17" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="BCCC17" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Análisis estadístico BCCC17" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="265">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -2938,6 +2939,170 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="45.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="52.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="64"/>
+    </row>
+    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="63"/>
+      <c r="B6" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="66"/>
+      <c r="B8" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="68"/>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -5190,6 +5355,108 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="52.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="64"/>
+    </row>
+    <row r="6" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5933,7 +6200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6511,168 +6778,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="45.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="52.63"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="62" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>189</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64" t="s">
-        <v>257</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="65" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64" t="s">
-        <v>259</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>258</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>260</v>
-      </c>
-      <c r="E5" s="64"/>
-    </row>
-    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63"/>
-      <c r="B6" s="64" t="s">
-        <v>262</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>263</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>189</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="64"/>
-      <c r="B7" s="64" t="s">
-        <v>257</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>256</v>
-      </c>
-      <c r="E7" s="65" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="66"/>
-      <c r="B8" s="66" t="s">
-        <v>259</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>258</v>
-      </c>
-      <c r="E8" s="67" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68"/>
-      <c r="B9" s="68" t="s">
-        <v>261</v>
-      </c>
-      <c r="C9" s="69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" s="68"/>
-    </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/02_datasets/metadata/METADATA.xlsx
+++ b/02_datasets/metadata/METADATA.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="280">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -1026,6 +1026,53 @@
     <t xml:space="preserve">CIC17__scaled__v1__pca_analisis__v1</t>
   </si>
   <si>
+    <t xml:space="preserve">RESULTADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPIEZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPLIT DATASET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divide el dataset en 80/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__split__v1__train.csv
+CIC17__split__v1__test.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE + PCA4 + KNN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__split__v1__pca4_knn__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicamos un cross validation con k = 5. Usamos PCA con 4 componentes y entrenamos un modelo de 5NN usando distancia de euclidea (no tiene sentido usar Mahalanobis si usamos PCA).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__split__v1__train.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE + PCA4 + KNN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__split__v1__RUS_SMOTE_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicamos RUS/SMOTE con 10000 por clase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE__v1__train.csv
+CIC17__RUS_SMOTE__v1__test.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE__v1__pca4_knn__v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIC17__RUS_SMOTE__v1__train.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">MODELOS GENERADOS</t>
   </si>
   <si>
@@ -1464,7 +1511,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1528,6 +1575,14 @@
     <font>
       <b val="true"/>
       <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Code PL"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
       <color rgb="FFC9211E"/>
       <name val="Cascadia Code PL"/>
       <family val="0"/>
@@ -1579,7 +1634,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1699,6 +1754,27 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1725,7 +1801,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2114,19 +2190,79 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2896,7 +3032,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="s">
         <v>68</v>
       </c>
@@ -2933,8 +3069,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2945,7 +3081,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="45.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="74.49"/>
@@ -2974,116 +3110,116 @@
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>102</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="64"/>
       <c r="B3" s="64" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>105</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="64"/>
       <c r="B4" s="64" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C4" s="64" t="s">
         <v>108</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="64"/>
       <c r="B5" s="64" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C5" s="65" t="s">
         <v>111</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="63"/>
       <c r="B6" s="64" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E6" s="65" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="64"/>
       <c r="B7" s="64" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C7" s="64" t="s">
         <v>105</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="66"/>
       <c r="B8" s="66" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C8" s="66" t="s">
         <v>108</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="E8" s="67" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="68"/>
       <c r="B9" s="68" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C9" s="69" t="s">
         <v>111</v>
       </c>
       <c r="D9" s="69" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E9" s="68"/>
     </row>
@@ -3097,8 +3233,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3809,8 +3945,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3821,7 +3957,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="45.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="74.49"/>
@@ -3915,8 +4051,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -4564,8 +4700,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5242,8 +5378,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5254,7 +5390,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="45.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="74.49"/>
@@ -5344,8 +5480,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5355,14 +5491,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="45.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="74.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="74.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="55.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="97" width="71.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5381,9 +5518,14 @@
       <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="98" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63"/>
+      <c r="A2" s="63" t="s">
+        <v>189</v>
+      </c>
       <c r="B2" s="64" t="s">
         <v>181</v>
       </c>
@@ -5396,58 +5538,84 @@
       <c r="E2" s="65" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64"/>
+      <c r="F2" s="99"/>
+    </row>
+    <row r="3" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="63" t="s">
+        <v>190</v>
+      </c>
       <c r="B3" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="64" t="s">
-        <v>105</v>
+      <c r="C3" s="65" t="s">
+        <v>191</v>
       </c>
       <c r="D3" s="65" t="s">
         <v>182</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="64"/>
-    </row>
-    <row r="6" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>192</v>
+      </c>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="100" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="101" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="102" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="102" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+    </row>
+    <row r="5" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="104" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="105" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="105" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="106" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="106" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="107"/>
+    </row>
+    <row r="6" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="108" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="109" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="110" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="110" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" s="109"/>
+      <c r="F6" s="111"/>
+    </row>
+    <row r="7" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5485,7 +5653,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G1" s="77"/>
       <c r="H1" s="77"/>
@@ -5500,7 +5668,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
@@ -5515,13 +5683,13 @@
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
@@ -5536,16 +5704,16 @@
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="77"/>
@@ -5557,13 +5725,13 @@
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
@@ -5578,16 +5746,16 @@
     <row r="6" s="2" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="77"/>
@@ -5601,16 +5769,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -5621,16 +5789,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="77"/>
@@ -5644,16 +5812,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="77"/>
@@ -5667,18 +5835,18 @@
         <v>33</v>
       </c>
       <c r="B10" s="79" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="F10" s="97"/>
+        <v>220</v>
+      </c>
+      <c r="F10" s="112"/>
       <c r="G10" s="77"/>
       <c r="H10" s="77"/>
       <c r="I10" s="77"/>
@@ -5690,16 +5858,16 @@
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="77"/>
@@ -5713,17 +5881,17 @@
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G12" s="77"/>
       <c r="H12" s="77"/>
@@ -5736,13 +5904,13 @@
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
@@ -5783,16 +5951,16 @@
         <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="77"/>
@@ -5806,16 +5974,16 @@
         <v>46</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="77"/>
@@ -5829,17 +5997,17 @@
         <v>46</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E18" s="43"/>
       <c r="F18" s="39" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G18" s="77"/>
       <c r="H18" s="77"/>
@@ -5852,13 +6020,13 @@
         <v>46</v>
       </c>
       <c r="B19" s="84" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C19" s="84" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="84" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E19" s="84"/>
       <c r="F19" s="28"/>
@@ -5882,12 +6050,12 @@
       <c r="K20" s="77"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="98"/>
-      <c r="B21" s="99"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="100"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="77"/>
       <c r="H21" s="77"/>
       <c r="I21" s="77"/>
@@ -5899,18 +6067,18 @@
         <v>57</v>
       </c>
       <c r="B22" s="79" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="F22" s="97"/>
+        <v>239</v>
+      </c>
+      <c r="F22" s="112"/>
       <c r="G22" s="77"/>
       <c r="H22" s="77"/>
       <c r="I22" s="77"/>
@@ -5922,16 +6090,16 @@
         <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="77"/>
@@ -5945,17 +6113,17 @@
         <v>57</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C24" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="39" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="G24" s="77"/>
       <c r="H24" s="77"/>
@@ -5968,13 +6136,13 @@
         <v>57</v>
       </c>
       <c r="B25" s="84" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="C25" s="84" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="84" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="E25" s="84"/>
       <c r="F25" s="28"/>
@@ -6015,16 +6183,16 @@
         <v>68</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="F28" s="34"/>
       <c r="G28" s="77"/>
@@ -6038,16 +6206,16 @@
         <v>68</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="77"/>
@@ -6061,17 +6229,17 @@
         <v>68</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C30" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="E30" s="43"/>
       <c r="F30" s="39" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
@@ -6084,13 +6252,13 @@
         <v>68</v>
       </c>
       <c r="B31" s="84" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C31" s="84" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="84" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="E31" s="84"/>
       <c r="F31" s="28"/>
@@ -6115,11 +6283,11 @@
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="102"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="117"/>
       <c r="G33" s="77"/>
       <c r="H33" s="77"/>
       <c r="I33" s="77"/>
@@ -6194,8 +6362,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6219,7 +6387,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="103" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="118" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
         <v>79</v>
       </c>
@@ -6227,13 +6395,13 @@
         <v>80</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D1" s="45" t="s">
         <v>82</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="F1" s="45" t="s">
         <v>27</v>
@@ -6254,7 +6422,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="48" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B2" s="49" t="n">
         <v>0</v>
@@ -6286,7 +6454,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B3" s="49" t="n">
         <v>1</v>
@@ -6318,7 +6486,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="48" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B4" s="49" t="n">
         <v>2</v>
@@ -6350,7 +6518,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B5" s="49" t="n">
         <v>3</v>
@@ -6414,7 +6582,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B7" s="49" t="n">
         <v>5</v>
@@ -6446,7 +6614,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B8" s="49" t="n">
         <v>6</v>
@@ -6510,7 +6678,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="B10" s="49" t="n">
         <v>8</v>
@@ -6542,7 +6710,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="B11" s="49" t="n">
         <v>9</v>
@@ -6574,7 +6742,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B12" s="49" t="n">
         <v>10</v>
@@ -6606,7 +6774,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B13" s="49" t="n">
         <v>11</v>
@@ -6638,7 +6806,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B14" s="49" t="n">
         <v>12</v>
@@ -6669,7 +6837,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="119" t="s">
         <v>180</v>
       </c>
       <c r="B15" s="56" t="n">
@@ -6774,8 +6942,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>